--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5169092-D08D-4B8E-B38D-02AC05C49E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DF89FD-9B7B-45B4-8451-053E1E3E093E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend" sheetId="8" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="150">
   <si>
     <t>L_den</t>
   </si>
@@ -362,9 +362,6 @@
     <t>Sum pi * (RR[Ni]-1)</t>
   </si>
   <si>
-    <t>YLL = YLLnat (= 0,2069215) ∙ AFtot</t>
-  </si>
-  <si>
     <t>Calculation of YLL and YLD</t>
   </si>
   <si>
@@ -554,6 +551,12 @@
   </si>
   <si>
     <t>YLD = YLD of the disease (= 0,0059261) * Aftot *  69.411.087</t>
+  </si>
+  <si>
+    <t>YLD = DW ∙ AFtot ∙ C0 (= 69.411.087)</t>
+  </si>
+  <si>
+    <t>YLL = YLLnat (= 0,2069215) ∙ Aftot * Summe der Exponierten</t>
   </si>
 </sst>
 </file>
@@ -759,7 +762,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -863,6 +866,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -891,7 +895,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1387,15 +1391,15 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
     </row>
     <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1404,70 +1408,70 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="62"/>
+      <c r="B10" s="63"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="J12" s="63" t="s">
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="J12" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="63"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
     </row>
     <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="H13" t="s">
         <v>76</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="O13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="65" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
@@ -1514,7 +1518,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="64"/>
+      <c r="A15" s="65"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1589,7 +1593,7 @@
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="65" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -1636,7 +1640,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="64"/>
+      <c r="A19" s="65"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1711,7 +1715,7 @@
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="65" t="s">
         <v>81</v>
       </c>
       <c r="B22" t="s">
@@ -1758,7 +1762,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="64"/>
+      <c r="A23" s="65"/>
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1809,10 +1813,10 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="62"/>
+      <c r="B32" s="63"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2006,22 +2010,22 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>75</v>
@@ -2177,7 +2181,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -2215,7 +2219,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -2288,7 +2292,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -2358,7 +2362,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -2393,69 +2397,69 @@
     </row>
     <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="67" t="s">
-        <v>93</v>
-      </c>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67" t="s">
+      <c r="D40" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="67"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="K40" s="68"/>
+      <c r="L40" s="68"/>
+      <c r="M40" s="68"/>
+      <c r="N40" s="68"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
         <v>88</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
-        <v>104</v>
+      <c r="A42" s="69" t="s">
+        <v>103</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>85</v>
@@ -2516,9 +2520,9 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="70"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -2557,9 +2561,9 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="69"/>
+      <c r="A44" s="70"/>
       <c r="B44" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -2610,21 +2614,21 @@
     </row>
     <row r="45" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="69" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="20"/>
@@ -2674,7 +2678,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="70"/>
+      <c r="A47" s="71"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
@@ -2732,9 +2736,9 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="70"/>
+      <c r="A48" s="71"/>
       <c r="B48" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C48" s="42">
         <f>(C47)/(1+C47)</f>
@@ -2757,9 +2761,9 @@
       <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="69"/>
-      <c r="B49" s="22" t="s">
-        <v>90</v>
+      <c r="A49" s="70"/>
+      <c r="B49" s="61" t="s">
+        <v>149</v>
       </c>
       <c r="C49" s="43">
         <f>0.2069215*C48</f>
@@ -2782,11 +2786,11 @@
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="69" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
@@ -2836,7 +2840,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="70"/>
+      <c r="A51" s="71"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
@@ -2894,9 +2898,9 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="70"/>
+      <c r="A52" s="71"/>
       <c r="B52" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C52" s="42">
         <f>C51/(1+C51)</f>
@@ -2919,9 +2923,9 @@
       <c r="O52" s="15"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="69"/>
-      <c r="B53" s="22" t="s">
-        <v>137</v>
+      <c r="A53" s="70"/>
+      <c r="B53" s="61" t="s">
+        <v>136</v>
       </c>
       <c r="C53" s="43">
         <f>0.0115708*C52</f>
@@ -2944,11 +2948,11 @@
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="68" t="s">
+      <c r="A54" s="69" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
@@ -2998,7 +3002,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="70"/>
+      <c r="A55" s="71"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
@@ -3056,9 +3060,9 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="70"/>
+      <c r="A56" s="71"/>
       <c r="B56" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C56" s="42">
         <f>C55/(1+C55)</f>
@@ -3081,9 +3085,9 @@
       <c r="O56" s="15"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="69"/>
-      <c r="B57" s="22" t="s">
-        <v>138</v>
+      <c r="A57" s="70"/>
+      <c r="B57" s="61" t="s">
+        <v>137</v>
       </c>
       <c r="C57" s="43">
         <f>0.0059261*C56</f>
@@ -3106,11 +3110,11 @@
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="69" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="20"/>
@@ -3160,7 +3164,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="70"/>
+      <c r="A59" s="71"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
@@ -3218,9 +3222,9 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="70"/>
+      <c r="A60" s="71"/>
       <c r="B60" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C60" s="15">
         <f>C59/(1+C59)</f>
@@ -3243,9 +3247,9 @@
       <c r="O60" s="15"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="69"/>
-      <c r="B61" s="22" t="s">
-        <v>139</v>
+      <c r="A61" s="70"/>
+      <c r="B61" s="61" t="s">
+        <v>138</v>
       </c>
       <c r="C61" s="22">
         <f>0.00127695*C60</f>
@@ -3268,11 +3272,11 @@
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="69" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" s="21">
         <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
@@ -3320,9 +3324,9 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="64"/>
+      <c r="A63" s="65"/>
       <c r="B63" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E63">
         <f>$E$44*E62</f>
@@ -3370,9 +3374,9 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="64"/>
+      <c r="A64" s="65"/>
       <c r="B64" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C64">
         <f>SUM(K63:O63)</f>
@@ -3385,9 +3389,9 @@
       <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="69"/>
-      <c r="B65" s="47" t="s">
-        <v>96</v>
+      <c r="A65" s="70"/>
+      <c r="B65" s="72" t="s">
+        <v>148</v>
       </c>
       <c r="C65" s="36">
         <f>C64*$J$30*69411087</f>
@@ -3432,14 +3436,14 @@
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
       <c r="E67" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F67" s="29"/>
       <c r="G67" s="29"/>
       <c r="H67" s="29"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L67" s="29"/>
       <c r="M67" s="29"/>
@@ -3454,40 +3458,40 @@
         <v>88</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="J68" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="68" t="s">
-        <v>104</v>
+      <c r="A69" s="69" t="s">
+        <v>103</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>85</v>
@@ -3540,9 +3544,9 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="70"/>
+      <c r="A70" s="71"/>
       <c r="B70" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
@@ -3579,9 +3583,9 @@
       <c r="O70" s="15"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="69"/>
+      <c r="A71" s="70"/>
       <c r="B71" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="31"/>
@@ -3629,14 +3633,14 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72" s="40"/>
       <c r="C72" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="40" t="s">
         <v>102</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>103</v>
       </c>
       <c r="E72" s="41"/>
       <c r="F72" s="41"/>
@@ -3651,11 +3655,11 @@
       <c r="O72" s="15"/>
     </row>
     <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="65" t="s">
+      <c r="A73" s="66" t="s">
         <v>53</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E73" s="34">
         <f>IF(E70&gt;$I$31,((19.4312 - 0.9336 *  E70 + 0.0126 *  E70^2)/100),0)</f>
@@ -3699,9 +3703,9 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="65"/>
+      <c r="A74" s="66"/>
       <c r="B74" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E74" s="34">
         <f>E73*E71</f>
@@ -3745,9 +3749,9 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="65"/>
+      <c r="A75" s="66"/>
       <c r="B75" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C75" s="34">
         <f>SUM(J74:N74)</f>
@@ -3759,9 +3763,9 @@
       </c>
     </row>
     <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
-      <c r="B76" s="47" t="s">
-        <v>96</v>
+      <c r="A76" s="67"/>
+      <c r="B76" s="72" t="s">
+        <v>95</v>
       </c>
       <c r="C76" s="36">
         <f>C75*J31*69411087</f>
@@ -3785,23 +3789,23 @@
     </row>
     <row r="79" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D80" t="s">
         <v>102</v>
       </c>
-      <c r="D80" t="s">
-        <v>103</v>
-      </c>
       <c r="E80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C81" s="48">
         <f>C61+C65+C76</f>
@@ -3818,7 +3822,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C82" s="49">
         <f>C81*70000</f>
@@ -3833,7 +3837,7 @@
         <v>586271389.76075816</v>
       </c>
       <c r="F82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3973,22 +3977,22 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>75</v>
@@ -4144,7 +4148,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -4182,7 +4186,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -4255,7 +4259,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -4325,7 +4329,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -4360,69 +4364,69 @@
     </row>
     <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="67" t="s">
-        <v>93</v>
-      </c>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67" t="s">
+      <c r="D40" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="67"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="K40" s="68"/>
+      <c r="L40" s="68"/>
+      <c r="M40" s="68"/>
+      <c r="N40" s="68"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
         <v>88</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
-        <v>104</v>
+      <c r="A42" s="69" t="s">
+        <v>103</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>85</v>
@@ -4483,9 +4487,9 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="70"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -4524,9 +4528,9 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="69"/>
+      <c r="A44" s="70"/>
       <c r="B44" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -4577,21 +4581,21 @@
     </row>
     <row r="45" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="69" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="20"/>
@@ -4641,7 +4645,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="70"/>
+      <c r="A47" s="71"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
@@ -4699,9 +4703,9 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="70"/>
+      <c r="A48" s="71"/>
       <c r="B48" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C48" s="42">
         <f>(C47)/(1+C47)</f>
@@ -4724,16 +4728,16 @@
       <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="69"/>
-      <c r="B49" s="71" t="s">
-        <v>146</v>
+      <c r="A49" s="70"/>
+      <c r="B49" s="61" t="s">
+        <v>145</v>
       </c>
       <c r="C49" s="43">
         <f>0.2069215*C48 * 69411087</f>
         <v>674918.72002453846</v>
       </c>
       <c r="D49" s="22">
-        <f>0.2069215*D48 *69411087</f>
+        <f>0.2069215 * D48 * 69411087</f>
         <v>849375.21856915392</v>
       </c>
       <c r="E49" s="18"/>
@@ -4749,11 +4753,11 @@
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="69" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
@@ -4803,7 +4807,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="70"/>
+      <c r="A51" s="71"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
@@ -4861,9 +4865,9 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="70"/>
+      <c r="A52" s="71"/>
       <c r="B52" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C52" s="42">
         <f>C51/(1+C51)</f>
@@ -4886,9 +4890,9 @@
       <c r="O52" s="15"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="69"/>
-      <c r="B53" s="71" t="s">
-        <v>147</v>
+      <c r="A53" s="70"/>
+      <c r="B53" s="61" t="s">
+        <v>146</v>
       </c>
       <c r="C53" s="43">
         <f>0.0115708*C52 * 69411087</f>
@@ -4911,11 +4915,11 @@
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="68" t="s">
+      <c r="A54" s="69" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
@@ -4965,7 +4969,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="70"/>
+      <c r="A55" s="71"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
@@ -5023,9 +5027,9 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="70"/>
+      <c r="A56" s="71"/>
       <c r="B56" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C56" s="42">
         <f>C55/(1+C55)</f>
@@ -5048,9 +5052,9 @@
       <c r="O56" s="15"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="69"/>
-      <c r="B57" s="71" t="s">
-        <v>148</v>
+      <c r="A57" s="70"/>
+      <c r="B57" s="61" t="s">
+        <v>147</v>
       </c>
       <c r="C57" s="43">
         <f>0.0059261*C56 * 69411087</f>
@@ -5073,11 +5077,11 @@
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="69" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="20"/>
@@ -5127,7 +5131,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="70"/>
+      <c r="A59" s="71"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
@@ -5185,9 +5189,9 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="70"/>
+      <c r="A60" s="71"/>
       <c r="B60" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C60" s="15">
         <f>C59/(1+C59)</f>
@@ -5210,9 +5214,9 @@
       <c r="O60" s="15"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="69"/>
+      <c r="A61" s="70"/>
       <c r="B61" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C61" s="22">
         <f>0.00127695*C60 * 69411087</f>
@@ -5235,11 +5239,11 @@
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="69" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" s="21">
         <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
@@ -5287,9 +5291,9 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="64"/>
+      <c r="A63" s="65"/>
       <c r="B63" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E63">
         <f>$E$44*E62</f>
@@ -5337,9 +5341,9 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="64"/>
+      <c r="A64" s="65"/>
       <c r="B64" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C64">
         <f>SUM(K63:O63)</f>
@@ -5352,9 +5356,9 @@
       <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="69"/>
+      <c r="A65" s="70"/>
       <c r="B65" s="47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65" s="36">
         <f>C64*$J$30*69411087</f>
@@ -5399,14 +5403,14 @@
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
       <c r="E67" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F67" s="29"/>
       <c r="G67" s="29"/>
       <c r="H67" s="29"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L67" s="29"/>
       <c r="M67" s="29"/>
@@ -5421,40 +5425,40 @@
         <v>88</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="J68" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="68" t="s">
-        <v>104</v>
+      <c r="A69" s="69" t="s">
+        <v>103</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>85</v>
@@ -5507,9 +5511,9 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="70"/>
+      <c r="A70" s="71"/>
       <c r="B70" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
@@ -5546,9 +5550,9 @@
       <c r="O70" s="15"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="69"/>
+      <c r="A71" s="70"/>
       <c r="B71" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="31"/>
@@ -5596,14 +5600,14 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72" s="40"/>
       <c r="C72" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="40" t="s">
         <v>102</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>103</v>
       </c>
       <c r="E72" s="41"/>
       <c r="F72" s="41"/>
@@ -5618,11 +5622,11 @@
       <c r="O72" s="15"/>
     </row>
     <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="65" t="s">
+      <c r="A73" s="66" t="s">
         <v>53</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E73" s="34">
         <f>IF(E70&gt;$I$31,((19.4312 - 0.9336 *  E70 + 0.0126 *  E70^2)/100),0)</f>
@@ -5666,9 +5670,9 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="65"/>
+      <c r="A74" s="66"/>
       <c r="B74" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E74" s="34">
         <f>E73*E71</f>
@@ -5712,9 +5716,9 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="65"/>
+      <c r="A75" s="66"/>
       <c r="B75" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C75" s="34">
         <f>SUM(J74:N74)</f>
@@ -5726,9 +5730,9 @@
       </c>
     </row>
     <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
+      <c r="A76" s="67"/>
       <c r="B76" s="47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" s="36">
         <f>C75*J31*69411087</f>
@@ -5752,23 +5756,23 @@
     </row>
     <row r="79" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
+        <v>101</v>
+      </c>
+      <c r="D80" t="s">
         <v>102</v>
       </c>
-      <c r="D80" t="s">
-        <v>103</v>
-      </c>
       <c r="E80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C81" s="48">
         <f>C61+C65+C76</f>
@@ -5785,7 +5789,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C82" s="49">
         <f>C81*70000</f>
@@ -5800,21 +5804,21 @@
         <v>63692323273.707344</v>
       </c>
       <c r="F82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="J40:N40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A54:A57"/>
     <mergeCell ref="A58:A61"/>
     <mergeCell ref="A62:A65"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="A73:A76"/>
     <mergeCell ref="D40:I40"/>
-    <mergeCell ref="J40:N40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5832,13 +5836,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5846,10 +5850,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5857,10 +5861,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5868,10 +5872,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5879,10 +5883,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
         <v>142</v>
-      </c>
-      <c r="C5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5890,10 +5894,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,23 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DF89FD-9B7B-45B4-8451-053E1E3E093E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9429B309-3E10-4FDE-97A6-BA5C75FFA764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend" sheetId="8" r:id="rId1"/>
     <sheet name="Agglomeration road" sheetId="1" r:id="rId2"/>
-    <sheet name="Agglomeration road (YLL_YLD)" sheetId="12" r:id="rId3"/>
-    <sheet name="Fragen" sheetId="11" r:id="rId4"/>
-    <sheet name="ERF HRA" sheetId="10" r:id="rId5"/>
-    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId6"/>
-    <sheet name="Agglomeration rail" sheetId="2" r:id="rId7"/>
-    <sheet name="Agglomeration air" sheetId="3" r:id="rId8"/>
-    <sheet name="Agglomeration industry" sheetId="4" r:id="rId9"/>
-    <sheet name="Major roads " sheetId="5" r:id="rId10"/>
-    <sheet name="Major railways " sheetId="6" r:id="rId11"/>
-    <sheet name="Major airports" sheetId="7" r:id="rId12"/>
+    <sheet name="Fragen" sheetId="11" r:id="rId3"/>
+    <sheet name="ERF HRA" sheetId="10" r:id="rId4"/>
+    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId5"/>
+    <sheet name="Agglomeration rail" sheetId="2" r:id="rId6"/>
+    <sheet name="Agglomeration air" sheetId="3" r:id="rId7"/>
+    <sheet name="Agglomeration industry" sheetId="4" r:id="rId8"/>
+    <sheet name="Major roads " sheetId="5" r:id="rId9"/>
+    <sheet name="Major railways " sheetId="6" r:id="rId10"/>
+    <sheet name="Major airports" sheetId="7" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="149">
   <si>
     <t>L_den</t>
   </si>
@@ -377,9 +376,6 @@
     <t>number of people exposed according to END (Lnight &gt;= 50 dB(A))</t>
   </si>
   <si>
-    <t>YLD = DW ∙ AFtot ∙ Co (= 69.411.087)</t>
-  </si>
-  <si>
     <t>High noise annoyance (HA)</t>
   </si>
   <si>
@@ -498,12 +494,6 @@
 Lnight70</t>
   </si>
   <si>
-    <t>Korrekt berechnet?</t>
-  </si>
-  <si>
-    <t>number of observed cases (Co) in each country</t>
-  </si>
-  <si>
     <t>Frage</t>
   </si>
   <si>
@@ -513,50 +503,59 @@
     <t>#</t>
   </si>
   <si>
-    <t>Bevölkerung über 18? "Co represents the total target population size"</t>
-  </si>
-  <si>
-    <t>YLD = YLD of the disease (= 0,0115708) * AFtot</t>
-  </si>
-  <si>
-    <t>YLD = YLD of the disease (= 0,0059261) * AFtot</t>
-  </si>
-  <si>
-    <t>YLD = YLD of the disease (= 0,001276950) * AFtot</t>
-  </si>
-  <si>
     <t>1 DALY = 70.000 EUR</t>
   </si>
   <si>
-    <t>bei HA und HSD: auch für midpoint of noise exposure in each category?
-"/100" für AR?</t>
-  </si>
-  <si>
     <t>HA/ HSD</t>
   </si>
   <si>
-    <t>Threshold?</t>
-  </si>
-  <si>
-    <t>in Annex 4: "All estimates are per person and per year" -&gt; also noch Multiplikation mit Personen/ Exponierten/ Bundesdeutsche Bevölkerung notwendig?</t>
-  </si>
-  <si>
     <t>YYL/ YLD für  mortality, CVD, Diabetes, IHD nach 2019 GBD</t>
   </si>
   <si>
-    <t>YLL = YLLnat (= 0,2069215) ∙ Aftot *  69.411.087</t>
-  </si>
-  <si>
-    <t>YLD = YLD of the disease (= 0,0115708) * Aftot *  69.411.087</t>
-  </si>
-  <si>
-    <t>YLD = YLD of the disease (= 0,0059261) * Aftot *  69.411.087</t>
-  </si>
-  <si>
-    <t>YLD = DW ∙ AFtot ∙ C0 (= 69.411.087)</t>
-  </si>
-  <si>
-    <t>YLL = YLLnat (= 0,2069215) ∙ Aftot * Summe der Exponierten</t>
+    <t>YLL = YLLnat (= 0,2069215) ∙ AFtot * Summe der Exponierten</t>
+  </si>
+  <si>
+    <t>YLD = YLD of the disease (= 0,0115708) * AFtot * Summe der Exponierten</t>
+  </si>
+  <si>
+    <t>YLD = YLD of the disease (= 0,0059261) * AFtot * Summe der Exponierten</t>
+  </si>
+  <si>
+    <t>YLD = YLD of the disease (= 0,001276950) * AFtot * Summe der Exponierten</t>
+  </si>
+  <si>
+    <t>YLD = DW * AFtot * Summe der Exponierten</t>
+  </si>
+  <si>
+    <t>ETC HE model</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Ballungsraum Straße</t>
+  </si>
+  <si>
+    <t>Korrekt berechnet? JA</t>
+  </si>
+  <si>
+    <t>bei HA und HSD:
+auch für midpoint of noise exposure in each category? JA
+"/100" für AR? JA</t>
+  </si>
+  <si>
+    <t>number of observed cases (Co) in each country / 
+"Co represents the total target population size"</t>
+  </si>
+  <si>
+    <t>Summe Belasteter in betreffender Kategorie ODER Summe Einwohner*innen in betreffender Kategorie
+(Kategorie hier: zB Straßen Ballungsraum)</t>
+  </si>
+  <si>
+    <t>Threshold? JA - umgesetzt</t>
+  </si>
+  <si>
+    <t>in Annex 4: "All estimates are per person and per year" -&gt; also  Multiplikation mit Exponierten der Kategorie (zB Ballungsraum Straßen) notwendig</t>
   </si>
 </sst>
 </file>
@@ -667,26 +666,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -762,7 +754,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -836,9 +828,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -848,25 +837,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -895,7 +868,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1367,11 +1354,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
@@ -1391,15 +1380,15 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
     </row>
     <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1408,70 +1397,70 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="63"/>
+      <c r="B10" s="52"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="J12" s="64" t="s">
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="J12" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="64"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
     </row>
     <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="H13" t="s">
         <v>76</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="O13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="54" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
@@ -1518,7 +1507,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
+      <c r="A15" s="54"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1593,7 +1582,7 @@
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="54" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -1640,7 +1629,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="65"/>
+      <c r="A19" s="54"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1715,7 +1704,7 @@
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="54" t="s">
         <v>81</v>
       </c>
       <c r="B22" t="s">
@@ -1762,7 +1751,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="65"/>
+      <c r="A23" s="54"/>
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1813,36 +1802,70 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="63" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="63"/>
+      <c r="A32" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="52"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>27</v>
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C35" s="8">
         <f>'Agglomeration road'!C18</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="8">
+      <c r="D35" s="8">
         <f>'Agglomeration road'!C19</f>
         <v>15021000</v>
       </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="8"/>
       <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="45">
+        <f>'Agglomeration road'!C81</f>
+        <v>6282.0875246781688</v>
+      </c>
+      <c r="D38" s="45">
+        <f>'Agglomeration road'!D81</f>
+        <v>278207.48309284041</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="66">
+        <f>'Agglomeration road'!C82</f>
+        <v>439746126.72747183</v>
+      </c>
+      <c r="D39" s="66">
+        <f>'Agglomeration road'!D82</f>
+        <v>19474523816.498829</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1861,16 +1884,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
-  <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1"/>
@@ -1880,7 +1893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1"/>
@@ -2010,22 +2023,22 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>75</v>
@@ -2181,7 +2194,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -2219,7 +2232,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -2292,7 +2305,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -2362,7 +2375,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -2403,69 +2416,69 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="68" t="s">
+      <c r="D40" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68" t="s">
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
         <v>88</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="56" t="s">
+      <c r="A42" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="64" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="20"/>
-      <c r="D42" s="57">
+      <c r="D42" s="37">
         <f>SUM(E42:O42)</f>
         <v>20796420.796399999</v>
       </c>
@@ -2520,9 +2533,9 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="71"/>
+      <c r="A43" s="60"/>
       <c r="B43" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -2561,9 +2574,9 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="70"/>
-      <c r="B44" s="16" t="s">
-        <v>110</v>
+      <c r="A44" s="59"/>
+      <c r="B44" s="24" t="s">
+        <v>109</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -2614,21 +2627,21 @@
     </row>
     <row r="45" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C45" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="69" t="s">
+      <c r="A46" s="58" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="20"/>
@@ -2678,7 +2691,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="71"/>
+      <c r="A47" s="60"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
@@ -2736,9 +2749,9 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="71"/>
+      <c r="A48" s="60"/>
       <c r="B48" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C48" s="42">
         <f>(C47)/(1+C47)</f>
@@ -2761,17 +2774,17 @@
       <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="70"/>
-      <c r="B49" s="61" t="s">
-        <v>149</v>
+      <c r="A49" s="59"/>
+      <c r="B49" s="63" t="s">
+        <v>135</v>
       </c>
       <c r="C49" s="43">
-        <f>0.2069215*C48</f>
-        <v>9.7235002244603734E-3</v>
+        <f>0.2069215*C48*D42</f>
+        <v>202214.00228176778</v>
       </c>
       <c r="D49" s="22">
-        <f>0.2069215*D48</f>
-        <v>1.2236881098968439E-2</v>
+        <f>0.2069215*D48*D42</f>
+        <v>254483.32856966133</v>
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
@@ -2786,11 +2799,11 @@
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="69" t="s">
+      <c r="A50" s="58" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
@@ -2840,7 +2853,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="71"/>
+      <c r="A51" s="60"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
@@ -2898,9 +2911,9 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="71"/>
+      <c r="A52" s="60"/>
       <c r="B52" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C52" s="42">
         <f>C51/(1+C51)</f>
@@ -2923,17 +2936,17 @@
       <c r="O52" s="15"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="70"/>
-      <c r="B53" s="61" t="s">
+      <c r="A53" s="59"/>
+      <c r="B53" s="63" t="s">
         <v>136</v>
       </c>
       <c r="C53" s="43">
-        <f>0.0115708*C52</f>
-        <v>3.1949680584372579E-4</v>
+        <f>0.0115708*C52*D42</f>
+        <v>6644.3900174318323</v>
       </c>
       <c r="D53" s="22">
-        <f>0.0115708*D52</f>
-        <v>4.0540822094705482E-4</v>
+        <f>0.0115708*D52*D42</f>
+        <v>8431.0399571348571</v>
       </c>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
@@ -2948,11 +2961,11 @@
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="58" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
@@ -3002,7 +3015,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="71"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
@@ -3060,9 +3073,9 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="71"/>
+      <c r="A56" s="60"/>
       <c r="B56" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C56" s="42">
         <f>C55/(1+C55)</f>
@@ -3085,17 +3098,17 @@
       <c r="O56" s="15"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="70"/>
-      <c r="B57" s="61" t="s">
+      <c r="A57" s="59"/>
+      <c r="B57" s="63" t="s">
         <v>137</v>
       </c>
       <c r="C57" s="43">
-        <f>0.0059261*C56</f>
-        <v>3.1296856885007095E-4</v>
+        <f>0.0059261*C56*D42</f>
+        <v>6508.6260538531606</v>
       </c>
       <c r="D57" s="22">
-        <f>0.0059261*D56</f>
-        <v>3.9290652602748795E-4</v>
+        <f>0.0059261*D56*D42</f>
+        <v>8171.0494489193279</v>
       </c>
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
@@ -3110,11 +3123,11 @@
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="69" t="s">
+      <c r="A58" s="58" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="20"/>
@@ -3164,7 +3177,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="71"/>
+      <c r="A59" s="60"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
@@ -3222,9 +3235,9 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="71"/>
+      <c r="A60" s="60"/>
       <c r="B60" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C60" s="15">
         <f>C59/(1+C59)</f>
@@ -3247,17 +3260,17 @@
       <c r="O60" s="15"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="70"/>
-      <c r="B61" s="61" t="s">
+      <c r="A61" s="59"/>
+      <c r="B61" s="63" t="s">
         <v>138</v>
       </c>
       <c r="C61" s="22">
-        <f>0.00127695*C60</f>
-        <v>4.714049533915084E-5</v>
+        <f>0.00127695*C60*D42</f>
+        <v>980.35357762371382</v>
       </c>
       <c r="D61" s="43">
-        <f>0.00127695*D60</f>
-        <v>4.714049533915084E-5</v>
+        <f>0.00127695*D60*D42</f>
+        <v>980.35357762371382</v>
       </c>
       <c r="E61" s="18"/>
       <c r="F61" s="18"/>
@@ -3272,11 +3285,11 @@
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="69" t="s">
+      <c r="A62" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>108</v>
+      <c r="B62" s="34" t="s">
+        <v>107</v>
       </c>
       <c r="E62" s="21">
         <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
@@ -3324,9 +3337,9 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="65"/>
+      <c r="A63" s="54"/>
       <c r="B63" s="34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E63">
         <f>$E$44*E62</f>
@@ -3374,9 +3387,9 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="65"/>
+      <c r="A64" s="54"/>
       <c r="B64" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C64">
         <f>SUM(K63:O63)</f>
@@ -3389,17 +3402,17 @@
       <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="70"/>
-      <c r="B65" s="72" t="s">
-        <v>148</v>
+      <c r="A65" s="59"/>
+      <c r="B65" s="65" t="s">
+        <v>139</v>
       </c>
       <c r="C65" s="36">
-        <f>C64*$J$30*69411087</f>
-        <v>690.22210906320026</v>
+        <f>C64*$J$30*D42</f>
+        <v>206.79908705445007</v>
       </c>
       <c r="D65" s="36">
-        <f>D64*$J$30*69411087</f>
-        <v>784.74255879444627</v>
+        <f>D64*$J$30*D42</f>
+        <v>235.11858371463006</v>
       </c>
       <c r="E65" s="18"/>
       <c r="F65" s="18"/>
@@ -3458,40 +3471,40 @@
         <v>88</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="J68" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M68" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="69" t="s">
-        <v>103</v>
+      <c r="A69" s="58" t="s">
+        <v>102</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>85</v>
@@ -3544,9 +3557,9 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="71"/>
+      <c r="A70" s="60"/>
       <c r="B70" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
@@ -3583,9 +3596,9 @@
       <c r="O70" s="15"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="70"/>
-      <c r="B71" s="16" t="s">
-        <v>110</v>
+      <c r="A71" s="59"/>
+      <c r="B71" s="24" t="s">
+        <v>109</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="31"/>
@@ -3633,14 +3646,14 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B72" s="40"/>
       <c r="C72" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="40" t="s">
         <v>101</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>102</v>
       </c>
       <c r="E72" s="41"/>
       <c r="F72" s="41"/>
@@ -3655,11 +3668,11 @@
       <c r="O72" s="15"/>
     </row>
     <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="66" t="s">
+      <c r="A73" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>108</v>
+      <c r="B73" s="34" t="s">
+        <v>107</v>
       </c>
       <c r="E73" s="34">
         <f>IF(E70&gt;$I$31,((19.4312 - 0.9336 *  E70 + 0.0126 *  E70^2)/100),0)</f>
@@ -3703,9 +3716,9 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
+      <c r="A74" s="55"/>
       <c r="B74" s="34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E74" s="34">
         <f>E73*E71</f>
@@ -3749,9 +3762,9 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
+      <c r="A75" s="55"/>
       <c r="B75" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75" s="34">
         <f>SUM(J74:N74)</f>
@@ -3763,17 +3776,17 @@
       </c>
     </row>
     <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="67"/>
-      <c r="B76" s="72" t="s">
-        <v>95</v>
+      <c r="A76" s="56"/>
+      <c r="B76" s="65" t="s">
+        <v>139</v>
       </c>
       <c r="C76" s="36">
-        <f>C75*J31*69411087</f>
-        <v>23543.370403221699</v>
+        <f>C75*J31*D69</f>
+        <v>5094.9348600000048</v>
       </c>
       <c r="D76" s="36">
-        <f>D75*J31*69411087</f>
-        <v>31824.142533445931</v>
+        <f>D75*J31*D69</f>
+        <v>6886.9465334103088</v>
       </c>
       <c r="E76" s="35"/>
       <c r="F76" s="35"/>
@@ -3789,55 +3802,58 @@
     </row>
     <row r="79" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D80" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
-        <v>107</v>
+        <v>106</v>
+      </c>
+      <c r="F80" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C81" s="48">
+        <v>99</v>
+      </c>
+      <c r="C81" s="61">
         <f>C61+C65+C76</f>
-        <v>24233.592559425393</v>
-      </c>
-      <c r="D81" s="48">
+        <v>6282.0875246781688</v>
+      </c>
+      <c r="D81" s="61">
         <f>D49+D53+D57+D65+D76</f>
-        <v>32608.898127436223</v>
+        <v>278207.48309284041</v>
       </c>
       <c r="E81" s="45">
         <f>D81-C81</f>
-        <v>8375.30556801083</v>
+        <v>271925.39556816226</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="C82" s="49">
+        <v>105</v>
+      </c>
+      <c r="C82" s="62">
         <f>C81*70000</f>
-        <v>1696351479.1597774</v>
-      </c>
-      <c r="D82" s="49">
+        <v>439746126.72747183</v>
+      </c>
+      <c r="D82" s="62">
         <f>D81*70000</f>
-        <v>2282622868.9205356</v>
+        <v>19474523816.498829</v>
       </c>
       <c r="E82" s="46">
         <f>D82-C82</f>
-        <v>586271389.76075816</v>
+        <v>19034777689.771358</v>
       </c>
       <c r="F82" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -3859,1973 +3875,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73CD4A7B-5043-4ACD-943E-75F29DF344B2}">
-  <dimension ref="A1:U82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="56.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="39.7109375" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="58" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.4250000000000001E-3</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4.1700000000000001E-3</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1.6857E-2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>6.8123000000000003E-2</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.278499</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.63092800000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="2">
-        <v>8.5990000000000007E-3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3.1836999999999997E-2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.14993899999999999</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.37795099999999998</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.431674</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="C12" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="6">
-        <f>Frontend!$H$15*C8</f>
-        <v>14817.435000000001</v>
-      </c>
-      <c r="D13" s="6">
-        <f>Frontend!$H$15*D8</f>
-        <v>43360.493999999999</v>
-      </c>
-      <c r="E13" s="6">
-        <f>Frontend!$H$15*E8</f>
-        <v>175282.45740000001</v>
-      </c>
-      <c r="F13" s="6">
-        <f>Frontend!$H$15*F8</f>
-        <v>708356.57860000001</v>
-      </c>
-      <c r="G13" s="6">
-        <f>Frontend!$H$15*G8</f>
-        <v>2895888.3018</v>
-      </c>
-      <c r="H13" s="6">
-        <f>Frontend!$H$15*H8</f>
-        <v>6560515.5296</v>
-      </c>
-      <c r="I13" s="6">
-        <f>SUM(C13:H13)</f>
-        <v>10398220.796399999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="6">
-        <f>Frontend!$O$15*C9</f>
-        <v>64582.789500000006</v>
-      </c>
-      <c r="D14" s="6">
-        <f>Frontend!$O$15*D9</f>
-        <v>239111.78849999997</v>
-      </c>
-      <c r="E14" s="6">
-        <f>Frontend!$O$15*E9</f>
-        <v>1126116.8595</v>
-      </c>
-      <c r="F14" s="6">
-        <f>Frontend!$O$15*F9</f>
-        <v>2838600.9855</v>
-      </c>
-      <c r="G14" s="6">
-        <f>Frontend!$O$15*G9</f>
-        <v>3242087.577</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="6">
-        <f>SUM(C14:G14)</f>
-        <v>7510500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="8">
-        <f>Frontend!$H$15+I13</f>
-        <v>20796420.796399999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="8">
-        <f>Frontend!$O$15+I14</f>
-        <v>15021000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="58" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="58" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" t="s">
-        <v>41</v>
-      </c>
-      <c r="I29" t="s">
-        <v>87</v>
-      </c>
-      <c r="J29" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29" t="s">
-        <v>70</v>
-      </c>
-      <c r="M29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="34">
-        <v>45</v>
-      </c>
-      <c r="J30">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" t="s">
-        <v>54</v>
-      </c>
-      <c r="H31" t="s">
-        <v>55</v>
-      </c>
-      <c r="I31" s="34">
-        <v>40</v>
-      </c>
-      <c r="J31">
-        <v>0.01</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="34">
-        <v>45</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H33" t="s">
-        <v>51</v>
-      </c>
-      <c r="I33">
-        <v>45</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" t="s">
-        <v>49</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" t="s">
-        <v>51</v>
-      </c>
-      <c r="I34">
-        <v>45</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H35" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35">
-        <v>53</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="58" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C40" s="15"/>
-      <c r="D40" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-    </row>
-    <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="D41" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="57">
-        <f>SUM(E42:O42)</f>
-        <v>20796420.796399999</v>
-      </c>
-      <c r="E42" s="21">
-        <f t="shared" ref="E42:J42" si="0">C13</f>
-        <v>14817.435000000001</v>
-      </c>
-      <c r="F42" s="21">
-        <f t="shared" si="0"/>
-        <v>43360.493999999999</v>
-      </c>
-      <c r="G42" s="21">
-        <f t="shared" si="0"/>
-        <v>175282.45740000001</v>
-      </c>
-      <c r="H42" s="21">
-        <f t="shared" si="0"/>
-        <v>708356.57860000001</v>
-      </c>
-      <c r="I42" s="21">
-        <f t="shared" si="0"/>
-        <v>2895888.3018</v>
-      </c>
-      <c r="J42" s="21">
-        <f t="shared" si="0"/>
-        <v>6560515.5296</v>
-      </c>
-      <c r="K42" s="21">
-        <f>Frontend!C15</f>
-        <v>3762100</v>
-      </c>
-      <c r="L42" s="21">
-        <f>Frontend!D15</f>
-        <v>3050900</v>
-      </c>
-      <c r="M42" s="21">
-        <f>Frontend!E15</f>
-        <v>2479000</v>
-      </c>
-      <c r="N42" s="21">
-        <f>Frontend!F15</f>
-        <v>1006400</v>
-      </c>
-      <c r="O42" s="21">
-        <f>Frontend!G15</f>
-        <v>99800</v>
-      </c>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="71"/>
-      <c r="B43" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15">
-        <v>27</v>
-      </c>
-      <c r="F43" s="15">
-        <v>32</v>
-      </c>
-      <c r="G43" s="15">
-        <v>37</v>
-      </c>
-      <c r="H43" s="15">
-        <v>42</v>
-      </c>
-      <c r="I43" s="15">
-        <v>47</v>
-      </c>
-      <c r="J43" s="15">
-        <v>52</v>
-      </c>
-      <c r="K43" s="15">
-        <v>57</v>
-      </c>
-      <c r="L43" s="15">
-        <v>62</v>
-      </c>
-      <c r="M43" s="15">
-        <v>67</v>
-      </c>
-      <c r="N43" s="15">
-        <v>72</v>
-      </c>
-      <c r="O43" s="16">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="70"/>
-      <c r="B44" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15">
-        <f t="shared" ref="E44:O44" si="1">E42/$D$42</f>
-        <v>7.1249928750071259E-4</v>
-      </c>
-      <c r="F44" s="15">
-        <f t="shared" si="1"/>
-        <v>2.0849979150020848E-3</v>
-      </c>
-      <c r="G44" s="15">
-        <f t="shared" si="1"/>
-        <v>8.4284915715084289E-3</v>
-      </c>
-      <c r="H44" s="15">
-        <f t="shared" si="1"/>
-        <v>3.4061465938534062E-2</v>
-      </c>
-      <c r="I44" s="15">
-        <f t="shared" si="1"/>
-        <v>0.13924936075063926</v>
-      </c>
-      <c r="J44" s="15">
-        <f t="shared" si="1"/>
-        <v>0.31546368453631546</v>
-      </c>
-      <c r="K44" s="15">
-        <f t="shared" si="1"/>
-        <v>0.18090132128174888</v>
-      </c>
-      <c r="L44" s="15">
-        <f t="shared" si="1"/>
-        <v>0.14670312886379619</v>
-      </c>
-      <c r="M44" s="15">
-        <f t="shared" si="1"/>
-        <v>0.11920320444896612</v>
-      </c>
-      <c r="N44" s="15">
-        <f t="shared" si="1"/>
-        <v>4.8392942701669828E-2</v>
-      </c>
-      <c r="O44" s="15">
-        <f t="shared" si="1"/>
-        <v>4.7989027043190075E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20">
-        <f>IF(E43&gt;$I$32, EXP((LN(1.055)/10)*(E43-$I$32)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="F46" s="20">
-        <f t="shared" ref="F46:O46" si="2">IF(F43&gt;$I$32, EXP((LN(1.055)/10)*(F43-$I$32)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="G46" s="20">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H46" s="20">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.0107656908500073</v>
-      </c>
-      <c r="J46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.0381897140207395</v>
-      </c>
-      <c r="K46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.0663578038467578</v>
-      </c>
-      <c r="L46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.09529014829188</v>
-      </c>
-      <c r="M46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.1250074830583294</v>
-      </c>
-      <c r="N46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.1555311064479334</v>
-      </c>
-      <c r="O46" s="20">
-        <f t="shared" si="2"/>
-        <v>1.1868828946265373</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="71"/>
-      <c r="B47" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" s="42">
-        <f>SUM(K47:O47)</f>
-        <v>4.9308310609276644E-2</v>
-      </c>
-      <c r="D47" s="15">
-        <f>SUM(E47:O47)</f>
-        <v>6.2854894074549819E-2</v>
-      </c>
-      <c r="E47" s="24">
-        <f>E44*(E46-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="24">
-        <f t="shared" ref="F47:O47" si="3">F44*(F46-1)</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="24">
-        <f>G44*(G46-1)</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="24">
-        <f t="shared" si="3"/>
-        <v>1.4991155689025278E-3</v>
-      </c>
-      <c r="J47" s="24">
-        <f t="shared" si="3"/>
-        <v>1.2047467896370654E-2</v>
-      </c>
-      <c r="K47" s="24">
-        <f t="shared" si="3"/>
-        <v>1.2004214393233608E-2</v>
-      </c>
-      <c r="L47" s="24">
-        <f t="shared" si="3"/>
-        <v>1.3979362904313918E-2</v>
-      </c>
-      <c r="M47" s="24">
-        <f t="shared" si="3"/>
-        <v>1.4901292560652712E-2</v>
-      </c>
-      <c r="N47" s="24">
-        <f t="shared" si="3"/>
-        <v>7.5266079226621535E-3</v>
-      </c>
-      <c r="O47" s="24">
-        <f t="shared" si="3"/>
-        <v>8.9683282841425394E-4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="71"/>
-      <c r="B48" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" s="42">
-        <f>(C47)/(1+C47)</f>
-        <v>4.6991251389828383E-2</v>
-      </c>
-      <c r="D48" s="17">
-        <f>(D47)/(1+D47)</f>
-        <v>5.9137794279320602E-2</v>
-      </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="70"/>
-      <c r="B49" s="61" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="43">
-        <f>0.2069215*C48 * 69411087</f>
-        <v>674918.72002453846</v>
-      </c>
-      <c r="D49" s="22">
-        <f>0.2069215 * D48 * 69411087</f>
-        <v>849375.21856915392</v>
-      </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20">
-        <f>IF(E43&gt;$I$33, EXP((LN(1.032)/10)*(E43-$I$33)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="F50" s="20">
-        <f t="shared" ref="F50:O50" si="4">IF(F43&gt;$I$33, EXP((LN(1.032)/10)*(F43-$I$33)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="G50" s="20">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H50" s="20">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.0063196184673233</v>
-      </c>
-      <c r="J50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.0222939440770498</v>
-      </c>
-      <c r="K50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.0385218462582777</v>
-      </c>
-      <c r="L50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.0550073502875155</v>
-      </c>
-      <c r="M50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.0717545453385426</v>
-      </c>
-      <c r="N50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.088767585496716</v>
-      </c>
-      <c r="O50" s="20">
-        <f t="shared" si="4"/>
-        <v>1.1060506907893759</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="71"/>
-      <c r="B51" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="42">
-        <f>SUM(K51:O51)</f>
-        <v>2.8396426647685286E-2</v>
-      </c>
-      <c r="D51" s="15">
-        <f>SUM(E51:O51)</f>
-        <v>3.6309359220840685E-2</v>
-      </c>
-      <c r="E51" s="15">
-        <f>E44*(E50-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="15">
-        <f t="shared" ref="F51:O51" si="5">F44*(F50-1)</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="15">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="15">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="15">
-        <f t="shared" si="5"/>
-        <v>8.8000283176270673E-4</v>
-      </c>
-      <c r="J51" s="15">
-        <f t="shared" si="5"/>
-        <v>7.0329297413926854E-3</v>
-      </c>
-      <c r="K51" s="15">
-        <f t="shared" si="5"/>
-        <v>6.9686528863348307E-3</v>
-      </c>
-      <c r="L51" s="15">
-        <f t="shared" si="5"/>
-        <v>8.0697503976853574E-3</v>
-      </c>
-      <c r="M51" s="15">
-        <f t="shared" si="5"/>
-        <v>8.5533717381329078E-3</v>
-      </c>
-      <c r="N51" s="15">
-        <f t="shared" si="5"/>
-        <v>4.2957246787081573E-3</v>
-      </c>
-      <c r="O51" s="15">
-        <f t="shared" si="5"/>
-        <v>5.0892694682403491E-4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="71"/>
-      <c r="B52" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" s="42">
-        <f>C51/(1+C51)</f>
-        <v>2.7612335002223338E-2</v>
-      </c>
-      <c r="D52" s="15">
-        <f>D51/(1+D51)</f>
-        <v>3.503718160775874E-2</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="70"/>
-      <c r="B53" s="61" t="s">
-        <v>146</v>
-      </c>
-      <c r="C53" s="43">
-        <f>0.0115708*C52 * 69411087</f>
-        <v>22176.620586640958</v>
-      </c>
-      <c r="D53" s="22">
-        <f>0.0115708*D52* 69411087</f>
-        <v>28139.825294671246</v>
-      </c>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20">
-        <f>IF(E43&gt;$I$34, EXP((LN(1.062)/10)*(E43-$I$34)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="F54" s="20">
-        <f t="shared" ref="F54:O54" si="6">IF(F43&gt;$I$34, EXP((LN(1.062)/10)*(F43-$I$34)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="G54" s="20">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="H54" s="20">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.0121034455497457</v>
-      </c>
-      <c r="J54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.043006852485771</v>
-      </c>
-      <c r="K54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.0748538591738301</v>
-      </c>
-      <c r="L54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.1076732773398887</v>
-      </c>
-      <c r="M54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.1414947984426076</v>
-      </c>
-      <c r="N54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.1763490205349618</v>
-      </c>
-      <c r="O54" s="20">
-        <f t="shared" si="6"/>
-        <v>1.2122674759460494</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="71"/>
-      <c r="B55" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="42">
-        <f>SUM(K55:O55)</f>
-        <v>5.5756501106184665E-2</v>
-      </c>
-      <c r="D55" s="15">
-        <f>SUM(E55:O55)</f>
-        <v>7.1008998307338034E-2</v>
-      </c>
-      <c r="E55" s="15">
-        <f>E44*(E54-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="15">
-        <f t="shared" ref="F55:O55" si="7">F44*(F54-1)</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="15">
-        <f t="shared" si="7"/>
-        <v>1.6853970556822639E-3</v>
-      </c>
-      <c r="J55" s="15">
-        <f t="shared" si="7"/>
-        <v>1.3567100145471106E-2</v>
-      </c>
-      <c r="K55" s="15">
-        <f t="shared" si="7"/>
-        <v>1.3541162027583832E-2</v>
-      </c>
-      <c r="L55" s="15">
-        <f t="shared" si="7"/>
-        <v>1.5796006680780964E-2</v>
-      </c>
-      <c r="M55" s="15">
-        <f t="shared" si="7"/>
-        <v>1.6866633387219405E-2</v>
-      </c>
-      <c r="N55" s="15">
-        <f t="shared" si="7"/>
-        <v>8.5340480462440024E-3</v>
-      </c>
-      <c r="O55" s="15">
-        <f t="shared" si="7"/>
-        <v>1.0186509643564665E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="71"/>
-      <c r="B56" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" s="42">
-        <f>C55/(1+C55)</f>
-        <v>5.2811894644044302E-2</v>
-      </c>
-      <c r="D56" s="15">
-        <f>D55/(1+D55)</f>
-        <v>6.6301028674421281E-2</v>
-      </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="70"/>
-      <c r="B57" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="43">
-        <f>0.0059261*C56 * 69411087</f>
-        <v>21723.488560717764</v>
-      </c>
-      <c r="D57" s="22">
-        <f>0.0059261*D56 * 69411087</f>
-        <v>27272.06906096173</v>
-      </c>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20">
-        <f>IF(E43&gt;$I$35, EXP((LN(1.08)/10)*(E43-$I$35)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="F58" s="20">
-        <f t="shared" ref="F58:O58" si="8">IF(F43&gt;$I$35, EXP((LN(1.08)/10)*(F43-$I$35)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="G58" s="20">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="H58" s="20">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="I58" s="20">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="J58" s="20">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K58" s="20">
-        <f t="shared" si="8"/>
-        <v>1.0312631565524872</v>
-      </c>
-      <c r="L58" s="20">
-        <f t="shared" si="8"/>
-        <v>1.0717201098736591</v>
-      </c>
-      <c r="M58" s="20">
-        <f t="shared" si="8"/>
-        <v>1.1137642090766864</v>
-      </c>
-      <c r="N58" s="20">
-        <f t="shared" si="8"/>
-        <v>1.157457718663552</v>
-      </c>
-      <c r="O58" s="20">
-        <f t="shared" si="8"/>
-        <v>1.2028653458028213</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="71"/>
-      <c r="B59" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" s="15">
-        <f>SUM(K59:O59)</f>
-        <v>3.8331542536053996E-2</v>
-      </c>
-      <c r="D59" s="42">
-        <f>SUM(E59:O59)</f>
-        <v>3.8331542536053996E-2</v>
-      </c>
-      <c r="E59" s="15">
-        <f>E44*(E58-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="15">
-        <f t="shared" ref="F59:O59" si="9">F44*(F58-1)</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="15">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="15">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="15">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="15">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="15">
-        <f t="shared" si="9"/>
-        <v>5.6555463277831062E-3</v>
-      </c>
-      <c r="L59" s="15">
-        <f t="shared" si="9"/>
-        <v>1.0521564520921027E-2</v>
-      </c>
-      <c r="M59" s="15">
-        <f t="shared" si="9"/>
-        <v>1.3561058273543175E-2</v>
-      </c>
-      <c r="N59" s="15">
-        <f t="shared" si="9"/>
-        <v>7.6198423572209177E-3</v>
-      </c>
-      <c r="O59" s="15">
-        <f t="shared" si="9"/>
-        <v>9.7353105658576995E-4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="71"/>
-      <c r="B60" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" s="15">
-        <f>C59/(1+C59)</f>
-        <v>3.69164770266266E-2</v>
-      </c>
-      <c r="D60" s="42">
-        <f>D59/(1+D59)</f>
-        <v>3.69164770266266E-2</v>
-      </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="70"/>
-      <c r="B61" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="22">
-        <f>0.00127695*C60 * 69411087</f>
-        <v>3272.0730232088936</v>
-      </c>
-      <c r="D61" s="43">
-        <f>0.00127695*D60 * 69411087</f>
-        <v>3272.0730232088936</v>
-      </c>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E62" s="21">
-        <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F62" s="21">
-        <f t="shared" ref="F62:O62" si="10">IF(F43&gt;$I$30,((78.927 - 3.1162 * F43 + 0.0342 * F43^2)/100),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G62" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="21">
-        <f t="shared" si="10"/>
-        <v>8.0134000000000191E-2</v>
-      </c>
-      <c r="J62" s="21">
-        <f t="shared" si="10"/>
-        <v>9.3613999999999892E-2</v>
-      </c>
-      <c r="K62" s="21">
-        <f t="shared" si="10"/>
-        <v>0.1241940000000001</v>
-      </c>
-      <c r="L62" s="21">
-        <f t="shared" si="10"/>
-        <v>0.17187400000000011</v>
-      </c>
-      <c r="M62" s="21">
-        <f t="shared" si="10"/>
-        <v>0.23665399999999978</v>
-      </c>
-      <c r="N62" s="21">
-        <f t="shared" si="10"/>
-        <v>0.31853400000000021</v>
-      </c>
-      <c r="O62" s="21">
-        <f t="shared" si="10"/>
-        <v>0.41751400000000016</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="65"/>
-      <c r="B63" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E63">
-        <f>$E$44*E62</f>
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <f t="shared" ref="F63:O63" si="11">$E$44*F62</f>
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <f t="shared" si="11"/>
-        <v>5.7095417904582238E-5</v>
-      </c>
-      <c r="J63">
-        <f t="shared" si="11"/>
-        <v>6.6699908300091627E-5</v>
-      </c>
-      <c r="K63">
-        <f t="shared" si="11"/>
-        <v>8.8488136511863564E-5</v>
-      </c>
-      <c r="L63">
-        <f t="shared" si="11"/>
-        <v>1.2246010253989754E-4</v>
-      </c>
-      <c r="M63">
-        <f t="shared" si="11"/>
-        <v>1.6861580638419349E-4</v>
-      </c>
-      <c r="N63">
-        <f t="shared" si="11"/>
-        <v>2.2695524804475212E-4</v>
-      </c>
-      <c r="O63">
-        <f t="shared" si="11"/>
-        <v>2.9747842752157261E-4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="65"/>
-      <c r="B64" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C64">
-        <f>SUM(K63:O63)</f>
-        <v>9.0399772100227928E-4</v>
-      </c>
-      <c r="D64">
-        <f>SUM(E63:O63)</f>
-        <v>1.0277930472069531E-3</v>
-      </c>
-      <c r="E64" s="23"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="70"/>
-      <c r="B65" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" s="36">
-        <f>C64*$J$30*69411087</f>
-        <v>690.22210906320026</v>
-      </c>
-      <c r="D65" s="36">
-        <f>D64*$J$30*69411087</f>
-        <v>784.74255879444627</v>
-      </c>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="60"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="60"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-    </row>
-    <row r="68" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="60"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O68" s="15"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="37">
-        <f>SUM(E69:N69)</f>
-        <v>15021000</v>
-      </c>
-      <c r="E69" s="33">
-        <f>C14</f>
-        <v>64582.789500000006</v>
-      </c>
-      <c r="F69" s="33">
-        <f>D14</f>
-        <v>239111.78849999997</v>
-      </c>
-      <c r="G69" s="33">
-        <f>E14</f>
-        <v>1126116.8595</v>
-      </c>
-      <c r="H69" s="33">
-        <f>F14</f>
-        <v>2838600.9855</v>
-      </c>
-      <c r="I69" s="33">
-        <f>G14</f>
-        <v>3242087.577</v>
-      </c>
-      <c r="J69" s="33">
-        <f>Frontend!J15</f>
-        <v>3383500</v>
-      </c>
-      <c r="K69" s="33">
-        <f>Frontend!K15</f>
-        <v>2682400</v>
-      </c>
-      <c r="L69" s="33">
-        <f>Frontend!L15</f>
-        <v>1283500</v>
-      </c>
-      <c r="M69" s="33">
-        <f>Frontend!M15</f>
-        <v>156200</v>
-      </c>
-      <c r="N69" s="33">
-        <f>Frontend!N15</f>
-        <v>4900</v>
-      </c>
-      <c r="O69" s="15"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="71"/>
-      <c r="B70" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15">
-        <v>27</v>
-      </c>
-      <c r="F70" s="15">
-        <v>32</v>
-      </c>
-      <c r="G70" s="15">
-        <v>37</v>
-      </c>
-      <c r="H70" s="15">
-        <v>42</v>
-      </c>
-      <c r="I70" s="15">
-        <v>47</v>
-      </c>
-      <c r="J70" s="15">
-        <v>52</v>
-      </c>
-      <c r="K70" s="15">
-        <v>57</v>
-      </c>
-      <c r="L70" s="15">
-        <v>62</v>
-      </c>
-      <c r="M70" s="15">
-        <v>67</v>
-      </c>
-      <c r="N70" s="16">
-        <v>72</v>
-      </c>
-      <c r="O70" s="15"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="70"/>
-      <c r="B71" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" s="18"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="32">
-        <f>E69/$D$69</f>
-        <v>4.2995000000000004E-3</v>
-      </c>
-      <c r="F71" s="32">
-        <f t="shared" ref="F71:N71" si="12">F69/$D$69</f>
-        <v>1.5918499999999999E-2</v>
-      </c>
-      <c r="G71" s="32">
-        <f t="shared" si="12"/>
-        <v>7.4969499999999994E-2</v>
-      </c>
-      <c r="H71" s="32">
-        <f t="shared" si="12"/>
-        <v>0.18897549999999999</v>
-      </c>
-      <c r="I71" s="32">
-        <f t="shared" si="12"/>
-        <v>0.215837</v>
-      </c>
-      <c r="J71" s="32">
-        <f t="shared" si="12"/>
-        <v>0.2252513148259104</v>
-      </c>
-      <c r="K71" s="32">
-        <f t="shared" si="12"/>
-        <v>0.17857665934358566</v>
-      </c>
-      <c r="L71" s="32">
-        <f t="shared" si="12"/>
-        <v>8.5447040809533317E-2</v>
-      </c>
-      <c r="M71" s="32">
-        <f t="shared" si="12"/>
-        <v>1.0398775048265762E-2</v>
-      </c>
-      <c r="N71" s="32">
-        <f t="shared" si="12"/>
-        <v>3.2620997270487985E-4</v>
-      </c>
-      <c r="O71" s="15"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="B72" s="40"/>
-      <c r="C72" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
-      <c r="L72" s="41"/>
-      <c r="M72" s="41"/>
-      <c r="N72" s="41"/>
-      <c r="O72" s="15"/>
-    </row>
-    <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="66" t="s">
-        <v>53</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E73" s="34">
-        <f>IF(E70&gt;$I$31,((19.4312 - 0.9336 *  E70 + 0.0126 *  E70^2)/100),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="34">
-        <f t="shared" ref="F73:N73" si="13">IF(F70&gt;$I$31,((19.4312 - 0.9336 *  F70 + 0.0126 *  F70^2)/100),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="34">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="34">
-        <f t="shared" si="13"/>
-        <v>2.4464000000000041E-2</v>
-      </c>
-      <c r="I73" s="34">
-        <f t="shared" si="13"/>
-        <v>3.3854000000000044E-2</v>
-      </c>
-      <c r="J73" s="34">
-        <f t="shared" si="13"/>
-        <v>4.9544000000000032E-2</v>
-      </c>
-      <c r="K73" s="34">
-        <f t="shared" si="13"/>
-        <v>7.1534000000000125E-2</v>
-      </c>
-      <c r="L73" s="34">
-        <f t="shared" si="13"/>
-        <v>9.9824000000000052E-2</v>
-      </c>
-      <c r="M73" s="34">
-        <f t="shared" si="13"/>
-        <v>0.13441399999999995</v>
-      </c>
-      <c r="N73" s="34">
-        <f t="shared" si="13"/>
-        <v>0.17530400000000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
-      <c r="B74" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E74" s="34">
-        <f>E73*E71</f>
-        <v>0</v>
-      </c>
-      <c r="F74" s="34">
-        <f t="shared" ref="F74:N74" si="14">F73*F71</f>
-        <v>0</v>
-      </c>
-      <c r="G74" s="34">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="34">
-        <f t="shared" si="14"/>
-        <v>4.6230966320000072E-3</v>
-      </c>
-      <c r="I74" s="34">
-        <f t="shared" si="14"/>
-        <v>7.3069457980000094E-3</v>
-      </c>
-      <c r="J74" s="34">
-        <f t="shared" si="14"/>
-        <v>1.1159851141734912E-2</v>
-      </c>
-      <c r="K74" s="34">
-        <f t="shared" si="14"/>
-        <v>1.2774302749484078E-2</v>
-      </c>
-      <c r="L74" s="34">
-        <f t="shared" si="14"/>
-        <v>8.5296654017708584E-3</v>
-      </c>
-      <c r="M74" s="34">
-        <f t="shared" si="14"/>
-        <v>1.3977409493375935E-3</v>
-      </c>
-      <c r="N74" s="34">
-        <f t="shared" si="14"/>
-        <v>5.718591305505626E-5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
-      <c r="B75" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C75" s="34">
-        <f>SUM(J74:N74)</f>
-        <v>3.3918746155382498E-2</v>
-      </c>
-      <c r="D75" s="34">
-        <f>SUM(E74:N74)</f>
-        <v>4.5848788585382522E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="67"/>
-      <c r="B76" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76" s="36">
-        <f>C75*J31*69411087</f>
-        <v>23543.370403221699</v>
-      </c>
-      <c r="D76" s="36">
-        <f>D75*J31*69411087</f>
-        <v>31824.142533445931</v>
-      </c>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
-      <c r="L76" s="35"/>
-      <c r="M76" s="35"/>
-      <c r="N76" s="35"/>
-      <c r="O76" s="24"/>
-    </row>
-    <row r="79" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="58" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C80" t="s">
-        <v>101</v>
-      </c>
-      <c r="D80" t="s">
-        <v>102</v>
-      </c>
-      <c r="E80" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B81" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C81" s="48">
-        <f>C61+C65+C76</f>
-        <v>27505.665535493794</v>
-      </c>
-      <c r="D81" s="48">
-        <f>D49+D53+D57+D65+D76</f>
-        <v>937395.99801702728</v>
-      </c>
-      <c r="E81" s="45">
-        <f>D81-C81</f>
-        <v>909890.33248153352</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B82" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="C82" s="49">
-        <f>C81*70000</f>
-        <v>1925396587.4845655</v>
-      </c>
-      <c r="D82" s="49">
-        <f>D81*70000</f>
-        <v>65617719861.19191</v>
-      </c>
-      <c r="E82" s="46">
-        <f>D82-C82</f>
-        <v>63692323273.707344</v>
-      </c>
-      <c r="F82" t="s">
-        <v>139</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="J40:N40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="D40:I40"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5836,68 +3885,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="47">
+        <v>1</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="47">
+        <v>2</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="47">
+        <v>3</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>4</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="50">
+        <v>5</v>
+      </c>
+      <c r="B6" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="B1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="50">
-        <v>1</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="50">
-        <v>2</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="50">
-        <v>3</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="50">
-        <v>4</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="55">
-        <v>5</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>144</v>
-      </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -5905,7 +3954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5915,7 +3964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5938,7 +3987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3BA502-77FB-4AA9-A654-F467290EB112}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G13"/>
@@ -6127,7 +4176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1"/>
@@ -6137,7 +4186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B738CEAF-BA8D-46A4-B41F-A105DC1BD636}">
   <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1"/>
@@ -6145,4 +4194,14 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
+  <sheetPr codeName="Tabelle5"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9429B309-3E10-4FDE-97A6-BA5C75FFA764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189560E9-9AF9-4119-A3F6-E6C3572EA995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Frontend" sheetId="8" r:id="rId1"/>
-    <sheet name="Agglomeration road" sheetId="1" r:id="rId2"/>
-    <sheet name="Fragen" sheetId="11" r:id="rId3"/>
-    <sheet name="ERF HRA" sheetId="10" r:id="rId4"/>
-    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId5"/>
-    <sheet name="Agglomeration rail" sheetId="2" r:id="rId6"/>
-    <sheet name="Agglomeration air" sheetId="3" r:id="rId7"/>
-    <sheet name="Agglomeration industry" sheetId="4" r:id="rId8"/>
-    <sheet name="Major roads " sheetId="5" r:id="rId9"/>
-    <sheet name="Major railways " sheetId="6" r:id="rId10"/>
-    <sheet name="Major airports" sheetId="7" r:id="rId11"/>
+    <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
+    <sheet name="Frontend" sheetId="8" r:id="rId2"/>
+    <sheet name="Agglomeration road" sheetId="1" r:id="rId3"/>
+    <sheet name="Fragen" sheetId="11" r:id="rId4"/>
+    <sheet name="ERF HRA" sheetId="10" r:id="rId5"/>
+    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId6"/>
+    <sheet name="Agglomeration rail" sheetId="2" r:id="rId7"/>
+    <sheet name="Agglomeration air" sheetId="3" r:id="rId8"/>
+    <sheet name="Agglomeration industry" sheetId="4" r:id="rId9"/>
+    <sheet name="Major roads " sheetId="5" r:id="rId10"/>
+    <sheet name="Major railways " sheetId="6" r:id="rId11"/>
+    <sheet name="Major airports" sheetId="7" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="150">
   <si>
     <t>L_den</t>
   </si>
@@ -556,6 +557,9 @@
   </si>
   <si>
     <t>in Annex 4: "All estimates are per person and per year" -&gt; also  Multiplikation mit Exponierten der Kategorie (zB Ballungsraum Straßen) notwendig</t>
+  </si>
+  <si>
+    <t>DALY pro 100.000</t>
   </si>
 </sst>
 </file>
@@ -754,7 +758,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -840,6 +844,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -848,12 +867,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -868,20 +881,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1353,6 +1363,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11457340-40AB-4C39-9488-F3F169CC7A0E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
+  <sheetPr codeName="Tabelle5"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
+  <sheetPr codeName="Tabelle6"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
+  <sheetPr codeName="Tabelle7"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
   <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1380,15 +1429,15 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
     </row>
     <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1397,29 +1446,29 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="52"/>
+      <c r="B10" s="61"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="J12" s="53" t="s">
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="J12" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
     </row>
     <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
@@ -1460,7 +1509,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="63" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
@@ -1507,7 +1556,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="54"/>
+      <c r="A15" s="63"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1582,7 +1631,7 @@
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -1629,7 +1678,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
+      <c r="A19" s="63"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1704,7 +1753,7 @@
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="63" t="s">
         <v>81</v>
       </c>
       <c r="B22" t="s">
@@ -1751,7 +1800,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
+      <c r="A23" s="63"/>
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1802,10 +1851,10 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="52"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -1858,11 +1907,11 @@
       <c r="B39" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="66">
+      <c r="C39" s="56">
         <f>'Agglomeration road'!C82</f>
         <v>439746126.72747183</v>
       </c>
-      <c r="D39" s="66">
+      <c r="D39" s="56">
         <f>'Agglomeration road'!D82</f>
         <v>19474523816.498829</v>
       </c>
@@ -1883,30 +1932,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
-  <sheetPr codeName="Tabelle6"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
-  <sheetPr codeName="Tabelle7"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -2416,21 +2445,21 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="57" t="s">
+      <c r="D40" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57" t="s">
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
-      <c r="N40" s="57"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="64"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
@@ -2471,10 +2500,10 @@
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="58" t="s">
+      <c r="A42" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B42" s="64" t="s">
+      <c r="B42" s="54" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="20"/>
@@ -2533,7 +2562,7 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="60"/>
+      <c r="A43" s="67"/>
       <c r="B43" s="15" t="s">
         <v>108</v>
       </c>
@@ -2574,7 +2603,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
+      <c r="A44" s="66"/>
       <c r="B44" s="24" t="s">
         <v>109</v>
       </c>
@@ -2637,7 +2666,7 @@
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="58" t="s">
+      <c r="A46" s="65" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="19" t="s">
@@ -2691,7 +2720,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="60"/>
+      <c r="A47" s="67"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
@@ -2749,7 +2778,7 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="60"/>
+      <c r="A48" s="67"/>
       <c r="B48" s="15" t="s">
         <v>111</v>
       </c>
@@ -2774,8 +2803,8 @@
       <c r="O48" s="15"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="59"/>
-      <c r="B49" s="63" t="s">
+      <c r="A49" s="66"/>
+      <c r="B49" s="53" t="s">
         <v>135</v>
       </c>
       <c r="C49" s="43">
@@ -2799,7 +2828,7 @@
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="58" t="s">
+      <c r="A50" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="19" t="s">
@@ -2853,7 +2882,7 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="60"/>
+      <c r="A51" s="67"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
@@ -2911,7 +2940,7 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="60"/>
+      <c r="A52" s="67"/>
       <c r="B52" s="15" t="s">
         <v>111</v>
       </c>
@@ -2936,8 +2965,8 @@
       <c r="O52" s="15"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="59"/>
-      <c r="B53" s="63" t="s">
+      <c r="A53" s="66"/>
+      <c r="B53" s="53" t="s">
         <v>136</v>
       </c>
       <c r="C53" s="43">
@@ -2961,7 +2990,7 @@
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="58" t="s">
+      <c r="A54" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="19" t="s">
@@ -3015,7 +3044,7 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="60"/>
+      <c r="A55" s="67"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
@@ -3073,7 +3102,7 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="60"/>
+      <c r="A56" s="67"/>
       <c r="B56" s="15" t="s">
         <v>111</v>
       </c>
@@ -3098,8 +3127,8 @@
       <c r="O56" s="15"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="59"/>
-      <c r="B57" s="63" t="s">
+      <c r="A57" s="66"/>
+      <c r="B57" s="53" t="s">
         <v>137</v>
       </c>
       <c r="C57" s="43">
@@ -3123,7 +3152,7 @@
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="58" t="s">
+      <c r="A58" s="65" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="19" t="s">
@@ -3177,7 +3206,7 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="60"/>
+      <c r="A59" s="67"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
@@ -3235,7 +3264,7 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="60"/>
+      <c r="A60" s="67"/>
       <c r="B60" s="15" t="s">
         <v>111</v>
       </c>
@@ -3260,8 +3289,8 @@
       <c r="O60" s="15"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="59"/>
-      <c r="B61" s="63" t="s">
+      <c r="A61" s="66"/>
+      <c r="B61" s="53" t="s">
         <v>138</v>
       </c>
       <c r="C61" s="22">
@@ -3285,7 +3314,7 @@
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="58" t="s">
+      <c r="A62" s="68" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="34" t="s">
@@ -3337,7 +3366,7 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
+      <c r="A63" s="69"/>
       <c r="B63" s="34" t="s">
         <v>112</v>
       </c>
@@ -3387,7 +3416,7 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
+      <c r="A64" s="69"/>
       <c r="B64" s="15" t="s">
         <v>111</v>
       </c>
@@ -3402,8 +3431,8 @@
       <c r="E64" s="23"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="59"/>
-      <c r="B65" s="65" t="s">
+      <c r="A65" s="70"/>
+      <c r="B65" s="55" t="s">
         <v>139</v>
       </c>
       <c r="C65" s="36">
@@ -3503,7 +3532,7 @@
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="58" t="s">
+      <c r="A69" s="65" t="s">
         <v>102</v>
       </c>
       <c r="B69" s="20" t="s">
@@ -3557,7 +3586,7 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="60"/>
+      <c r="A70" s="67"/>
       <c r="B70" s="15" t="s">
         <v>108</v>
       </c>
@@ -3596,7 +3625,7 @@
       <c r="O70" s="15"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="59"/>
+      <c r="A71" s="66"/>
       <c r="B71" s="24" t="s">
         <v>109</v>
       </c>
@@ -3668,7 +3697,7 @@
       <c r="O72" s="15"/>
     </row>
     <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="55" t="s">
+      <c r="A73" s="71" t="s">
         <v>53</v>
       </c>
       <c r="B73" s="34" t="s">
@@ -3716,7 +3745,7 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="55"/>
+      <c r="A74" s="71"/>
       <c r="B74" s="34" t="s">
         <v>112</v>
       </c>
@@ -3762,7 +3791,7 @@
       </c>
     </row>
     <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="55"/>
+      <c r="A75" s="71"/>
       <c r="B75" s="15" t="s">
         <v>111</v>
       </c>
@@ -3776,8 +3805,8 @@
       </c>
     </row>
     <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="56"/>
-      <c r="B76" s="65" t="s">
+      <c r="A76" s="70"/>
+      <c r="B76" s="55" t="s">
         <v>139</v>
       </c>
       <c r="C76" s="36">
@@ -3823,11 +3852,11 @@
       <c r="B81" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="C81" s="61">
+      <c r="C81" s="51">
         <f>C61+C65+C76</f>
         <v>6282.0875246781688</v>
       </c>
-      <c r="D81" s="61">
+      <c r="D81" s="51">
         <f>D49+D53+D57+D65+D76</f>
         <v>278207.48309284041</v>
       </c>
@@ -3840,11 +3869,11 @@
       <c r="B82" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C82" s="62">
+      <c r="C82" s="52">
         <f>C81*70000</f>
         <v>439746126.72747183</v>
       </c>
-      <c r="D82" s="62">
+      <c r="D82" s="52">
         <f>D81*70000</f>
         <v>19474523816.498829</v>
       </c>
@@ -3854,6 +3883,11 @@
       </c>
       <c r="F82" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3874,7 +3908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3898,7 +3932,7 @@
       <c r="A2" s="47">
         <v>1</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="57" t="s">
         <v>109</v>
       </c>
       <c r="C2" s="49" t="s">
@@ -3909,7 +3943,7 @@
       <c r="A3" s="47">
         <v>2</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="58" t="s">
         <v>107</v>
       </c>
       <c r="C3" s="48" t="s">
@@ -3920,7 +3954,7 @@
       <c r="A4" s="47">
         <v>3</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="59" t="s">
         <v>145</v>
       </c>
       <c r="C4" s="48" t="s">
@@ -3931,7 +3965,7 @@
       <c r="A5" s="47">
         <v>4</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="58" t="s">
         <v>133</v>
       </c>
       <c r="C5" t="s">
@@ -3942,7 +3976,7 @@
       <c r="A6" s="50">
         <v>5</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="58" t="s">
         <v>134</v>
       </c>
       <c r="C6" t="s">
@@ -3954,7 +3988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3964,7 +3998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3987,7 +4021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3BA502-77FB-4AA9-A654-F467290EB112}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G13"/>
@@ -4176,7 +4210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1"/>
@@ -4186,7 +4220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B738CEAF-BA8D-46A4-B41F-A105DC1BD636}">
   <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1"/>
@@ -4194,14 +4228,4 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
-  <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189560E9-9AF9-4119-A3F6-E6C3572EA995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A1B052-1B98-4ECA-BD22-E37BF79E7598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="153">
   <si>
     <t>L_den</t>
   </si>
@@ -428,9 +428,6 @@
     <t>AFtot = Total attributable fraction from noise exposure</t>
   </si>
   <si>
-    <t>p[i]*ERF[Ni]</t>
-  </si>
-  <si>
     <t>Exposed 
 35 - 39 dB</t>
   </si>
@@ -513,9 +510,6 @@
     <t>YYL/ YLD für  mortality, CVD, Diabetes, IHD nach 2019 GBD</t>
   </si>
   <si>
-    <t>YLL = YLLnat (= 0,2069215) ∙ AFtot * Summe der Exponierten</t>
-  </si>
-  <si>
     <t>YLD = YLD of the disease (= 0,0115708) * AFtot * Summe der Exponierten</t>
   </si>
   <si>
@@ -523,9 +517,6 @@
   </si>
   <si>
     <t>YLD = YLD of the disease (= 0,001276950) * AFtot * Summe der Exponierten</t>
-  </si>
-  <si>
-    <t>YLD = DW * AFtot * Summe der Exponierten</t>
   </si>
   <si>
     <t>ETC HE model</t>
@@ -559,7 +550,71 @@
     <t>in Annex 4: "All estimates are per person and per year" -&gt; also  Multiplikation mit Exponierten der Kategorie (zB Ballungsraum Straßen) notwendig</t>
   </si>
   <si>
-    <t>DALY pro 100.000</t>
+    <t>Sum exposed</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">YLL = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YLLnat (= 0,2069215)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ∙ AFtot * Summe der Exponierten</t>
+    </r>
+  </si>
+  <si>
+    <t>Sum p[i]*ERF[Ni]</t>
+  </si>
+  <si>
+    <t>YLD = DW * Sum p[i]*ERF[Ni] * Summe der Exponierten Lden</t>
+  </si>
+  <si>
+    <t>YLD = DW * Sum p[i]*ERF[Ni] * Summe der Exponierten Lnight</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DALY pro 100.000 (DALY * </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Exponierte Lden </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>* 100k)</t>
+    </r>
+  </si>
+  <si>
+    <t>EURO pro 100.000 (EURO * Exponierte Lden * 100k)</t>
   </si>
 </sst>
 </file>
@@ -572,7 +627,7 @@
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,16 +731,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -749,6 +836,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -758,7 +889,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -781,16 +912,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -805,15 +931,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -822,11 +941,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -869,28 +983,117 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1429,15 +1632,15 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1446,70 +1649,70 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="61" t="s">
+      <c r="A10" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="61"/>
+      <c r="B10" s="50"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="J12" s="62" t="s">
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="J12" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="62"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
     </row>
     <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H13" t="s">
         <v>76</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="O13" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
@@ -1556,7 +1759,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="63"/>
+      <c r="A15" s="52"/>
       <c r="B15" t="s">
         <v>84</v>
       </c>
@@ -1631,7 +1834,7 @@
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="52" t="s">
         <v>78</v>
       </c>
       <c r="B18" t="s">
@@ -1678,7 +1881,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="63"/>
+      <c r="A19" s="52"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1753,7 +1956,7 @@
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="52" t="s">
         <v>81</v>
       </c>
       <c r="B22" t="s">
@@ -1800,7 +2003,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="63"/>
+      <c r="A23" s="52"/>
       <c r="B23" t="s">
         <v>83</v>
       </c>
@@ -1851,10 +2054,10 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="61"/>
+      <c r="A32" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="50"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -1887,33 +2090,33 @@
         <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="44" t="s">
+      <c r="B38" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="45">
-        <f>'Agglomeration road'!C81</f>
-        <v>6282.0875246781688</v>
-      </c>
-      <c r="D38" s="45">
-        <f>'Agglomeration road'!D81</f>
-        <v>278207.48309284041</v>
+      <c r="C38" s="34">
+        <f>'Agglomeration road'!C79</f>
+        <v>27420.859000423719</v>
+      </c>
+      <c r="D38" s="34">
+        <f>'Agglomeration road'!D79</f>
+        <v>308626.30242553435</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="44" t="s">
+      <c r="B39" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="56">
-        <f>'Agglomeration road'!C82</f>
-        <v>439746126.72747183</v>
-      </c>
-      <c r="D39" s="56">
-        <f>'Agglomeration road'!D82</f>
-        <v>19474523816.498829</v>
+      <c r="C39" s="45">
+        <f>'Agglomeration road'!C80</f>
+        <v>1919460130.0296605</v>
+      </c>
+      <c r="D39" s="45">
+        <f>'Agglomeration road'!D80</f>
+        <v>21603841169.787403</v>
       </c>
     </row>
   </sheetData>
@@ -1935,7 +2138,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:U84"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -2052,22 +2255,22 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>75</v>
@@ -2243,7 +2446,7 @@
       <c r="H30" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="27">
         <v>45</v>
       </c>
       <c r="J30">
@@ -2281,7 +2484,7 @@
       <c r="H31" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="27">
         <v>40</v>
       </c>
       <c r="J31">
@@ -2319,7 +2522,7 @@
       <c r="H32" t="s">
         <v>51</v>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="27">
         <v>45</v>
       </c>
       <c r="K32">
@@ -2445,113 +2648,113 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="D40" s="64" t="s">
+      <c r="E40" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64" t="s">
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K40" s="64"/>
-      <c r="L40" s="64"/>
-      <c r="M40" s="64"/>
-      <c r="N40" s="64"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="H41" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="O41" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="37">
+      <c r="C42" s="18"/>
+      <c r="D42" s="29">
         <f>SUM(E42:O42)</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="75">
         <f t="shared" ref="E42:J42" si="0">C13</f>
         <v>14817.435000000001</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="75">
         <f t="shared" si="0"/>
         <v>43360.493999999999</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="75">
         <f t="shared" si="0"/>
         <v>175282.45740000001</v>
       </c>
-      <c r="H42" s="21">
+      <c r="H42" s="75">
         <f t="shared" si="0"/>
         <v>708356.57860000001</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="75">
         <f t="shared" si="0"/>
         <v>2895888.3018</v>
       </c>
-      <c r="J42" s="21">
+      <c r="J42" s="75">
         <f t="shared" si="0"/>
         <v>6560515.5296</v>
       </c>
-      <c r="K42" s="21">
+      <c r="K42" s="60">
         <f>Frontend!C15</f>
         <v>3762100</v>
       </c>
-      <c r="L42" s="21">
+      <c r="L42" s="61">
         <f>Frontend!D15</f>
         <v>3050900</v>
       </c>
-      <c r="M42" s="21">
+      <c r="M42" s="61">
         <f>Frontend!E15</f>
         <v>2479000</v>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="61">
         <f>Frontend!F15</f>
         <v>1006400</v>
       </c>
-      <c r="O42" s="21">
+      <c r="O42" s="61">
         <f>Frontend!G15</f>
         <v>99800</v>
       </c>
@@ -2562,1346 +2765,1372 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="67"/>
+      <c r="A43" s="54"/>
       <c r="B43" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="15">
+      <c r="E43" s="76">
         <v>27</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="76">
         <v>32</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="76">
         <v>37</v>
       </c>
-      <c r="H43" s="15">
+      <c r="H43" s="76">
         <v>42</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="76">
         <v>47</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="76">
         <v>52</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="62">
         <v>57</v>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="63">
         <v>62</v>
       </c>
-      <c r="M43" s="15">
+      <c r="M43" s="63">
         <v>67</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="63">
         <v>72</v>
       </c>
-      <c r="O43" s="16">
+      <c r="O43" s="64">
         <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="66"/>
-      <c r="B44" s="24" t="s">
+      <c r="A44" s="55"/>
+      <c r="B44" s="19" t="s">
         <v>109</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="15">
+      <c r="E44" s="76">
         <f t="shared" ref="E44:O44" si="1">E42/$D$42</f>
         <v>7.1249928750071259E-4</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="76">
         <f t="shared" si="1"/>
         <v>2.0849979150020848E-3</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="76">
         <f t="shared" si="1"/>
         <v>8.4284915715084289E-3</v>
       </c>
-      <c r="H44" s="15">
+      <c r="H44" s="76">
         <f t="shared" si="1"/>
         <v>3.4061465938534062E-2</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="76">
         <f t="shared" si="1"/>
         <v>0.13924936075063926</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="76">
         <f t="shared" si="1"/>
         <v>0.31546368453631546</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="62">
         <f t="shared" si="1"/>
         <v>0.18090132128174888</v>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="63">
         <f t="shared" si="1"/>
         <v>0.14670312886379619</v>
       </c>
-      <c r="M44" s="15">
+      <c r="M44" s="63">
         <f t="shared" si="1"/>
         <v>0.11920320444896612</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="63">
         <f t="shared" si="1"/>
         <v>4.8392942701669828E-2</v>
       </c>
-      <c r="O44" s="15">
+      <c r="O44" s="63">
         <f t="shared" si="1"/>
         <v>4.7989027043190075E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27" t="s">
+    <row r="45" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>101</v>
-      </c>
+      <c r="D45" s="92" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="77"/>
+      <c r="F45" s="77"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="77"/>
+      <c r="I45" s="77"/>
+      <c r="J45" s="77"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="66"/>
+      <c r="M45" s="66"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20">
+      <c r="C46" s="101"/>
+      <c r="D46" s="92"/>
+      <c r="E46" s="77">
         <f>IF(E43&gt;$I$32, EXP((LN(1.055)/10)*(E43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="77">
         <f t="shared" ref="F46:O46" si="2">IF(F43&gt;$I$32, EXP((LN(1.055)/10)*(F43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="77">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H46" s="20">
+      <c r="H46" s="77">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I46" s="20">
+      <c r="I46" s="77">
         <f t="shared" si="2"/>
         <v>1.0107656908500073</v>
       </c>
-      <c r="J46" s="20">
+      <c r="J46" s="77">
         <f t="shared" si="2"/>
         <v>1.0381897140207395</v>
       </c>
-      <c r="K46" s="20">
+      <c r="K46" s="65">
         <f t="shared" si="2"/>
         <v>1.0663578038467578</v>
       </c>
-      <c r="L46" s="20">
+      <c r="L46" s="66">
         <f t="shared" si="2"/>
         <v>1.09529014829188</v>
       </c>
-      <c r="M46" s="20">
+      <c r="M46" s="66">
         <f t="shared" si="2"/>
         <v>1.1250074830583294</v>
       </c>
-      <c r="N46" s="20">
+      <c r="N46" s="66">
         <f t="shared" si="2"/>
         <v>1.1555311064479334</v>
       </c>
-      <c r="O46" s="20">
+      <c r="O46" s="66">
         <f t="shared" si="2"/>
         <v>1.1868828946265373</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="67"/>
+      <c r="A47" s="54"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="42">
+      <c r="C47" s="102">
         <f>SUM(K47:O47)</f>
         <v>4.9308310609276644E-2</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="93">
         <f>SUM(E47:O47)</f>
         <v>6.2854894074549819E-2</v>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="78">
         <f>E44*(E46-1)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="78">
         <f t="shared" ref="F47:O47" si="3">F44*(F46-1)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="24">
+      <c r="G47" s="78">
         <f>G44*(G46-1)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="24">
+      <c r="H47" s="78">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I47" s="24">
+      <c r="I47" s="78">
         <f t="shared" si="3"/>
         <v>1.4991155689025278E-3</v>
       </c>
-      <c r="J47" s="24">
+      <c r="J47" s="78">
         <f t="shared" si="3"/>
         <v>1.2047467896370654E-2</v>
       </c>
-      <c r="K47" s="24">
+      <c r="K47" s="67">
         <f t="shared" si="3"/>
         <v>1.2004214393233608E-2</v>
       </c>
-      <c r="L47" s="24">
+      <c r="L47" s="68">
         <f t="shared" si="3"/>
         <v>1.3979362904313918E-2</v>
       </c>
-      <c r="M47" s="24">
+      <c r="M47" s="68">
         <f t="shared" si="3"/>
         <v>1.4901292560652712E-2</v>
       </c>
-      <c r="N47" s="24">
+      <c r="N47" s="68">
         <f t="shared" si="3"/>
         <v>7.5266079226621535E-3</v>
       </c>
-      <c r="O47" s="24">
+      <c r="O47" s="68">
         <f t="shared" si="3"/>
         <v>8.9683282841425394E-4</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="67"/>
+      <c r="A48" s="54"/>
       <c r="B48" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="42">
+      <c r="C48" s="102">
         <f>(C47)/(1+C47)</f>
         <v>4.6991251389828383E-2</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="94">
         <f>(D47)/(1+D47)</f>
         <v>5.9137794279320602E-2</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="62"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="63"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="66"/>
-      <c r="B49" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="C49" s="43">
+      <c r="A49" s="55"/>
+      <c r="B49" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" s="113">
         <f>0.2069215*C48*D42</f>
         <v>202214.00228176778</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="112">
         <f>0.2069215*D48*D42</f>
         <v>254483.32856966133</v>
       </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
+      <c r="E49" s="79"/>
+      <c r="F49" s="79"/>
+      <c r="G49" s="79"/>
+      <c r="H49" s="79"/>
+      <c r="I49" s="79"/>
+      <c r="J49" s="79"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="70"/>
+      <c r="M49" s="70"/>
+      <c r="N49" s="70"/>
+      <c r="O49" s="70"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20">
+      <c r="C50" s="101"/>
+      <c r="D50" s="92"/>
+      <c r="E50" s="77">
         <f>IF(E43&gt;$I$33, EXP((LN(1.032)/10)*(E43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="77">
         <f t="shared" ref="F50:O50" si="4">IF(F43&gt;$I$33, EXP((LN(1.032)/10)*(F43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="77">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H50" s="20">
+      <c r="H50" s="77">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I50" s="20">
+      <c r="I50" s="77">
         <f t="shared" si="4"/>
         <v>1.0063196184673233</v>
       </c>
-      <c r="J50" s="20">
+      <c r="J50" s="77">
         <f t="shared" si="4"/>
         <v>1.0222939440770498</v>
       </c>
-      <c r="K50" s="20">
+      <c r="K50" s="65">
         <f t="shared" si="4"/>
         <v>1.0385218462582777</v>
       </c>
-      <c r="L50" s="20">
+      <c r="L50" s="66">
         <f t="shared" si="4"/>
         <v>1.0550073502875155</v>
       </c>
-      <c r="M50" s="20">
+      <c r="M50" s="66">
         <f t="shared" si="4"/>
         <v>1.0717545453385426</v>
       </c>
-      <c r="N50" s="20">
+      <c r="N50" s="66">
         <f t="shared" si="4"/>
         <v>1.088767585496716</v>
       </c>
-      <c r="O50" s="20">
+      <c r="O50" s="66">
         <f t="shared" si="4"/>
         <v>1.1060506907893759</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="67"/>
+      <c r="A51" s="54"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C51" s="42">
+      <c r="C51" s="102">
         <f>SUM(K51:O51)</f>
         <v>2.8396426647685286E-2</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="93">
         <f>SUM(E51:O51)</f>
         <v>3.6309359220840685E-2</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="76">
         <f>E44*(E50-1)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="76">
         <f t="shared" ref="F51:O51" si="5">F44*(F50-1)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="76">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H51" s="15">
+      <c r="H51" s="76">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I51" s="15">
+      <c r="I51" s="76">
         <f t="shared" si="5"/>
         <v>8.8000283176270673E-4</v>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="76">
         <f t="shared" si="5"/>
         <v>7.0329297413926854E-3</v>
       </c>
-      <c r="K51" s="15">
+      <c r="K51" s="62">
         <f t="shared" si="5"/>
         <v>6.9686528863348307E-3</v>
       </c>
-      <c r="L51" s="15">
+      <c r="L51" s="63">
         <f t="shared" si="5"/>
         <v>8.0697503976853574E-3</v>
       </c>
-      <c r="M51" s="15">
+      <c r="M51" s="63">
         <f t="shared" si="5"/>
         <v>8.5533717381329078E-3</v>
       </c>
-      <c r="N51" s="15">
+      <c r="N51" s="63">
         <f t="shared" si="5"/>
         <v>4.2957246787081573E-3</v>
       </c>
-      <c r="O51" s="15">
+      <c r="O51" s="63">
         <f t="shared" si="5"/>
         <v>5.0892694682403491E-4</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="67"/>
+      <c r="A52" s="54"/>
       <c r="B52" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="42">
+      <c r="C52" s="102">
         <f>C51/(1+C51)</f>
         <v>2.7612335002223338E-2</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="93">
         <f>D51/(1+D51)</f>
         <v>3.503718160775874E-2</v>
       </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="76"/>
+      <c r="H52" s="76"/>
+      <c r="I52" s="76"/>
+      <c r="J52" s="76"/>
+      <c r="K52" s="62"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="63"/>
+      <c r="N52" s="63"/>
+      <c r="O52" s="63"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
-      <c r="B53" s="53" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="43">
+      <c r="A53" s="55"/>
+      <c r="B53" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" s="110">
         <f>0.0115708*C52*D42</f>
         <v>6644.3900174318323</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="111">
         <f>0.0115708*D52*D42</f>
         <v>8431.0399571348571</v>
       </c>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
+      <c r="E53" s="79"/>
+      <c r="F53" s="79"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="79"/>
+      <c r="I53" s="79"/>
+      <c r="J53" s="79"/>
+      <c r="K53" s="69"/>
+      <c r="L53" s="70"/>
+      <c r="M53" s="70"/>
+      <c r="N53" s="70"/>
+      <c r="O53" s="70"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="65" t="s">
+      <c r="A54" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20">
+      <c r="C54" s="101"/>
+      <c r="D54" s="92"/>
+      <c r="E54" s="77">
         <f>IF(E43&gt;$I$34, EXP((LN(1.062)/10)*(E43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="77">
         <f t="shared" ref="F54:O54" si="6">IF(F43&gt;$I$34, EXP((LN(1.062)/10)*(F43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="G54" s="20">
+      <c r="G54" s="77">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="H54" s="20">
+      <c r="H54" s="77">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="I54" s="20">
+      <c r="I54" s="77">
         <f t="shared" si="6"/>
         <v>1.0121034455497457</v>
       </c>
-      <c r="J54" s="20">
+      <c r="J54" s="77">
         <f t="shared" si="6"/>
         <v>1.043006852485771</v>
       </c>
-      <c r="K54" s="20">
+      <c r="K54" s="65">
         <f t="shared" si="6"/>
         <v>1.0748538591738301</v>
       </c>
-      <c r="L54" s="20">
+      <c r="L54" s="66">
         <f t="shared" si="6"/>
         <v>1.1076732773398887</v>
       </c>
-      <c r="M54" s="20">
+      <c r="M54" s="66">
         <f t="shared" si="6"/>
         <v>1.1414947984426076</v>
       </c>
-      <c r="N54" s="20">
+      <c r="N54" s="66">
         <f t="shared" si="6"/>
         <v>1.1763490205349618</v>
       </c>
-      <c r="O54" s="20">
+      <c r="O54" s="66">
         <f t="shared" si="6"/>
         <v>1.2122674759460494</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="67"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="42">
+      <c r="C55" s="102">
         <f>SUM(K55:O55)</f>
         <v>5.5756501106184665E-2</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="93">
         <f>SUM(E55:O55)</f>
         <v>7.1008998307338034E-2</v>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="76">
         <f>E44*(E54-1)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="76">
         <f t="shared" ref="F55:O55" si="7">F44*(F54-1)</f>
         <v>0</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="76">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H55" s="15">
+      <c r="H55" s="76">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I55" s="15">
+      <c r="I55" s="76">
         <f t="shared" si="7"/>
         <v>1.6853970556822639E-3</v>
       </c>
-      <c r="J55" s="15">
+      <c r="J55" s="76">
         <f t="shared" si="7"/>
         <v>1.3567100145471106E-2</v>
       </c>
-      <c r="K55" s="15">
+      <c r="K55" s="62">
         <f t="shared" si="7"/>
         <v>1.3541162027583832E-2</v>
       </c>
-      <c r="L55" s="15">
+      <c r="L55" s="63">
         <f t="shared" si="7"/>
         <v>1.5796006680780964E-2</v>
       </c>
-      <c r="M55" s="15">
+      <c r="M55" s="63">
         <f t="shared" si="7"/>
         <v>1.6866633387219405E-2</v>
       </c>
-      <c r="N55" s="15">
+      <c r="N55" s="63">
         <f t="shared" si="7"/>
         <v>8.5340480462440024E-3</v>
       </c>
-      <c r="O55" s="15">
+      <c r="O55" s="63">
         <f t="shared" si="7"/>
         <v>1.0186509643564665E-3</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="67"/>
+      <c r="A56" s="54"/>
       <c r="B56" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="42">
+      <c r="C56" s="102">
         <f>C55/(1+C55)</f>
         <v>5.2811894644044302E-2</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="93">
         <f>D55/(1+D55)</f>
         <v>6.6301028674421281E-2</v>
       </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
+      <c r="E56" s="76"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76"/>
+      <c r="J56" s="76"/>
+      <c r="K56" s="62"/>
+      <c r="L56" s="63"/>
+      <c r="M56" s="63"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="63"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="66"/>
-      <c r="B57" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" s="43">
+      <c r="A57" s="55"/>
+      <c r="B57" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="110">
         <f>0.0059261*C56*D42</f>
         <v>6508.6260538531606</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="111">
         <f>0.0059261*D56*D42</f>
         <v>8171.0494489193279</v>
       </c>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
+      <c r="E57" s="79"/>
+      <c r="F57" s="79"/>
+      <c r="G57" s="79"/>
+      <c r="H57" s="79"/>
+      <c r="I57" s="79"/>
+      <c r="J57" s="79"/>
+      <c r="K57" s="69"/>
+      <c r="L57" s="70"/>
+      <c r="M57" s="70"/>
+      <c r="N57" s="70"/>
+      <c r="O57" s="70"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20">
+      <c r="C58" s="104"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="77">
         <f>IF(E43&gt;$I$35, EXP((LN(1.08)/10)*(E43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="77">
         <f t="shared" ref="F58:O58" si="8">IF(F43&gt;$I$35, EXP((LN(1.08)/10)*(F43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="77">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="H58" s="20">
+      <c r="H58" s="77">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I58" s="20">
+      <c r="I58" s="77">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="J58" s="20">
+      <c r="J58" s="77">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K58" s="20">
+      <c r="K58" s="65">
         <f t="shared" si="8"/>
         <v>1.0312631565524872</v>
       </c>
-      <c r="L58" s="20">
+      <c r="L58" s="66">
         <f t="shared" si="8"/>
         <v>1.0717201098736591</v>
       </c>
-      <c r="M58" s="20">
+      <c r="M58" s="66">
         <f t="shared" si="8"/>
         <v>1.1137642090766864</v>
       </c>
-      <c r="N58" s="20">
+      <c r="N58" s="66">
         <f t="shared" si="8"/>
         <v>1.157457718663552</v>
       </c>
-      <c r="O58" s="20">
+      <c r="O58" s="66">
         <f t="shared" si="8"/>
         <v>1.2028653458028213</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="67"/>
+      <c r="A59" s="54"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="105">
         <f>SUM(K59:O59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="D59" s="42">
+      <c r="D59" s="102">
         <f>SUM(E59:O59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="E59" s="15">
+      <c r="E59" s="76">
         <f>E44*(E58-1)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="76">
         <f t="shared" ref="F59:O59" si="9">F44*(F58-1)</f>
         <v>0</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H59" s="15">
+      <c r="H59" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I59" s="15">
+      <c r="I59" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J59" s="15">
+      <c r="J59" s="76">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K59" s="15">
+      <c r="K59" s="62">
         <f t="shared" si="9"/>
         <v>5.6555463277831062E-3</v>
       </c>
-      <c r="L59" s="15">
+      <c r="L59" s="63">
         <f t="shared" si="9"/>
         <v>1.0521564520921027E-2</v>
       </c>
-      <c r="M59" s="15">
+      <c r="M59" s="63">
         <f t="shared" si="9"/>
         <v>1.3561058273543175E-2</v>
       </c>
-      <c r="N59" s="15">
+      <c r="N59" s="63">
         <f t="shared" si="9"/>
         <v>7.6198423572209177E-3</v>
       </c>
-      <c r="O59" s="15">
+      <c r="O59" s="63">
         <f t="shared" si="9"/>
         <v>9.7353105658576995E-4</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="67"/>
+      <c r="A60" s="54"/>
       <c r="B60" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="15">
+      <c r="C60" s="105">
         <f>C59/(1+C59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="D60" s="42">
+      <c r="D60" s="102">
         <f>D59/(1+D59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="62"/>
+      <c r="L60" s="63"/>
+      <c r="M60" s="63"/>
+      <c r="N60" s="63"/>
+      <c r="O60" s="63"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
-      <c r="B61" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="22">
+      <c r="A61" s="55"/>
+      <c r="B61" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="109">
         <f>0.00127695*C60*D42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="D61" s="43">
+      <c r="D61" s="110">
         <f>0.00127695*D60*D42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
+      <c r="E61" s="79"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
+      <c r="H61" s="79"/>
+      <c r="I61" s="79"/>
+      <c r="J61" s="79"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="70"/>
+      <c r="M61" s="70"/>
+      <c r="N61" s="70"/>
+      <c r="O61" s="70"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="B62" s="34" t="s">
+      <c r="B62" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E62" s="21">
+      <c r="C62" s="106"/>
+      <c r="D62" s="95"/>
+      <c r="E62" s="80">
         <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="80">
         <f t="shared" ref="F62:O62" si="10">IF(F43&gt;$I$30,((78.927 - 3.1162 * F43 + 0.0342 * F43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="G62" s="21">
+      <c r="G62" s="80">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="80">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I62" s="21">
+      <c r="I62" s="80">
         <f t="shared" si="10"/>
         <v>8.0134000000000191E-2</v>
       </c>
-      <c r="J62" s="21">
+      <c r="J62" s="80">
         <f t="shared" si="10"/>
         <v>9.3613999999999892E-2</v>
       </c>
-      <c r="K62" s="21">
+      <c r="K62" s="71">
         <f t="shared" si="10"/>
         <v>0.1241940000000001</v>
       </c>
-      <c r="L62" s="21">
+      <c r="L62" s="72">
         <f t="shared" si="10"/>
         <v>0.17187400000000011</v>
       </c>
-      <c r="M62" s="21">
+      <c r="M62" s="72">
         <f t="shared" si="10"/>
         <v>0.23665399999999978</v>
       </c>
-      <c r="N62" s="21">
+      <c r="N62" s="72">
         <f t="shared" si="10"/>
         <v>0.31853400000000021</v>
       </c>
-      <c r="O62" s="21">
+      <c r="O62" s="72">
         <f t="shared" si="10"/>
         <v>0.41751400000000016</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="69"/>
-      <c r="B63" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E63">
-        <f>$E$44*E62</f>
+      <c r="A63" s="115"/>
+      <c r="B63" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" s="106">
+        <f>SUM(K63:O63)</f>
+        <v>9.3309634085492005E-2</v>
+      </c>
+      <c r="D63" s="95">
+        <f>SUM(E63:O63)</f>
+        <v>0.13400005972406637</v>
+      </c>
+      <c r="E63" s="81">
+        <f>E44*E62</f>
         <v>0</v>
       </c>
-      <c r="F63">
-        <f t="shared" ref="F63:O63" si="11">$E$44*F62</f>
+      <c r="F63" s="81">
+        <f t="shared" ref="F63:O63" si="11">F44*F62</f>
         <v>0</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="81">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="81">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="81">
         <f t="shared" si="11"/>
-        <v>5.7095417904582238E-5</v>
-      </c>
-      <c r="J63">
+        <v>1.1158608274391753E-2</v>
+      </c>
+      <c r="J63" s="81">
         <f t="shared" si="11"/>
-        <v>6.6699908300091627E-5</v>
-      </c>
-      <c r="K63">
+        <v>2.9531817364182603E-2</v>
+      </c>
+      <c r="K63" s="62">
         <f t="shared" si="11"/>
-        <v>8.8488136511863564E-5</v>
-      </c>
-      <c r="L63">
+        <v>2.2466858695265539E-2</v>
+      </c>
+      <c r="L63" s="63">
         <f t="shared" si="11"/>
-        <v>1.2246010253989754E-4</v>
-      </c>
-      <c r="M63">
+        <v>2.5214453570336123E-2</v>
+      </c>
+      <c r="M63" s="63">
         <f t="shared" si="11"/>
-        <v>1.6861580638419349E-4</v>
-      </c>
-      <c r="N63">
+        <v>2.8209915145665603E-2</v>
+      </c>
+      <c r="N63" s="63">
         <f t="shared" si="11"/>
-        <v>2.2695524804475212E-4</v>
-      </c>
-      <c r="O63">
+        <v>1.5414797610533706E-2</v>
+      </c>
+      <c r="O63" s="63">
         <f t="shared" si="11"/>
-        <v>2.9747842752157261E-4</v>
+        <v>2.0036090636910467E-3</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="69"/>
-      <c r="B64" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64">
-        <f>SUM(K63:O63)</f>
-        <v>9.0399772100227928E-4</v>
-      </c>
-      <c r="D64">
-        <f>SUM(E63:O63)</f>
-        <v>1.0277930472069531E-3</v>
-      </c>
-      <c r="E64" s="23"/>
+      <c r="A64" s="116"/>
+      <c r="B64" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="99">
+        <f>C63*$J$30*D42</f>
+        <v>21345.5705628</v>
+      </c>
+      <c r="D64" s="96">
+        <f>J30*D63*D42</f>
+        <v>30653.937916408569</v>
+      </c>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="70"/>
-      <c r="B65" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65" s="36">
-        <f>C64*$J$30*D42</f>
-        <v>206.79908705445007</v>
-      </c>
-      <c r="D65" s="36">
-        <f>D64*$J$30*D42</f>
-        <v>235.11858371463006</v>
-      </c>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
+      <c r="A65" s="21"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="26"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="26"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="29" t="s">
+      <c r="A66" s="21"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="23"/>
+      <c r="E66" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29" t="s">
+      <c r="F66" s="73"/>
+      <c r="G66" s="73"/>
+      <c r="H66" s="73"/>
+      <c r="I66" s="73"/>
+      <c r="J66" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-    </row>
-    <row r="68" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="26"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="30" t="s">
+      <c r="K66" s="57"/>
+      <c r="L66" s="57"/>
+      <c r="M66" s="57"/>
+      <c r="N66" s="57"/>
+      <c r="O66" s="24"/>
+    </row>
+    <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="21"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E67" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="G67" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="H67" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="I67" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J68" s="1" t="s">
+      <c r="J67" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="K67" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L67" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="M67" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N67" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O68" s="15"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="65" t="s">
+      <c r="O67" s="15"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B68" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="37">
-        <f>SUM(E69:N69)</f>
+      <c r="C68" s="18"/>
+      <c r="D68" s="29">
+        <f>SUM(E68:N68)</f>
         <v>15021000</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E68" s="82">
         <f>C14</f>
         <v>64582.789500000006</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F68" s="82">
         <f>D14</f>
         <v>239111.78849999997</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G68" s="82">
         <f>E14</f>
         <v>1126116.8595</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H68" s="82">
         <f>F14</f>
         <v>2838600.9855</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I68" s="82">
         <f>G14</f>
         <v>3242087.577</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J68" s="89">
         <f>Frontend!J15</f>
         <v>3383500</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K68" s="86">
         <f>Frontend!K15</f>
         <v>2682400</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L68" s="86">
         <f>Frontend!L15</f>
         <v>1283500</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M68" s="86">
         <f>Frontend!M15</f>
         <v>156200</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N68" s="86">
         <f>Frontend!N15</f>
         <v>4900</v>
       </c>
+      <c r="O68" s="15"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="54"/>
+      <c r="B69" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="76">
+        <v>27</v>
+      </c>
+      <c r="F69" s="76">
+        <v>32</v>
+      </c>
+      <c r="G69" s="76">
+        <v>37</v>
+      </c>
+      <c r="H69" s="76">
+        <v>42</v>
+      </c>
+      <c r="I69" s="76">
+        <v>47</v>
+      </c>
+      <c r="J69" s="62">
+        <v>52</v>
+      </c>
+      <c r="K69" s="63">
+        <v>57</v>
+      </c>
+      <c r="L69" s="63">
+        <v>62</v>
+      </c>
+      <c r="M69" s="63">
+        <v>67</v>
+      </c>
+      <c r="N69" s="64">
+        <v>72</v>
+      </c>
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="67"/>
-      <c r="B70" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15">
-        <v>27</v>
-      </c>
-      <c r="F70" s="15">
-        <v>32</v>
-      </c>
-      <c r="G70" s="15">
-        <v>37</v>
-      </c>
-      <c r="H70" s="15">
-        <v>42</v>
-      </c>
-      <c r="I70" s="15">
-        <v>47</v>
-      </c>
-      <c r="J70" s="15">
-        <v>52</v>
-      </c>
-      <c r="K70" s="15">
-        <v>57</v>
-      </c>
-      <c r="L70" s="15">
-        <v>62</v>
-      </c>
-      <c r="M70" s="15">
-        <v>67</v>
-      </c>
-      <c r="N70" s="16">
-        <v>72</v>
-      </c>
-      <c r="O70" s="15"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="24" t="s">
+      <c r="A70" s="55"/>
+      <c r="B70" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C71" s="18"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="32">
-        <f>E69/$D$69</f>
+      <c r="C70" s="16"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="83">
+        <f>E68/$D$68</f>
         <v>4.2995000000000004E-3</v>
       </c>
-      <c r="F71" s="32">
-        <f t="shared" ref="F71:N71" si="12">F69/$D$69</f>
+      <c r="F70" s="83">
+        <f t="shared" ref="F70:N70" si="12">F68/$D$68</f>
         <v>1.5918499999999999E-2</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G70" s="83">
         <f t="shared" si="12"/>
         <v>7.4969499999999994E-2</v>
       </c>
-      <c r="H71" s="32">
+      <c r="H70" s="83">
         <f t="shared" si="12"/>
         <v>0.18897549999999999</v>
       </c>
-      <c r="I71" s="32">
+      <c r="I70" s="83">
         <f t="shared" si="12"/>
         <v>0.215837</v>
       </c>
-      <c r="J71" s="32">
+      <c r="J70" s="90">
         <f t="shared" si="12"/>
         <v>0.2252513148259104</v>
       </c>
-      <c r="K71" s="32">
+      <c r="K70" s="87">
         <f t="shared" si="12"/>
         <v>0.17857665934358566</v>
       </c>
-      <c r="L71" s="32">
+      <c r="L70" s="87">
         <f t="shared" si="12"/>
         <v>8.5447040809533317E-2</v>
       </c>
-      <c r="M71" s="32">
+      <c r="M70" s="87">
         <f t="shared" si="12"/>
         <v>1.0398775048265762E-2</v>
       </c>
-      <c r="N71" s="32">
+      <c r="N70" s="87">
         <f t="shared" si="12"/>
         <v>3.2620997270487985E-4</v>
       </c>
+      <c r="O70" s="15"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" s="32"/>
+      <c r="C71" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="107" t="s">
+        <v>101</v>
+      </c>
+      <c r="E71" s="84"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="84"/>
+      <c r="H71" s="84"/>
+      <c r="I71" s="84"/>
+      <c r="J71" s="91"/>
+      <c r="K71" s="88"/>
+      <c r="L71" s="88"/>
+      <c r="M71" s="88"/>
+      <c r="N71" s="88"/>
       <c r="O71" s="15"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B72" s="40"/>
-      <c r="C72" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
-      <c r="L72" s="41"/>
-      <c r="M72" s="41"/>
-      <c r="N72" s="41"/>
-      <c r="O72" s="15"/>
-    </row>
-    <row r="73" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="71" t="s">
+    <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="B73" s="34" t="s">
+      <c r="B72" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E73" s="34">
-        <f>IF(E70&gt;$I$31,((19.4312 - 0.9336 *  E70 + 0.0126 *  E70^2)/100),0)</f>
+      <c r="C72" s="98"/>
+      <c r="D72" s="108"/>
+      <c r="E72" s="85">
+        <f>IF(E69&gt;$I$31,((19.4312 - 0.9336 *  E69 + 0.0126 *  E69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="F73" s="34">
-        <f t="shared" ref="F73:N73" si="13">IF(F70&gt;$I$31,((19.4312 - 0.9336 *  F70 + 0.0126 *  F70^2)/100),0)</f>
+      <c r="F72" s="85">
+        <f t="shared" ref="F72:N72" si="13">IF(F69&gt;$I$31,((19.4312 - 0.9336 *  F69 + 0.0126 *  F69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="G73" s="34">
+      <c r="G72" s="85">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H73" s="34">
+      <c r="H72" s="85">
         <f t="shared" si="13"/>
         <v>2.4464000000000041E-2</v>
       </c>
-      <c r="I73" s="34">
+      <c r="I72" s="85">
         <f t="shared" si="13"/>
         <v>3.3854000000000044E-2</v>
       </c>
-      <c r="J73" s="34">
+      <c r="J72" s="67">
         <f t="shared" si="13"/>
         <v>4.9544000000000032E-2</v>
       </c>
-      <c r="K73" s="34">
+      <c r="K72" s="68">
         <f t="shared" si="13"/>
         <v>7.1534000000000125E-2</v>
       </c>
-      <c r="L73" s="34">
+      <c r="L72" s="68">
         <f t="shared" si="13"/>
         <v>9.9824000000000052E-2</v>
       </c>
-      <c r="M73" s="34">
+      <c r="M72" s="68">
         <f t="shared" si="13"/>
         <v>0.13441399999999995</v>
       </c>
-      <c r="N73" s="34">
+      <c r="N72" s="68">
         <f t="shared" si="13"/>
         <v>0.17530400000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="71"/>
-      <c r="B74" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E74" s="34">
-        <f>E73*E71</f>
+    <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="117"/>
+      <c r="B73" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" s="98">
+        <f>SUM(J73:N73)</f>
+        <v>3.3918746155382498E-2</v>
+      </c>
+      <c r="D73" s="108">
+        <f>SUM(E73:N73)</f>
+        <v>4.5848788585382522E-2</v>
+      </c>
+      <c r="E73" s="85">
+        <f>E72*E70</f>
         <v>0</v>
       </c>
-      <c r="F74" s="34">
-        <f t="shared" ref="F74:N74" si="14">F73*F71</f>
+      <c r="F73" s="85">
+        <f t="shared" ref="F73:N73" si="14">F72*F70</f>
         <v>0</v>
       </c>
-      <c r="G74" s="34">
+      <c r="G73" s="85">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H74" s="34">
+      <c r="H73" s="85">
         <f t="shared" si="14"/>
         <v>4.6230966320000072E-3</v>
       </c>
-      <c r="I74" s="34">
+      <c r="I73" s="85">
         <f t="shared" si="14"/>
         <v>7.3069457980000094E-3</v>
       </c>
-      <c r="J74" s="34">
+      <c r="J73" s="67">
         <f t="shared" si="14"/>
         <v>1.1159851141734912E-2</v>
       </c>
-      <c r="K74" s="34">
+      <c r="K73" s="68">
         <f t="shared" si="14"/>
         <v>1.2774302749484078E-2</v>
       </c>
-      <c r="L74" s="34">
+      <c r="L73" s="68">
         <f t="shared" si="14"/>
         <v>8.5296654017708584E-3</v>
       </c>
-      <c r="M74" s="34">
+      <c r="M73" s="68">
         <f t="shared" si="14"/>
         <v>1.3977409493375935E-3</v>
       </c>
-      <c r="N74" s="34">
+      <c r="N73" s="68">
         <f t="shared" si="14"/>
         <v>5.718591305505626E-5</v>
       </c>
     </row>
-    <row r="75" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="71"/>
-      <c r="B75" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="34">
-        <f>SUM(J74:N74)</f>
-        <v>3.3918746155382498E-2</v>
-      </c>
-      <c r="D75" s="34">
-        <f>SUM(E74:N74)</f>
-        <v>4.5848788585382522E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="70"/>
-      <c r="B76" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="C76" s="36">
-        <f>C75*J31*D69</f>
+    <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="116"/>
+      <c r="B74" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="99">
+        <f>J31*C73*D68</f>
         <v>5094.9348600000048</v>
       </c>
-      <c r="D76" s="36">
-        <f>D75*J31*D69</f>
+      <c r="D74" s="96">
+        <f>J31*D73*D68</f>
         <v>6886.9465334103088</v>
       </c>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
-      <c r="L76" s="35"/>
-      <c r="M76" s="35"/>
-      <c r="N76" s="35"/>
-      <c r="O76" s="24"/>
-    </row>
-    <row r="79" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="25" t="s">
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="28"/>
+      <c r="L74" s="28"/>
+      <c r="M74" s="28"/>
+      <c r="N74" s="28"/>
+      <c r="O74" s="19"/>
+    </row>
+    <row r="77" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C80" t="s">
+    <row r="78" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
         <v>100</v>
       </c>
-      <c r="D80" t="s">
-        <v>140</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="D78" t="s">
+        <v>137</v>
+      </c>
+      <c r="E78" t="s">
         <v>106</v>
       </c>
+      <c r="F78" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B79" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" s="40">
+        <f>C61+C64+C74</f>
+        <v>27420.859000423719</v>
+      </c>
+      <c r="D79" s="40">
+        <f>D49+D53+D57+D64+D74</f>
+        <v>308626.30242553435</v>
+      </c>
+      <c r="E79" s="34">
+        <f>D79-C79</f>
+        <v>281205.44342511066</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B80" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C80" s="41">
+        <f>C79*70000</f>
+        <v>1919460130.0296605</v>
+      </c>
+      <c r="D80" s="41">
+        <f>D79*70000</f>
+        <v>21603841169.787403</v>
+      </c>
+      <c r="E80" s="35">
+        <f>D80-C80</f>
+        <v>19684381039.757744</v>
+      </c>
       <c r="F80" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B81" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" s="51">
-        <f>C61+C65+C76</f>
-        <v>6282.0875246781688</v>
-      </c>
-      <c r="D81" s="51">
-        <f>D49+D53+D57+D65+D76</f>
-        <v>278207.48309284041</v>
-      </c>
-      <c r="E81" s="45">
-        <f>D81-C81</f>
-        <v>271925.39556816226</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B82" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="C82" s="52">
-        <f>C81*70000</f>
-        <v>439746126.72747183</v>
-      </c>
-      <c r="D82" s="52">
-        <f>D81*70000</f>
-        <v>19474523816.498829</v>
-      </c>
-      <c r="E82" s="46">
-        <f>D82-C82</f>
-        <v>19034777689.771358</v>
-      </c>
-      <c r="F82" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>149</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" s="40">
+        <f>C79/D42*100000</f>
+        <v>131.85374189567494</v>
+      </c>
+      <c r="D82" s="40">
+        <f>D79/D42*100000</f>
+        <v>1484.035668671215</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B83" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C83" s="45">
+        <f>C80/D42*100000</f>
+        <v>9229761.9326972459</v>
+      </c>
+      <c r="D83" s="45">
+        <f>D80/D42*100000</f>
+        <v>103882496.80698505</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="J40:N40"/>
-    <mergeCell ref="A62:A65"/>
+  <mergeCells count="12">
+    <mergeCell ref="E40:J40"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="E66:I66"/>
+    <mergeCell ref="J66:N66"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A62:A64"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="A58:A61"/>
-    <mergeCell ref="D40:I40"/>
     <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A68:A70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3918,69 +4147,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>131</v>
+      <c r="A1" s="30" t="s">
+        <v>130</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="47">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="36">
+        <v>2</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="36">
+        <v>3</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="37" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="47">
-        <v>2</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="48" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="36">
+        <v>4</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
-        <v>3</v>
-      </c>
-      <c r="B4" s="59" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="39">
+        <v>5</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" t="s">
         <v>145</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
-        <v>4</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="50">
-        <v>5</v>
-      </c>
-      <c r="B6" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A1B052-1B98-4ECA-BD22-E37BF79E7598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEB5DC1-4A20-4A20-BB0B-3731B1B2A70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="156">
   <si>
     <t>L_den</t>
   </si>
@@ -589,32 +589,19 @@
     <t>YLD = DW * Sum p[i]*ERF[Ni] * Summe der Exponierten Lnight</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">DALY pro 100.000 (DALY * </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Exponierte Lden </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>* 100k)</t>
-    </r>
-  </si>
-  <si>
-    <t>EURO pro 100.000 (EURO * Exponierte Lden * 100k)</t>
+    <t>Kartierungsgebiet</t>
+  </si>
+  <si>
+    <t>Quelle</t>
+  </si>
+  <si>
+    <t>DALY pro 100.000 = (DALY / Population in Ballungsraum) * 100k</t>
+  </si>
+  <si>
+    <t>EURO pro 100.000 = (EURO / Population in Ballungsraum) * 100k</t>
+  </si>
+  <si>
+    <t>Population in Ballungsräumen Deutschland</t>
   </si>
 </sst>
 </file>
@@ -740,7 +727,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -771,8 +758,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -880,6 +885,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -889,7 +931,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -972,31 +1014,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1017,9 +1034,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1084,18 +1098,71 @@
     <xf numFmtId="4" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1606,458 +1673,476 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
     </row>
-    <row r="4" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+    <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-    </row>
-    <row r="8" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="50" t="s">
+    <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="120" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="50"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="51" t="s">
+      <c r="B10" s="120"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="110" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="110" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="J12" s="51" t="s">
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="K12" s="118" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-    </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="C13" s="1" t="s">
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+    </row>
+    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="110"/>
+      <c r="B13" s="110"/>
+      <c r="D13" s="104" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="104" t="s">
         <v>121</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="107" t="s">
         <v>126</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="107" t="s">
         <v>127</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" s="108" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="52" t="s">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="8">
+      <c r="D14" s="106">
         <v>3725500</v>
       </c>
-      <c r="D14" s="8">
+      <c r="E14" s="106">
         <v>1643600</v>
       </c>
-      <c r="E14" s="8">
+      <c r="F14" s="106">
         <v>998600</v>
       </c>
-      <c r="F14" s="8">
+      <c r="G14" s="106">
         <v>481900</v>
       </c>
-      <c r="G14" s="8">
+      <c r="H14" s="106">
         <v>33500</v>
       </c>
-      <c r="H14" s="8">
-        <f>SUM(C14:G14)</f>
+      <c r="I14" s="106">
+        <f>SUM(D14:H14)</f>
         <v>6883100</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8">
+      <c r="J14" s="8"/>
+      <c r="K14" s="109">
         <v>2411700</v>
       </c>
-      <c r="K14" s="8">
+      <c r="L14" s="109">
         <v>1244300</v>
       </c>
-      <c r="L14" s="8">
+      <c r="M14" s="109">
         <v>574000</v>
       </c>
-      <c r="M14" s="8">
+      <c r="N14" s="109">
         <v>54400</v>
       </c>
-      <c r="N14" s="8">
+      <c r="O14" s="109">
         <v>2100</v>
       </c>
-      <c r="O14" s="8">
-        <f>SUM(J14:N14)</f>
+      <c r="P14" s="109">
+        <f>SUM(K14:O14)</f>
         <v>4286500</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
-      <c r="B15" t="s">
+    <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="121"/>
+      <c r="B15" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="112"/>
+      <c r="D15" s="113">
         <v>3762100</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E15" s="113">
         <v>3050900</v>
       </c>
-      <c r="E15" s="8">
+      <c r="F15" s="117">
         <v>2479000</v>
       </c>
-      <c r="F15" s="8">
+      <c r="G15" s="113">
         <v>1006400</v>
       </c>
-      <c r="G15" s="8">
+      <c r="H15" s="113">
         <v>99800</v>
       </c>
-      <c r="H15" s="8">
-        <f t="shared" ref="H15:H23" si="0">SUM(C15:G15)</f>
+      <c r="I15" s="113">
+        <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
         <v>10398200</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8">
+      <c r="J15" s="114"/>
+      <c r="K15" s="115">
         <v>3383500</v>
       </c>
-      <c r="K15" s="8">
+      <c r="L15" s="115">
         <v>2682400</v>
       </c>
-      <c r="L15" s="8">
+      <c r="M15" s="115">
         <v>1283500</v>
       </c>
-      <c r="M15" s="8">
+      <c r="N15" s="115">
         <v>156200</v>
       </c>
-      <c r="N15" s="8">
+      <c r="O15" s="115">
         <v>4900</v>
       </c>
-      <c r="O15" s="8">
-        <f t="shared" ref="O15:O23" si="1">SUM(J15:N15)</f>
+      <c r="P15" s="116">
+        <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
         <v>7510500</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+    <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="110"/>
+      <c r="B16" s="110"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="109"/>
+      <c r="M16" s="109"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="109"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="110"/>
+      <c r="B17" s="110"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="K17" s="109"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="109"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="121" t="s">
         <v>78</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="110" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="8">
+      <c r="D18" s="106">
         <v>716500</v>
       </c>
-      <c r="D18" s="8">
+      <c r="E18" s="106">
         <v>340700</v>
       </c>
-      <c r="E18" s="8">
+      <c r="F18" s="106">
         <v>141700</v>
       </c>
-      <c r="F18" s="8">
+      <c r="G18" s="106">
         <v>36000</v>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="106">
         <v>4600</v>
       </c>
-      <c r="H18" s="8">
+      <c r="I18" s="106">
         <f t="shared" si="0"/>
         <v>1239500</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8">
+      <c r="J18" s="8"/>
+      <c r="K18" s="109">
         <v>568900</v>
       </c>
-      <c r="K18" s="8">
+      <c r="L18" s="109">
         <v>258600</v>
       </c>
-      <c r="L18" s="8">
+      <c r="M18" s="109">
         <v>93100</v>
       </c>
-      <c r="M18" s="8">
+      <c r="N18" s="109">
         <v>21100</v>
       </c>
-      <c r="N18" s="8">
+      <c r="O18" s="109">
         <v>2200</v>
       </c>
-      <c r="O18" s="8">
+      <c r="P18" s="109">
         <f t="shared" si="1"/>
         <v>943900</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
-      <c r="B19" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="121"/>
+      <c r="B19" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="8">
+      <c r="D19" s="106">
         <v>1289300</v>
       </c>
-      <c r="D19" s="8">
+      <c r="E19" s="106">
         <v>787600</v>
       </c>
-      <c r="E19" s="8">
+      <c r="F19" s="106">
         <v>383200</v>
       </c>
-      <c r="F19" s="8">
+      <c r="G19" s="106">
         <v>74300</v>
       </c>
-      <c r="G19" s="8">
+      <c r="H19" s="106">
         <v>13200</v>
       </c>
-      <c r="H19" s="8">
+      <c r="I19" s="106">
         <f t="shared" si="0"/>
         <v>2547600</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8">
+      <c r="J19" s="8"/>
+      <c r="K19" s="109">
         <v>1058400</v>
       </c>
-      <c r="K19" s="8">
+      <c r="L19" s="109">
         <v>609100</v>
       </c>
-      <c r="L19" s="8">
+      <c r="M19" s="109">
         <v>175500</v>
       </c>
-      <c r="M19" s="8">
+      <c r="N19" s="109">
         <v>32000</v>
       </c>
-      <c r="N19" s="8">
+      <c r="O19" s="109">
         <v>7700</v>
       </c>
-      <c r="O19" s="8">
+      <c r="P19" s="109">
         <f t="shared" si="1"/>
         <v>1882700</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="109"/>
+      <c r="P20" s="109"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="110"/>
+      <c r="B21" s="110"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="52" t="s">
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="121" t="s">
         <v>81</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="110" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="8">
+      <c r="D22" s="106">
         <v>303900</v>
       </c>
-      <c r="D22" s="8">
+      <c r="E22" s="106">
         <v>69900</v>
       </c>
-      <c r="E22" s="8">
+      <c r="F22" s="106">
         <v>3900</v>
       </c>
-      <c r="F22" s="8">
+      <c r="G22" s="106">
         <v>0</v>
       </c>
-      <c r="G22" s="8">
+      <c r="H22" s="106">
         <v>0</v>
       </c>
-      <c r="H22" s="8">
+      <c r="I22" s="106">
         <f t="shared" si="0"/>
         <v>377700</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8">
+      <c r="J22" s="8"/>
+      <c r="K22" s="109">
         <v>123200</v>
       </c>
-      <c r="K22" s="8">
+      <c r="L22" s="109">
         <v>17600</v>
       </c>
-      <c r="L22" s="8">
+      <c r="M22" s="109">
         <v>400</v>
       </c>
-      <c r="M22" s="8">
+      <c r="N22" s="109">
         <v>0</v>
       </c>
-      <c r="N22" s="8">
+      <c r="O22" s="109">
         <v>0</v>
       </c>
-      <c r="O22" s="8">
+      <c r="P22" s="109">
         <f t="shared" si="1"/>
         <v>141200</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
-      <c r="B23" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="121"/>
+      <c r="B23" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="8">
+      <c r="D23" s="106">
         <v>419800</v>
       </c>
-      <c r="D23" s="8">
+      <c r="E23" s="106">
         <v>51900</v>
       </c>
-      <c r="E23" s="8">
+      <c r="F23" s="106">
         <v>3000</v>
       </c>
-      <c r="F23" s="8">
+      <c r="G23" s="106">
         <v>700</v>
       </c>
-      <c r="G23" s="8">
+      <c r="H23" s="106">
         <v>0</v>
       </c>
-      <c r="H23" s="8">
+      <c r="I23" s="106">
         <f t="shared" si="0"/>
         <v>475400</v>
       </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8">
+      <c r="J23" s="8"/>
+      <c r="K23" s="109">
         <v>121500</v>
       </c>
-      <c r="K23" s="8">
+      <c r="L23" s="109">
         <v>10900</v>
       </c>
-      <c r="L23" s="8">
+      <c r="M23" s="109">
         <v>400</v>
       </c>
-      <c r="M23" s="8">
+      <c r="N23" s="109">
         <v>0</v>
       </c>
-      <c r="N23" s="8">
+      <c r="O23" s="109">
         <v>0</v>
       </c>
-      <c r="O23" s="8">
+      <c r="P23" s="109">
         <f t="shared" si="1"/>
         <v>132800</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="50" t="s">
+    <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="120" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="50"/>
+      <c r="B32" s="120"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2121,14 +2206,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="K12:P12"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="J12:O12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A22:A23"/>
+    <mergeCell ref="D12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2138,7 +2223,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -2281,27 +2366,27 @@
         <v>73</v>
       </c>
       <c r="C13" s="6">
-        <f>Frontend!$H$15*C8</f>
+        <f>Frontend!$I$15*C8</f>
         <v>14817.435000000001</v>
       </c>
       <c r="D13" s="6">
-        <f>Frontend!$H$15*D8</f>
+        <f>Frontend!$I$15*D8</f>
         <v>43360.493999999999</v>
       </c>
       <c r="E13" s="6">
-        <f>Frontend!$H$15*E8</f>
+        <f>Frontend!$I$15*E8</f>
         <v>175282.45740000001</v>
       </c>
       <c r="F13" s="6">
-        <f>Frontend!$H$15*F8</f>
+        <f>Frontend!$I$15*F8</f>
         <v>708356.57860000001</v>
       </c>
       <c r="G13" s="6">
-        <f>Frontend!$H$15*G8</f>
+        <f>Frontend!$I$15*G8</f>
         <v>2895888.3018</v>
       </c>
       <c r="H13" s="6">
-        <f>Frontend!$H$15*H8</f>
+        <f>Frontend!$I$15*H8</f>
         <v>6560515.5296</v>
       </c>
       <c r="I13" s="6">
@@ -2314,23 +2399,23 @@
         <v>74</v>
       </c>
       <c r="C14" s="6">
-        <f>Frontend!$O$15*C9</f>
+        <f>Frontend!$P$15*C9</f>
         <v>64582.789500000006</v>
       </c>
       <c r="D14" s="6">
-        <f>Frontend!$O$15*D9</f>
+        <f>Frontend!$P$15*D9</f>
         <v>239111.78849999997</v>
       </c>
       <c r="E14" s="6">
-        <f>Frontend!$O$15*E9</f>
+        <f>Frontend!$P$15*E9</f>
         <v>1126116.8595</v>
       </c>
       <c r="F14" s="6">
-        <f>Frontend!$O$15*F9</f>
+        <f>Frontend!$P$15*F9</f>
         <v>2838600.9855</v>
       </c>
       <c r="G14" s="6">
-        <f>Frontend!$O$15*G9</f>
+        <f>Frontend!$P$15*G9</f>
         <v>3242087.577</v>
       </c>
       <c r="H14" s="7" t="s">
@@ -2356,7 +2441,7 @@
         <v>73</v>
       </c>
       <c r="C18" s="8">
-        <f>Frontend!$H$15+I13</f>
+        <f>Frontend!$I$15+I13</f>
         <v>20796420.796399999</v>
       </c>
     </row>
@@ -2365,7 +2450,7 @@
         <v>74</v>
       </c>
       <c r="C19" s="8">
-        <f>Frontend!$O$15+I14</f>
+        <f>Frontend!$P$15+I14</f>
         <v>15021000</v>
       </c>
     </row>
@@ -2648,62 +2733,62 @@
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="E40" s="73" t="s">
+      <c r="E40" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="56" t="s">
+      <c r="F40" s="123"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="123"/>
+      <c r="I40" s="123"/>
+      <c r="J40" s="123"/>
+      <c r="K40" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="57"/>
+      <c r="L40" s="125"/>
+      <c r="M40" s="125"/>
+      <c r="N40" s="125"/>
+      <c r="O40" s="125"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="E41" s="74" t="s">
+      <c r="E41" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="74" t="s">
+      <c r="F41" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G41" s="74" t="s">
+      <c r="G41" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="74" t="s">
+      <c r="H41" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="I41" s="74" t="s">
+      <c r="I41" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="J41" s="74" t="s">
+      <c r="J41" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="K41" s="58" t="s">
+      <c r="K41" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="L41" s="59" t="s">
+      <c r="L41" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="M41" s="59" t="s">
+      <c r="M41" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="N41" s="59" t="s">
+      <c r="N41" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="O41" s="59" t="s">
+      <c r="O41" s="50" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="130" t="s">
         <v>102</v>
       </c>
       <c r="B42" s="43" t="s">
@@ -2714,48 +2799,48 @@
         <f>SUM(E42:O42)</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="E42" s="75">
+      <c r="E42" s="65">
         <f t="shared" ref="E42:J42" si="0">C13</f>
         <v>14817.435000000001</v>
       </c>
-      <c r="F42" s="75">
+      <c r="F42" s="65">
         <f t="shared" si="0"/>
         <v>43360.493999999999</v>
       </c>
-      <c r="G42" s="75">
+      <c r="G42" s="65">
         <f t="shared" si="0"/>
         <v>175282.45740000001</v>
       </c>
-      <c r="H42" s="75">
+      <c r="H42" s="65">
         <f t="shared" si="0"/>
         <v>708356.57860000001</v>
       </c>
-      <c r="I42" s="75">
+      <c r="I42" s="65">
         <f t="shared" si="0"/>
         <v>2895888.3018</v>
       </c>
-      <c r="J42" s="75">
+      <c r="J42" s="65">
         <f t="shared" si="0"/>
         <v>6560515.5296</v>
       </c>
-      <c r="K42" s="60">
-        <f>Frontend!C15</f>
+      <c r="K42" s="51">
+        <f>Frontend!D15</f>
         <v>3762100</v>
       </c>
-      <c r="L42" s="61">
-        <f>Frontend!D15</f>
+      <c r="L42" s="52">
+        <f>Frontend!E15</f>
         <v>3050900</v>
       </c>
-      <c r="M42" s="61">
-        <f>Frontend!E15</f>
+      <c r="M42" s="52">
+        <f>Frontend!F15</f>
         <v>2479000</v>
       </c>
-      <c r="N42" s="61">
-        <f>Frontend!F15</f>
+      <c r="N42" s="52">
+        <f>Frontend!G15</f>
         <v>1006400</v>
       </c>
-      <c r="O42" s="61">
-        <f>Frontend!G15</f>
+      <c r="O42" s="52">
+        <f>Frontend!H15</f>
         <v>99800</v>
       </c>
       <c r="Q42" s="8"/>
@@ -2765,94 +2850,94 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="54"/>
+      <c r="A43" s="131"/>
       <c r="B43" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="76">
+      <c r="E43" s="66">
         <v>27</v>
       </c>
-      <c r="F43" s="76">
+      <c r="F43" s="66">
         <v>32</v>
       </c>
-      <c r="G43" s="76">
+      <c r="G43" s="66">
         <v>37</v>
       </c>
-      <c r="H43" s="76">
+      <c r="H43" s="66">
         <v>42</v>
       </c>
-      <c r="I43" s="76">
+      <c r="I43" s="66">
         <v>47</v>
       </c>
-      <c r="J43" s="76">
+      <c r="J43" s="66">
         <v>52</v>
       </c>
-      <c r="K43" s="62">
+      <c r="K43" s="53">
         <v>57</v>
       </c>
-      <c r="L43" s="63">
+      <c r="L43" s="54">
         <v>62</v>
       </c>
-      <c r="M43" s="63">
+      <c r="M43" s="54">
         <v>67</v>
       </c>
-      <c r="N43" s="63">
+      <c r="N43" s="54">
         <v>72</v>
       </c>
-      <c r="O43" s="64">
+      <c r="O43" s="55">
         <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="55"/>
+      <c r="A44" s="132"/>
       <c r="B44" s="19" t="s">
         <v>109</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="76">
-        <f t="shared" ref="E44:O44" si="1">E42/$D$42</f>
+      <c r="E44" s="66">
+        <f>E42/$D$42</f>
         <v>7.1249928750071259E-4</v>
       </c>
-      <c r="F44" s="76">
-        <f t="shared" si="1"/>
+      <c r="F44" s="66">
+        <f t="shared" ref="F44:O44" si="1">F42/$D$42</f>
         <v>2.0849979150020848E-3</v>
       </c>
-      <c r="G44" s="76">
+      <c r="G44" s="66">
         <f t="shared" si="1"/>
         <v>8.4284915715084289E-3</v>
       </c>
-      <c r="H44" s="76">
+      <c r="H44" s="66">
         <f t="shared" si="1"/>
         <v>3.4061465938534062E-2</v>
       </c>
-      <c r="I44" s="76">
+      <c r="I44" s="66">
         <f t="shared" si="1"/>
         <v>0.13924936075063926</v>
       </c>
-      <c r="J44" s="76">
+      <c r="J44" s="66">
         <f t="shared" si="1"/>
         <v>0.31546368453631546</v>
       </c>
-      <c r="K44" s="62">
+      <c r="K44" s="53">
         <f t="shared" si="1"/>
         <v>0.18090132128174888</v>
       </c>
-      <c r="L44" s="63">
+      <c r="L44" s="54">
         <f t="shared" si="1"/>
         <v>0.14670312886379619</v>
       </c>
-      <c r="M44" s="63">
+      <c r="M44" s="54">
         <f t="shared" si="1"/>
         <v>0.11920320444896612</v>
       </c>
-      <c r="N44" s="63">
+      <c r="N44" s="54">
         <f t="shared" si="1"/>
         <v>4.8392942701669828E-2</v>
       </c>
-      <c r="O44" s="63">
+      <c r="O44" s="54">
         <f t="shared" si="1"/>
         <v>4.7989027043190075E-3</v>
       </c>
@@ -2861,794 +2946,794 @@
       <c r="A45" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="103" t="s">
+      <c r="C45" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="92" t="s">
+      <c r="D45" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="77"/>
-      <c r="J45" s="77"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="66"/>
-      <c r="M45" s="66"/>
-      <c r="N45" s="66"/>
-      <c r="O45" s="66"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="67"/>
+      <c r="J45" s="67"/>
+      <c r="K45" s="56"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="57"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="130" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="101"/>
-      <c r="D46" s="92"/>
-      <c r="E46" s="77">
+      <c r="C46" s="91"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="67">
         <f>IF(E43&gt;$I$32, EXP((LN(1.055)/10)*(E43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="F46" s="77">
+      <c r="F46" s="67">
         <f t="shared" ref="F46:O46" si="2">IF(F43&gt;$I$32, EXP((LN(1.055)/10)*(F43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="G46" s="77">
+      <c r="G46" s="67">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H46" s="77">
+      <c r="H46" s="67">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I46" s="77">
+      <c r="I46" s="67">
         <f t="shared" si="2"/>
         <v>1.0107656908500073</v>
       </c>
-      <c r="J46" s="77">
+      <c r="J46" s="67">
         <f t="shared" si="2"/>
         <v>1.0381897140207395</v>
       </c>
-      <c r="K46" s="65">
+      <c r="K46" s="56">
         <f t="shared" si="2"/>
         <v>1.0663578038467578</v>
       </c>
-      <c r="L46" s="66">
+      <c r="L46" s="57">
         <f t="shared" si="2"/>
         <v>1.09529014829188</v>
       </c>
-      <c r="M46" s="66">
+      <c r="M46" s="57">
         <f t="shared" si="2"/>
         <v>1.1250074830583294</v>
       </c>
-      <c r="N46" s="66">
+      <c r="N46" s="57">
         <f t="shared" si="2"/>
         <v>1.1555311064479334</v>
       </c>
-      <c r="O46" s="66">
+      <c r="O46" s="57">
         <f t="shared" si="2"/>
         <v>1.1868828946265373</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
+      <c r="A47" s="131"/>
       <c r="B47" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="102">
+      <c r="C47" s="92">
         <f>SUM(K47:O47)</f>
         <v>4.9308310609276644E-2</v>
       </c>
-      <c r="D47" s="93">
+      <c r="D47" s="83">
         <f>SUM(E47:O47)</f>
         <v>6.2854894074549819E-2</v>
       </c>
-      <c r="E47" s="78">
+      <c r="E47" s="68">
         <f>E44*(E46-1)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="78">
+      <c r="F47" s="68">
         <f t="shared" ref="F47:O47" si="3">F44*(F46-1)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="78">
+      <c r="G47" s="68">
         <f>G44*(G46-1)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="78">
+      <c r="H47" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I47" s="78">
+      <c r="I47" s="68">
         <f t="shared" si="3"/>
         <v>1.4991155689025278E-3</v>
       </c>
-      <c r="J47" s="78">
+      <c r="J47" s="68">
         <f t="shared" si="3"/>
         <v>1.2047467896370654E-2</v>
       </c>
-      <c r="K47" s="67">
+      <c r="K47" s="58">
         <f t="shared" si="3"/>
         <v>1.2004214393233608E-2</v>
       </c>
-      <c r="L47" s="68">
+      <c r="L47" s="59">
         <f t="shared" si="3"/>
         <v>1.3979362904313918E-2</v>
       </c>
-      <c r="M47" s="68">
+      <c r="M47" s="59">
         <f t="shared" si="3"/>
         <v>1.4901292560652712E-2</v>
       </c>
-      <c r="N47" s="68">
+      <c r="N47" s="59">
         <f t="shared" si="3"/>
         <v>7.5266079226621535E-3</v>
       </c>
-      <c r="O47" s="68">
+      <c r="O47" s="59">
         <f t="shared" si="3"/>
         <v>8.9683282841425394E-4</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
+      <c r="A48" s="131"/>
       <c r="B48" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="102">
+      <c r="C48" s="92">
         <f>(C47)/(1+C47)</f>
         <v>4.6991251389828383E-2</v>
       </c>
-      <c r="D48" s="94">
+      <c r="D48" s="84">
         <f>(D47)/(1+D47)</f>
         <v>5.9137794279320602E-2</v>
       </c>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="76"/>
-      <c r="K48" s="62"/>
-      <c r="L48" s="63"/>
-      <c r="M48" s="63"/>
-      <c r="N48" s="63"/>
-      <c r="O48" s="63"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
+      <c r="K48" s="53"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="55"/>
+      <c r="A49" s="132"/>
       <c r="B49" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="113">
+      <c r="C49" s="103">
         <f>0.2069215*C48*D42</f>
         <v>202214.00228176778</v>
       </c>
-      <c r="D49" s="112">
+      <c r="D49" s="102">
         <f>0.2069215*D48*D42</f>
         <v>254483.32856966133</v>
       </c>
-      <c r="E49" s="79"/>
-      <c r="F49" s="79"/>
-      <c r="G49" s="79"/>
-      <c r="H49" s="79"/>
-      <c r="I49" s="79"/>
-      <c r="J49" s="79"/>
-      <c r="K49" s="69"/>
-      <c r="L49" s="70"/>
-      <c r="M49" s="70"/>
-      <c r="N49" s="70"/>
-      <c r="O49" s="70"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="60"/>
+      <c r="L49" s="61"/>
+      <c r="M49" s="61"/>
+      <c r="N49" s="61"/>
+      <c r="O49" s="61"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="53" t="s">
+      <c r="A50" s="130" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="101"/>
-      <c r="D50" s="92"/>
-      <c r="E50" s="77">
+      <c r="C50" s="91"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="67">
         <f>IF(E43&gt;$I$33, EXP((LN(1.032)/10)*(E43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="F50" s="77">
+      <c r="F50" s="67">
         <f t="shared" ref="F50:O50" si="4">IF(F43&gt;$I$33, EXP((LN(1.032)/10)*(F43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="G50" s="77">
+      <c r="G50" s="67">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H50" s="77">
+      <c r="H50" s="67">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I50" s="77">
+      <c r="I50" s="67">
         <f t="shared" si="4"/>
         <v>1.0063196184673233</v>
       </c>
-      <c r="J50" s="77">
+      <c r="J50" s="67">
         <f t="shared" si="4"/>
         <v>1.0222939440770498</v>
       </c>
-      <c r="K50" s="65">
+      <c r="K50" s="56">
         <f t="shared" si="4"/>
         <v>1.0385218462582777</v>
       </c>
-      <c r="L50" s="66">
+      <c r="L50" s="57">
         <f t="shared" si="4"/>
         <v>1.0550073502875155</v>
       </c>
-      <c r="M50" s="66">
+      <c r="M50" s="57">
         <f t="shared" si="4"/>
         <v>1.0717545453385426</v>
       </c>
-      <c r="N50" s="66">
+      <c r="N50" s="57">
         <f t="shared" si="4"/>
         <v>1.088767585496716</v>
       </c>
-      <c r="O50" s="66">
+      <c r="O50" s="57">
         <f t="shared" si="4"/>
         <v>1.1060506907893759</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="54"/>
+      <c r="A51" s="131"/>
       <c r="B51" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C51" s="102">
+      <c r="C51" s="92">
         <f>SUM(K51:O51)</f>
         <v>2.8396426647685286E-2</v>
       </c>
-      <c r="D51" s="93">
+      <c r="D51" s="83">
         <f>SUM(E51:O51)</f>
         <v>3.6309359220840685E-2</v>
       </c>
-      <c r="E51" s="76">
+      <c r="E51" s="66">
         <f>E44*(E50-1)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="76">
+      <c r="F51" s="66">
         <f t="shared" ref="F51:O51" si="5">F44*(F50-1)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="76">
+      <c r="G51" s="66">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H51" s="76">
+      <c r="H51" s="66">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I51" s="76">
+      <c r="I51" s="66">
         <f t="shared" si="5"/>
         <v>8.8000283176270673E-4</v>
       </c>
-      <c r="J51" s="76">
+      <c r="J51" s="66">
         <f t="shared" si="5"/>
         <v>7.0329297413926854E-3</v>
       </c>
-      <c r="K51" s="62">
+      <c r="K51" s="53">
         <f t="shared" si="5"/>
         <v>6.9686528863348307E-3</v>
       </c>
-      <c r="L51" s="63">
+      <c r="L51" s="54">
         <f t="shared" si="5"/>
         <v>8.0697503976853574E-3</v>
       </c>
-      <c r="M51" s="63">
+      <c r="M51" s="54">
         <f t="shared" si="5"/>
         <v>8.5533717381329078E-3</v>
       </c>
-      <c r="N51" s="63">
+      <c r="N51" s="54">
         <f t="shared" si="5"/>
         <v>4.2957246787081573E-3</v>
       </c>
-      <c r="O51" s="63">
+      <c r="O51" s="54">
         <f t="shared" si="5"/>
         <v>5.0892694682403491E-4</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
+      <c r="A52" s="131"/>
       <c r="B52" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="102">
+      <c r="C52" s="92">
         <f>C51/(1+C51)</f>
         <v>2.7612335002223338E-2</v>
       </c>
-      <c r="D52" s="93">
+      <c r="D52" s="83">
         <f>D51/(1+D51)</f>
         <v>3.503718160775874E-2</v>
       </c>
-      <c r="E52" s="76"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="76"/>
-      <c r="H52" s="76"/>
-      <c r="I52" s="76"/>
-      <c r="J52" s="76"/>
-      <c r="K52" s="62"/>
-      <c r="L52" s="63"/>
-      <c r="M52" s="63"/>
-      <c r="N52" s="63"/>
-      <c r="O52" s="63"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="66"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="66"/>
+      <c r="J52" s="66"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="54"/>
+      <c r="M52" s="54"/>
+      <c r="N52" s="54"/>
+      <c r="O52" s="54"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="55"/>
+      <c r="A53" s="132"/>
       <c r="B53" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="C53" s="110">
+      <c r="C53" s="100">
         <f>0.0115708*C52*D42</f>
         <v>6644.3900174318323</v>
       </c>
-      <c r="D53" s="111">
+      <c r="D53" s="101">
         <f>0.0115708*D52*D42</f>
         <v>8431.0399571348571</v>
       </c>
-      <c r="E53" s="79"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
-      <c r="I53" s="79"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="69"/>
-      <c r="L53" s="70"/>
-      <c r="M53" s="70"/>
-      <c r="N53" s="70"/>
-      <c r="O53" s="70"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="60"/>
+      <c r="L53" s="61"/>
+      <c r="M53" s="61"/>
+      <c r="N53" s="61"/>
+      <c r="O53" s="61"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="53" t="s">
+      <c r="A54" s="130" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="101"/>
-      <c r="D54" s="92"/>
-      <c r="E54" s="77">
+      <c r="C54" s="91"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="67">
         <f>IF(E43&gt;$I$34, EXP((LN(1.062)/10)*(E43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="F54" s="77">
+      <c r="F54" s="67">
         <f t="shared" ref="F54:O54" si="6">IF(F43&gt;$I$34, EXP((LN(1.062)/10)*(F43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="G54" s="77">
+      <c r="G54" s="67">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="H54" s="77">
+      <c r="H54" s="67">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="I54" s="77">
+      <c r="I54" s="67">
         <f t="shared" si="6"/>
         <v>1.0121034455497457</v>
       </c>
-      <c r="J54" s="77">
+      <c r="J54" s="67">
         <f t="shared" si="6"/>
         <v>1.043006852485771</v>
       </c>
-      <c r="K54" s="65">
+      <c r="K54" s="56">
         <f t="shared" si="6"/>
         <v>1.0748538591738301</v>
       </c>
-      <c r="L54" s="66">
+      <c r="L54" s="57">
         <f t="shared" si="6"/>
         <v>1.1076732773398887</v>
       </c>
-      <c r="M54" s="66">
+      <c r="M54" s="57">
         <f t="shared" si="6"/>
         <v>1.1414947984426076</v>
       </c>
-      <c r="N54" s="66">
+      <c r="N54" s="57">
         <f t="shared" si="6"/>
         <v>1.1763490205349618</v>
       </c>
-      <c r="O54" s="66">
+      <c r="O54" s="57">
         <f t="shared" si="6"/>
         <v>1.2122674759460494</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="54"/>
+      <c r="A55" s="131"/>
       <c r="B55" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="102">
+      <c r="C55" s="92">
         <f>SUM(K55:O55)</f>
         <v>5.5756501106184665E-2</v>
       </c>
-      <c r="D55" s="93">
+      <c r="D55" s="83">
         <f>SUM(E55:O55)</f>
         <v>7.1008998307338034E-2</v>
       </c>
-      <c r="E55" s="76">
+      <c r="E55" s="66">
         <f>E44*(E54-1)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="76">
+      <c r="F55" s="66">
         <f t="shared" ref="F55:O55" si="7">F44*(F54-1)</f>
         <v>0</v>
       </c>
-      <c r="G55" s="76">
+      <c r="G55" s="66">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H55" s="76">
+      <c r="H55" s="66">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I55" s="76">
+      <c r="I55" s="66">
         <f t="shared" si="7"/>
         <v>1.6853970556822639E-3</v>
       </c>
-      <c r="J55" s="76">
+      <c r="J55" s="66">
         <f t="shared" si="7"/>
         <v>1.3567100145471106E-2</v>
       </c>
-      <c r="K55" s="62">
+      <c r="K55" s="53">
         <f t="shared" si="7"/>
         <v>1.3541162027583832E-2</v>
       </c>
-      <c r="L55" s="63">
+      <c r="L55" s="54">
         <f t="shared" si="7"/>
         <v>1.5796006680780964E-2</v>
       </c>
-      <c r="M55" s="63">
+      <c r="M55" s="54">
         <f t="shared" si="7"/>
         <v>1.6866633387219405E-2</v>
       </c>
-      <c r="N55" s="63">
+      <c r="N55" s="54">
         <f t="shared" si="7"/>
         <v>8.5340480462440024E-3</v>
       </c>
-      <c r="O55" s="63">
+      <c r="O55" s="54">
         <f t="shared" si="7"/>
         <v>1.0186509643564665E-3</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
+      <c r="A56" s="131"/>
       <c r="B56" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="102">
+      <c r="C56" s="92">
         <f>C55/(1+C55)</f>
         <v>5.2811894644044302E-2</v>
       </c>
-      <c r="D56" s="93">
+      <c r="D56" s="83">
         <f>D55/(1+D55)</f>
         <v>6.6301028674421281E-2</v>
       </c>
-      <c r="E56" s="76"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="76"/>
-      <c r="H56" s="76"/>
-      <c r="I56" s="76"/>
-      <c r="J56" s="76"/>
-      <c r="K56" s="62"/>
-      <c r="L56" s="63"/>
-      <c r="M56" s="63"/>
-      <c r="N56" s="63"/>
-      <c r="O56" s="63"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="66"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="55"/>
+      <c r="A57" s="132"/>
       <c r="B57" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C57" s="110">
+      <c r="C57" s="100">
         <f>0.0059261*C56*D42</f>
         <v>6508.6260538531606</v>
       </c>
-      <c r="D57" s="111">
+      <c r="D57" s="101">
         <f>0.0059261*D56*D42</f>
         <v>8171.0494489193279</v>
       </c>
-      <c r="E57" s="79"/>
-      <c r="F57" s="79"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
-      <c r="I57" s="79"/>
-      <c r="J57" s="79"/>
-      <c r="K57" s="69"/>
-      <c r="L57" s="70"/>
-      <c r="M57" s="70"/>
-      <c r="N57" s="70"/>
-      <c r="O57" s="70"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="60"/>
+      <c r="L57" s="61"/>
+      <c r="M57" s="61"/>
+      <c r="N57" s="61"/>
+      <c r="O57" s="61"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="53" t="s">
+      <c r="A58" s="130" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C58" s="104"/>
-      <c r="D58" s="100"/>
-      <c r="E58" s="77">
+      <c r="C58" s="94"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="67">
         <f>IF(E43&gt;$I$35, EXP((LN(1.08)/10)*(E43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="F58" s="77">
+      <c r="F58" s="67">
         <f t="shared" ref="F58:O58" si="8">IF(F43&gt;$I$35, EXP((LN(1.08)/10)*(F43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="G58" s="77">
+      <c r="G58" s="67">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="H58" s="77">
+      <c r="H58" s="67">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I58" s="77">
+      <c r="I58" s="67">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="J58" s="77">
+      <c r="J58" s="67">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K58" s="65">
+      <c r="K58" s="56">
         <f t="shared" si="8"/>
         <v>1.0312631565524872</v>
       </c>
-      <c r="L58" s="66">
+      <c r="L58" s="57">
         <f t="shared" si="8"/>
         <v>1.0717201098736591</v>
       </c>
-      <c r="M58" s="66">
+      <c r="M58" s="57">
         <f t="shared" si="8"/>
         <v>1.1137642090766864</v>
       </c>
-      <c r="N58" s="66">
+      <c r="N58" s="57">
         <f t="shared" si="8"/>
         <v>1.157457718663552</v>
       </c>
-      <c r="O58" s="66">
+      <c r="O58" s="57">
         <f t="shared" si="8"/>
         <v>1.2028653458028213</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="54"/>
+      <c r="A59" s="131"/>
       <c r="B59" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="105">
+      <c r="C59" s="95">
         <f>SUM(K59:O59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="D59" s="102">
+      <c r="D59" s="92">
         <f>SUM(E59:O59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="E59" s="76">
+      <c r="E59" s="66">
         <f>E44*(E58-1)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="76">
+      <c r="F59" s="66">
         <f t="shared" ref="F59:O59" si="9">F44*(F58-1)</f>
         <v>0</v>
       </c>
-      <c r="G59" s="76">
+      <c r="G59" s="66">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H59" s="76">
+      <c r="H59" s="66">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I59" s="76">
+      <c r="I59" s="66">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J59" s="76">
+      <c r="J59" s="66">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K59" s="62">
+      <c r="K59" s="53">
         <f t="shared" si="9"/>
         <v>5.6555463277831062E-3</v>
       </c>
-      <c r="L59" s="63">
+      <c r="L59" s="54">
         <f t="shared" si="9"/>
         <v>1.0521564520921027E-2</v>
       </c>
-      <c r="M59" s="63">
+      <c r="M59" s="54">
         <f t="shared" si="9"/>
         <v>1.3561058273543175E-2</v>
       </c>
-      <c r="N59" s="63">
+      <c r="N59" s="54">
         <f t="shared" si="9"/>
         <v>7.6198423572209177E-3</v>
       </c>
-      <c r="O59" s="63">
+      <c r="O59" s="54">
         <f t="shared" si="9"/>
         <v>9.7353105658576995E-4</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
+      <c r="A60" s="131"/>
       <c r="B60" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="105">
+      <c r="C60" s="95">
         <f>C59/(1+C59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="D60" s="102">
+      <c r="D60" s="92">
         <f>D59/(1+D59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="E60" s="76"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="63"/>
-      <c r="M60" s="63"/>
-      <c r="N60" s="63"/>
-      <c r="O60" s="63"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="66"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="66"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="54"/>
+      <c r="M60" s="54"/>
+      <c r="N60" s="54"/>
+      <c r="O60" s="54"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="55"/>
+      <c r="A61" s="132"/>
       <c r="B61" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="109">
+      <c r="C61" s="99">
         <f>0.00127695*C60*D42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="D61" s="110">
+      <c r="D61" s="100">
         <f>0.00127695*D60*D42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="69"/>
-      <c r="L61" s="70"/>
-      <c r="M61" s="70"/>
-      <c r="N61" s="70"/>
-      <c r="O61" s="70"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="60"/>
+      <c r="L61" s="61"/>
+      <c r="M61" s="61"/>
+      <c r="N61" s="61"/>
+      <c r="O61" s="61"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="114" t="s">
+      <c r="A62" s="128" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C62" s="106"/>
-      <c r="D62" s="95"/>
-      <c r="E62" s="80">
+      <c r="C62" s="96"/>
+      <c r="D62" s="85"/>
+      <c r="E62" s="70">
         <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="F62" s="80">
+      <c r="F62" s="70">
         <f t="shared" ref="F62:O62" si="10">IF(F43&gt;$I$30,((78.927 - 3.1162 * F43 + 0.0342 * F43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="G62" s="80">
+      <c r="G62" s="70">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H62" s="80">
+      <c r="H62" s="70">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I62" s="80">
+      <c r="I62" s="70">
         <f t="shared" si="10"/>
         <v>8.0134000000000191E-2</v>
       </c>
-      <c r="J62" s="80">
+      <c r="J62" s="70">
         <f t="shared" si="10"/>
         <v>9.3613999999999892E-2</v>
       </c>
-      <c r="K62" s="71">
+      <c r="K62" s="62">
         <f t="shared" si="10"/>
         <v>0.1241940000000001</v>
       </c>
-      <c r="L62" s="72">
+      <c r="L62" s="63">
         <f t="shared" si="10"/>
         <v>0.17187400000000011</v>
       </c>
-      <c r="M62" s="72">
+      <c r="M62" s="63">
         <f t="shared" si="10"/>
         <v>0.23665399999999978</v>
       </c>
-      <c r="N62" s="72">
+      <c r="N62" s="63">
         <f t="shared" si="10"/>
         <v>0.31853400000000021</v>
       </c>
-      <c r="O62" s="72">
+      <c r="O62" s="63">
         <f t="shared" si="10"/>
         <v>0.41751400000000016</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="115"/>
+      <c r="A63" s="129"/>
       <c r="B63" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="C63" s="106">
+      <c r="C63" s="96">
         <f>SUM(K63:O63)</f>
         <v>9.3309634085492005E-2</v>
       </c>
-      <c r="D63" s="95">
+      <c r="D63" s="85">
         <f>SUM(E63:O63)</f>
         <v>0.13400005972406637</v>
       </c>
-      <c r="E63" s="81">
+      <c r="E63" s="71">
         <f>E44*E62</f>
         <v>0</v>
       </c>
-      <c r="F63" s="81">
+      <c r="F63" s="71">
         <f t="shared" ref="F63:O63" si="11">F44*F62</f>
         <v>0</v>
       </c>
-      <c r="G63" s="81">
+      <c r="G63" s="71">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H63" s="81">
+      <c r="H63" s="71">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I63" s="81">
+      <c r="I63" s="71">
         <f t="shared" si="11"/>
         <v>1.1158608274391753E-2</v>
       </c>
-      <c r="J63" s="81">
+      <c r="J63" s="71">
         <f t="shared" si="11"/>
         <v>2.9531817364182603E-2</v>
       </c>
-      <c r="K63" s="62">
+      <c r="K63" s="53">
         <f t="shared" si="11"/>
         <v>2.2466858695265539E-2</v>
       </c>
-      <c r="L63" s="63">
+      <c r="L63" s="54">
         <f t="shared" si="11"/>
         <v>2.5214453570336123E-2</v>
       </c>
-      <c r="M63" s="63">
+      <c r="M63" s="54">
         <f t="shared" si="11"/>
         <v>2.8209915145665603E-2</v>
       </c>
-      <c r="N63" s="63">
+      <c r="N63" s="54">
         <f t="shared" si="11"/>
         <v>1.5414797610533706E-2</v>
       </c>
-      <c r="O63" s="63">
+      <c r="O63" s="54">
         <f t="shared" si="11"/>
         <v>2.0036090636910467E-3</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="116"/>
+      <c r="A64" s="127"/>
       <c r="B64" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="C64" s="99">
+      <c r="C64" s="89">
         <f>C63*$J$30*D42</f>
         <v>21345.5705628</v>
       </c>
-      <c r="D64" s="96">
+      <c r="D64" s="86">
         <f>J30*D63*D42</f>
         <v>30653.937916408569</v>
       </c>
@@ -3686,20 +3771,20 @@
       <c r="B66" s="23"/>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
-      <c r="E66" s="73" t="s">
+      <c r="E66" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="F66" s="73"/>
-      <c r="G66" s="73"/>
-      <c r="H66" s="73"/>
-      <c r="I66" s="73"/>
-      <c r="J66" s="56" t="s">
+      <c r="F66" s="123"/>
+      <c r="G66" s="123"/>
+      <c r="H66" s="123"/>
+      <c r="I66" s="123"/>
+      <c r="J66" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="K66" s="57"/>
-      <c r="L66" s="57"/>
-      <c r="M66" s="57"/>
-      <c r="N66" s="57"/>
+      <c r="K66" s="125"/>
+      <c r="L66" s="125"/>
+      <c r="M66" s="125"/>
+      <c r="N66" s="125"/>
       <c r="O66" s="24"/>
     </row>
     <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -3709,40 +3794,40 @@
       <c r="D67" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E67" s="74" t="s">
+      <c r="E67" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="F67" s="74" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="74" t="s">
+      <c r="G67" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="H67" s="74" t="s">
+      <c r="H67" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="I67" s="74" t="s">
+      <c r="I67" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="J67" s="58" t="s">
+      <c r="J67" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="K67" s="59" t="s">
+      <c r="K67" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="L67" s="59" t="s">
+      <c r="L67" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="M67" s="59" t="s">
+      <c r="M67" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="N67" s="59" t="s">
+      <c r="N67" s="50" t="s">
         <v>127</v>
       </c>
       <c r="O67" s="15"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="53" t="s">
+      <c r="A68" s="130" t="s">
         <v>102</v>
       </c>
       <c r="B68" s="18" t="s">
@@ -3753,131 +3838,131 @@
         <f>SUM(E68:N68)</f>
         <v>15021000</v>
       </c>
-      <c r="E68" s="82">
+      <c r="E68" s="72">
         <f>C14</f>
         <v>64582.789500000006</v>
       </c>
-      <c r="F68" s="82">
+      <c r="F68" s="72">
         <f>D14</f>
         <v>239111.78849999997</v>
       </c>
-      <c r="G68" s="82">
+      <c r="G68" s="72">
         <f>E14</f>
         <v>1126116.8595</v>
       </c>
-      <c r="H68" s="82">
+      <c r="H68" s="72">
         <f>F14</f>
         <v>2838600.9855</v>
       </c>
-      <c r="I68" s="82">
+      <c r="I68" s="72">
         <f>G14</f>
         <v>3242087.577</v>
       </c>
-      <c r="J68" s="89">
-        <f>Frontend!J15</f>
+      <c r="J68" s="79">
+        <f>Frontend!K15</f>
         <v>3383500</v>
       </c>
-      <c r="K68" s="86">
-        <f>Frontend!K15</f>
+      <c r="K68" s="76">
+        <f>Frontend!L15</f>
         <v>2682400</v>
       </c>
-      <c r="L68" s="86">
-        <f>Frontend!L15</f>
+      <c r="L68" s="76">
+        <f>Frontend!M15</f>
         <v>1283500</v>
       </c>
-      <c r="M68" s="86">
-        <f>Frontend!M15</f>
+      <c r="M68" s="76">
+        <f>Frontend!N15</f>
         <v>156200</v>
       </c>
-      <c r="N68" s="86">
-        <f>Frontend!N15</f>
+      <c r="N68" s="76">
+        <f>Frontend!O15</f>
         <v>4900</v>
       </c>
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="54"/>
+      <c r="A69" s="131"/>
       <c r="B69" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
-      <c r="E69" s="76">
+      <c r="E69" s="66">
         <v>27</v>
       </c>
-      <c r="F69" s="76">
+      <c r="F69" s="66">
         <v>32</v>
       </c>
-      <c r="G69" s="76">
+      <c r="G69" s="66">
         <v>37</v>
       </c>
-      <c r="H69" s="76">
+      <c r="H69" s="66">
         <v>42</v>
       </c>
-      <c r="I69" s="76">
+      <c r="I69" s="66">
         <v>47</v>
       </c>
-      <c r="J69" s="62">
+      <c r="J69" s="53">
         <v>52</v>
       </c>
-      <c r="K69" s="63">
+      <c r="K69" s="54">
         <v>57</v>
       </c>
-      <c r="L69" s="63">
+      <c r="L69" s="54">
         <v>62</v>
       </c>
-      <c r="M69" s="63">
+      <c r="M69" s="54">
         <v>67</v>
       </c>
-      <c r="N69" s="64">
+      <c r="N69" s="55">
         <v>72</v>
       </c>
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="55"/>
+      <c r="A70" s="132"/>
       <c r="B70" s="19" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="26"/>
-      <c r="E70" s="83">
+      <c r="E70" s="73">
         <f>E68/$D$68</f>
         <v>4.2995000000000004E-3</v>
       </c>
-      <c r="F70" s="83">
+      <c r="F70" s="73">
         <f t="shared" ref="F70:N70" si="12">F68/$D$68</f>
         <v>1.5918499999999999E-2</v>
       </c>
-      <c r="G70" s="83">
+      <c r="G70" s="73">
         <f t="shared" si="12"/>
         <v>7.4969499999999994E-2</v>
       </c>
-      <c r="H70" s="83">
+      <c r="H70" s="73">
         <f t="shared" si="12"/>
         <v>0.18897549999999999</v>
       </c>
-      <c r="I70" s="83">
+      <c r="I70" s="73">
         <f t="shared" si="12"/>
         <v>0.215837</v>
       </c>
-      <c r="J70" s="90">
+      <c r="J70" s="80">
         <f t="shared" si="12"/>
         <v>0.2252513148259104</v>
       </c>
-      <c r="K70" s="87">
+      <c r="K70" s="77">
         <f t="shared" si="12"/>
         <v>0.17857665934358566</v>
       </c>
-      <c r="L70" s="87">
+      <c r="L70" s="77">
         <f t="shared" si="12"/>
         <v>8.5447040809533317E-2</v>
       </c>
-      <c r="M70" s="87">
+      <c r="M70" s="77">
         <f t="shared" si="12"/>
         <v>1.0398775048265762E-2</v>
       </c>
-      <c r="N70" s="87">
+      <c r="N70" s="77">
         <f t="shared" si="12"/>
         <v>3.2620997270487985E-4</v>
       </c>
@@ -3888,138 +3973,138 @@
         <v>103</v>
       </c>
       <c r="B71" s="32"/>
-      <c r="C71" s="97" t="s">
+      <c r="C71" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="D71" s="107" t="s">
+      <c r="D71" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="E71" s="84"/>
-      <c r="F71" s="84"/>
-      <c r="G71" s="84"/>
-      <c r="H71" s="84"/>
-      <c r="I71" s="84"/>
-      <c r="J71" s="91"/>
-      <c r="K71" s="88"/>
-      <c r="L71" s="88"/>
-      <c r="M71" s="88"/>
-      <c r="N71" s="88"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="81"/>
+      <c r="K71" s="78"/>
+      <c r="L71" s="78"/>
+      <c r="M71" s="78"/>
+      <c r="N71" s="78"/>
       <c r="O71" s="15"/>
     </row>
     <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="117" t="s">
+      <c r="A72" s="126" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C72" s="98"/>
-      <c r="D72" s="108"/>
-      <c r="E72" s="85">
+      <c r="C72" s="88"/>
+      <c r="D72" s="98"/>
+      <c r="E72" s="75">
         <f>IF(E69&gt;$I$31,((19.4312 - 0.9336 *  E69 + 0.0126 *  E69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="F72" s="85">
+      <c r="F72" s="75">
         <f t="shared" ref="F72:N72" si="13">IF(F69&gt;$I$31,((19.4312 - 0.9336 *  F69 + 0.0126 *  F69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="G72" s="85">
+      <c r="G72" s="75">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H72" s="85">
+      <c r="H72" s="75">
         <f t="shared" si="13"/>
         <v>2.4464000000000041E-2</v>
       </c>
-      <c r="I72" s="85">
+      <c r="I72" s="75">
         <f t="shared" si="13"/>
         <v>3.3854000000000044E-2</v>
       </c>
-      <c r="J72" s="67">
+      <c r="J72" s="58">
         <f t="shared" si="13"/>
         <v>4.9544000000000032E-2</v>
       </c>
-      <c r="K72" s="68">
+      <c r="K72" s="59">
         <f t="shared" si="13"/>
         <v>7.1534000000000125E-2</v>
       </c>
-      <c r="L72" s="68">
+      <c r="L72" s="59">
         <f t="shared" si="13"/>
         <v>9.9824000000000052E-2</v>
       </c>
-      <c r="M72" s="68">
+      <c r="M72" s="59">
         <f t="shared" si="13"/>
         <v>0.13441399999999995</v>
       </c>
-      <c r="N72" s="68">
+      <c r="N72" s="59">
         <f t="shared" si="13"/>
         <v>0.17530400000000002</v>
       </c>
     </row>
     <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="117"/>
+      <c r="A73" s="126"/>
       <c r="B73" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="C73" s="98">
+      <c r="C73" s="88">
         <f>SUM(J73:N73)</f>
         <v>3.3918746155382498E-2</v>
       </c>
-      <c r="D73" s="108">
+      <c r="D73" s="98">
         <f>SUM(E73:N73)</f>
         <v>4.5848788585382522E-2</v>
       </c>
-      <c r="E73" s="85">
+      <c r="E73" s="75">
         <f>E72*E70</f>
         <v>0</v>
       </c>
-      <c r="F73" s="85">
+      <c r="F73" s="75">
         <f t="shared" ref="F73:N73" si="14">F72*F70</f>
         <v>0</v>
       </c>
-      <c r="G73" s="85">
+      <c r="G73" s="75">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H73" s="85">
+      <c r="H73" s="75">
         <f t="shared" si="14"/>
         <v>4.6230966320000072E-3</v>
       </c>
-      <c r="I73" s="85">
+      <c r="I73" s="75">
         <f t="shared" si="14"/>
         <v>7.3069457980000094E-3</v>
       </c>
-      <c r="J73" s="67">
+      <c r="J73" s="58">
         <f t="shared" si="14"/>
         <v>1.1159851141734912E-2</v>
       </c>
-      <c r="K73" s="68">
+      <c r="K73" s="59">
         <f t="shared" si="14"/>
         <v>1.2774302749484078E-2</v>
       </c>
-      <c r="L73" s="68">
+      <c r="L73" s="59">
         <f t="shared" si="14"/>
         <v>8.5296654017708584E-3</v>
       </c>
-      <c r="M73" s="68">
+      <c r="M73" s="59">
         <f t="shared" si="14"/>
         <v>1.3977409493375935E-3</v>
       </c>
-      <c r="N73" s="68">
+      <c r="N73" s="59">
         <f t="shared" si="14"/>
         <v>5.718591305505626E-5</v>
       </c>
     </row>
     <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="116"/>
+      <c r="A74" s="127"/>
       <c r="B74" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="C74" s="99">
+      <c r="C74" s="89">
         <f>J31*C73*D68</f>
         <v>5094.9348600000048</v>
       </c>
-      <c r="D74" s="96">
+      <c r="D74" s="86">
         <f>J31*D73*D68</f>
         <v>6886.9465334103088</v>
       </c>
@@ -4092,29 +4177,37 @@
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="33" t="s">
-        <v>151</v>
+      <c r="B82" s="133" t="s">
+        <v>153</v>
       </c>
       <c r="C82" s="40">
-        <f>C79/D42*100000</f>
-        <v>131.85374189567494</v>
+        <f>(C79/C85)*100000</f>
+        <v>106.86035636315063</v>
       </c>
       <c r="D82" s="40">
-        <f>D79/D42*100000</f>
-        <v>1484.035668671215</v>
+        <f>(D79/C85)*100000</f>
+        <v>1202.730981539436</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B83" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C83" s="45">
-        <f>C80/D42*100000</f>
-        <v>9229761.9326972459</v>
-      </c>
-      <c r="D83" s="45">
-        <f>D80/D42*100000</f>
-        <v>103882496.80698505</v>
+      <c r="B83" s="133" t="s">
+        <v>154</v>
+      </c>
+      <c r="C83" s="134">
+        <f>C80/C85*100000</f>
+        <v>7480224.9454205437</v>
+      </c>
+      <c r="D83" s="134">
+        <f>(D80/C85)*100000</f>
+        <v>84191168.707760513</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B85" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C85" s="8">
+        <v>25660460</v>
       </c>
     </row>
   </sheetData>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -5,26 +5,26 @@
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\LÄRM Projekte\Quantifizierung von Lärmschadenskosten\GitHub Repository\Hessen_END_Healthiar\Lärmschadenstool_EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEB5DC1-4A20-4A20-BB0B-3731B1B2A70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC11835-95AE-4FCD-86BD-294E2959B9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
     <sheet name="Frontend" sheetId="8" r:id="rId2"/>
-    <sheet name="Agglomeration road" sheetId="1" r:id="rId3"/>
-    <sheet name="Fragen" sheetId="11" r:id="rId4"/>
-    <sheet name="ERF HRA" sheetId="10" r:id="rId5"/>
-    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId6"/>
+    <sheet name="Frontend DEMO DAGA" sheetId="13" r:id="rId3"/>
+    <sheet name="Agglomeration road" sheetId="1" r:id="rId4"/>
+    <sheet name="Fragen" sheetId="11" r:id="rId5"/>
+    <sheet name="ERF HRA" sheetId="10" r:id="rId6"/>
     <sheet name="Agglomeration rail" sheetId="2" r:id="rId7"/>
     <sheet name="Agglomeration air" sheetId="3" r:id="rId8"/>
-    <sheet name="Agglomeration industry" sheetId="4" r:id="rId9"/>
-    <sheet name="Major roads " sheetId="5" r:id="rId10"/>
-    <sheet name="Major railways " sheetId="6" r:id="rId11"/>
-    <sheet name="Major airports" sheetId="7" r:id="rId12"/>
+    <sheet name="Major roads " sheetId="5" r:id="rId9"/>
+    <sheet name="Major railways " sheetId="6" r:id="rId10"/>
+    <sheet name="Major airports" sheetId="7" r:id="rId11"/>
+    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="158">
   <si>
     <t>L_den</t>
   </si>
@@ -350,9 +350,6 @@
     <t>aggroad number exposed</t>
   </si>
   <si>
-    <t>Anzahl belasteter Personen nach ULR (EN: END)</t>
-  </si>
-  <si>
     <t>threshold in dB</t>
   </si>
   <si>
@@ -499,9 +496,6 @@
   </si>
   <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1 DALY = 70.000 EUR</t>
   </si>
   <si>
     <t>HA/ HSD</t>
@@ -598,10 +592,22 @@
     <t>DALY pro 100.000 = (DALY / Population in Ballungsraum) * 100k</t>
   </si>
   <si>
-    <t>EURO pro 100.000 = (EURO / Population in Ballungsraum) * 100k</t>
-  </si>
-  <si>
     <t>Population in Ballungsräumen Deutschland</t>
+  </si>
+  <si>
+    <t>EURO pro Person = EURO Ballungsraum / Population in Ballungsraum</t>
+  </si>
+  <si>
+    <t>1 DALY =</t>
+  </si>
+  <si>
+    <t>Anzahl belasteter Personen nach ULR</t>
+  </si>
+  <si>
+    <t>- tba -</t>
+  </si>
+  <si>
+    <t>END Model + Imputation</t>
   </si>
 </sst>
 </file>
@@ -931,7 +937,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1115,7 +1121,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1159,10 +1168,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1642,16 +1668,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
-  <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1"/>
@@ -1661,7 +1677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1"/>
@@ -1671,14 +1687,37 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.7109375" customWidth="1"/>
   </cols>
@@ -1700,15 +1739,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1717,78 +1756,78 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="120" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="120"/>
+      <c r="A10" s="121" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="121"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" s="122" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="K12" s="118" t="s">
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="K12" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="118"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="119"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="110"/>
       <c r="B13" s="110"/>
       <c r="D13" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="104" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="F13" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="G13" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="H13" s="104" t="s">
         <v>121</v>
-      </c>
-      <c r="H13" s="104" t="s">
-        <v>122</v>
       </c>
       <c r="I13" s="105" t="s">
         <v>76</v>
       </c>
       <c r="K13" s="107" t="s">
+        <v>122</v>
+      </c>
+      <c r="L13" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="L13" s="107" t="s">
+      <c r="M13" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="M13" s="107" t="s">
+      <c r="N13" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="N13" s="107" t="s">
+      <c r="O13" s="107" t="s">
         <v>126</v>
-      </c>
-      <c r="O13" s="107" t="s">
-        <v>127</v>
       </c>
       <c r="P13" s="108" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="121" t="s">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="122" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="110" t="s">
@@ -1834,53 +1873,53 @@
         <v>4286500</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121"/>
-      <c r="B15" s="111" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="122"/>
+      <c r="B15" s="134" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="113">
+      <c r="C15" s="15"/>
+      <c r="D15" s="135">
         <v>3762100</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="135">
         <v>3050900</v>
       </c>
-      <c r="F15" s="117">
+      <c r="F15" s="135">
         <v>2479000</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="135">
         <v>1006400</v>
       </c>
-      <c r="H15" s="113">
+      <c r="H15" s="135">
         <v>99800</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="135">
         <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
         <v>10398200</v>
       </c>
-      <c r="J15" s="114"/>
-      <c r="K15" s="115">
+      <c r="J15" s="136"/>
+      <c r="K15" s="137">
         <v>3383500</v>
       </c>
-      <c r="L15" s="115">
+      <c r="L15" s="137">
         <v>2682400</v>
       </c>
-      <c r="M15" s="115">
+      <c r="M15" s="137">
         <v>1283500</v>
       </c>
-      <c r="N15" s="115">
+      <c r="N15" s="137">
         <v>156200</v>
       </c>
-      <c r="O15" s="115">
+      <c r="O15" s="137">
         <v>4900</v>
       </c>
-      <c r="P15" s="116">
+      <c r="P15" s="137">
         <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
         <v>7510500</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="110"/>
       <c r="B16" s="110"/>
       <c r="D16" s="106"/>
@@ -1915,7 +1954,7 @@
       <c r="P17" s="109"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="121" t="s">
+      <c r="A18" s="122" t="s">
         <v>78</v>
       </c>
       <c r="B18" s="110" t="s">
@@ -1962,7 +2001,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="121"/>
+      <c r="A19" s="122"/>
       <c r="B19" s="110" t="s">
         <v>80</v>
       </c>
@@ -2026,7 +2065,7 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="110"/>
       <c r="B21" s="110"/>
-      <c r="D21" s="106"/>
+      <c r="D21" s="138"/>
       <c r="E21" s="106"/>
       <c r="F21" s="106"/>
       <c r="G21" s="106"/>
@@ -2041,7 +2080,7 @@
       <c r="P21" s="109"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="121" t="s">
+      <c r="A22" s="122" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="110" t="s">
@@ -2088,7 +2127,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="121"/>
+      <c r="A23" s="122"/>
       <c r="B23" s="110" t="s">
         <v>83</v>
       </c>
@@ -2139,67 +2178,81 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="120" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="120"/>
+      <c r="A32" s="121" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="121"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
+      <c r="B34" s="110"/>
+      <c r="C34" s="106" t="s">
         <v>73</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="109" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+      <c r="B35" s="110" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="106">
+        <f>I15</f>
+        <v>10398200</v>
+      </c>
+      <c r="D35" s="109">
+        <f>P15</f>
+        <v>7510500</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C36" s="106">
         <f>'Agglomeration road'!C18</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D36" s="109">
         <f>'Agglomeration road'!C19</f>
         <v>15021000</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-    </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>137</v>
-      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="33" t="s">
+      <c r="C38" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="34">
+      <c r="D38" s="85" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="139">
         <f>'Agglomeration road'!C79</f>
         <v>27420.859000423719</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D39" s="141">
         <f>'Agglomeration road'!D79</f>
         <v>308626.30242553435</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="45">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="140">
         <f>'Agglomeration road'!C80</f>
         <v>1919460130.0296605</v>
       </c>
-      <c r="D39" s="45">
+      <c r="D40" s="142">
         <f>'Agglomeration road'!D80</f>
         <v>21603841169.787403</v>
       </c>
@@ -2221,9 +2274,568 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCA578C-B553-47BE-9A2E-931A94425EB8}">
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="121" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="121"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="110" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="123" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="K12" s="119" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="119"/>
+    </row>
+    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="110"/>
+      <c r="B13" s="110"/>
+      <c r="D13" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="104" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="104" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" s="104" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="104" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="105" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="107" t="s">
+        <v>122</v>
+      </c>
+      <c r="L13" s="107" t="s">
+        <v>123</v>
+      </c>
+      <c r="M13" s="107" t="s">
+        <v>124</v>
+      </c>
+      <c r="N13" s="107" t="s">
+        <v>125</v>
+      </c>
+      <c r="O13" s="107" t="s">
+        <v>126</v>
+      </c>
+      <c r="P13" s="108" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="122" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="106">
+        <v>3725500</v>
+      </c>
+      <c r="E14" s="106">
+        <v>1643600</v>
+      </c>
+      <c r="F14" s="106">
+        <v>998600</v>
+      </c>
+      <c r="G14" s="106">
+        <v>481900</v>
+      </c>
+      <c r="H14" s="106">
+        <v>33500</v>
+      </c>
+      <c r="I14" s="106">
+        <f>SUM(D14:H14)</f>
+        <v>6883100</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="109">
+        <v>2411700</v>
+      </c>
+      <c r="L14" s="109">
+        <v>1244300</v>
+      </c>
+      <c r="M14" s="109">
+        <v>574000</v>
+      </c>
+      <c r="N14" s="109">
+        <v>54400</v>
+      </c>
+      <c r="O14" s="109">
+        <v>2100</v>
+      </c>
+      <c r="P14" s="109">
+        <f>SUM(K14:O14)</f>
+        <v>4286500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="122"/>
+      <c r="B15" s="111" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="112"/>
+      <c r="D15" s="113">
+        <v>3762100</v>
+      </c>
+      <c r="E15" s="113">
+        <v>3050900</v>
+      </c>
+      <c r="F15" s="113">
+        <v>2479000</v>
+      </c>
+      <c r="G15" s="113">
+        <v>1006400</v>
+      </c>
+      <c r="H15" s="113">
+        <v>99800</v>
+      </c>
+      <c r="I15" s="113">
+        <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
+        <v>10398200</v>
+      </c>
+      <c r="J15" s="114"/>
+      <c r="K15" s="115">
+        <v>3383500</v>
+      </c>
+      <c r="L15" s="115">
+        <v>2682400</v>
+      </c>
+      <c r="M15" s="115">
+        <v>1283500</v>
+      </c>
+      <c r="N15" s="115">
+        <v>156200</v>
+      </c>
+      <c r="O15" s="115">
+        <v>4900</v>
+      </c>
+      <c r="P15" s="116">
+        <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
+        <v>7510500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="110"/>
+      <c r="B16" s="110"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="109"/>
+      <c r="M16" s="109"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="109"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="110"/>
+      <c r="B17" s="110"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="109"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="122" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="110" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="106">
+        <v>716500</v>
+      </c>
+      <c r="E18" s="106">
+        <v>340700</v>
+      </c>
+      <c r="F18" s="106">
+        <v>141700</v>
+      </c>
+      <c r="G18" s="106">
+        <v>36000</v>
+      </c>
+      <c r="H18" s="106">
+        <v>4600</v>
+      </c>
+      <c r="I18" s="106">
+        <f t="shared" si="0"/>
+        <v>1239500</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="109">
+        <v>568900</v>
+      </c>
+      <c r="L18" s="109">
+        <v>258600</v>
+      </c>
+      <c r="M18" s="109">
+        <v>93100</v>
+      </c>
+      <c r="N18" s="109">
+        <v>21100</v>
+      </c>
+      <c r="O18" s="109">
+        <v>2200</v>
+      </c>
+      <c r="P18" s="109">
+        <f t="shared" si="1"/>
+        <v>943900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="122"/>
+      <c r="B19" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="106">
+        <v>1289300</v>
+      </c>
+      <c r="E19" s="106">
+        <v>787600</v>
+      </c>
+      <c r="F19" s="106">
+        <v>383200</v>
+      </c>
+      <c r="G19" s="106">
+        <v>74300</v>
+      </c>
+      <c r="H19" s="106">
+        <v>13200</v>
+      </c>
+      <c r="I19" s="106">
+        <f t="shared" si="0"/>
+        <v>2547600</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="109">
+        <v>1058400</v>
+      </c>
+      <c r="L19" s="109">
+        <v>609100</v>
+      </c>
+      <c r="M19" s="109">
+        <v>175500</v>
+      </c>
+      <c r="N19" s="109">
+        <v>32000</v>
+      </c>
+      <c r="O19" s="109">
+        <v>7700</v>
+      </c>
+      <c r="P19" s="109">
+        <f t="shared" si="1"/>
+        <v>1882700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="110"/>
+      <c r="B20" s="110"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="109"/>
+      <c r="P20" s="109"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="110"/>
+      <c r="B21" s="110"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="122" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="110" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="106">
+        <v>303900</v>
+      </c>
+      <c r="E22" s="106">
+        <v>69900</v>
+      </c>
+      <c r="F22" s="106">
+        <v>3900</v>
+      </c>
+      <c r="G22" s="106">
+        <v>0</v>
+      </c>
+      <c r="H22" s="106">
+        <v>0</v>
+      </c>
+      <c r="I22" s="106">
+        <f t="shared" si="0"/>
+        <v>377700</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="109">
+        <v>123200</v>
+      </c>
+      <c r="L22" s="109">
+        <v>17600</v>
+      </c>
+      <c r="M22" s="109">
+        <v>400</v>
+      </c>
+      <c r="N22" s="109">
+        <v>0</v>
+      </c>
+      <c r="O22" s="109">
+        <v>0</v>
+      </c>
+      <c r="P22" s="109">
+        <f t="shared" si="1"/>
+        <v>141200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="122"/>
+      <c r="B23" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="106">
+        <v>419800</v>
+      </c>
+      <c r="E23" s="106">
+        <v>51900</v>
+      </c>
+      <c r="F23" s="106">
+        <v>3000</v>
+      </c>
+      <c r="G23" s="106">
+        <v>700</v>
+      </c>
+      <c r="H23" s="106">
+        <v>0</v>
+      </c>
+      <c r="I23" s="106">
+        <f t="shared" si="0"/>
+        <v>475400</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="109">
+        <v>121500</v>
+      </c>
+      <c r="L23" s="109">
+        <v>10900</v>
+      </c>
+      <c r="M23" s="109">
+        <v>400</v>
+      </c>
+      <c r="N23" s="109">
+        <v>0</v>
+      </c>
+      <c r="O23" s="109">
+        <v>0</v>
+      </c>
+      <c r="P23" s="109">
+        <f t="shared" si="1"/>
+        <v>132800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="121" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="121"/>
+    </row>
+    <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="110"/>
+      <c r="C34" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="109" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="110" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="106">
+        <f>I15</f>
+        <v>10398200</v>
+      </c>
+      <c r="D35" s="109">
+        <f>P15</f>
+        <v>7510500</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="106">
+        <f>'Agglomeration road'!C18</f>
+        <v>20796420.796399999</v>
+      </c>
+      <c r="D36" s="109">
+        <f>'Agglomeration road'!C19</f>
+        <v>15021000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C38" s="96" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="85" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="143" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="144" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="145" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="146" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -2340,22 +2952,22 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>75</v>
@@ -2494,7 +3106,7 @@
         <v>41</v>
       </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s">
         <v>43</v>
@@ -2511,7 +3123,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -2549,7 +3161,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -2622,7 +3234,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -2692,7 +3304,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -2727,69 +3339,69 @@
     </row>
     <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
-      <c r="E40" s="123" t="s">
-        <v>92</v>
-      </c>
-      <c r="F40" s="123"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="123"/>
-      <c r="I40" s="123"/>
-      <c r="J40" s="123"/>
-      <c r="K40" s="124" t="s">
+      <c r="E40" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="L40" s="125"/>
-      <c r="M40" s="125"/>
-      <c r="N40" s="125"/>
-      <c r="O40" s="125"/>
+      <c r="F40" s="124"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="124"/>
+      <c r="J40" s="124"/>
+      <c r="K40" s="125" t="s">
+        <v>90</v>
+      </c>
+      <c r="L40" s="126"/>
+      <c r="M40" s="126"/>
+      <c r="N40" s="126"/>
+      <c r="O40" s="126"/>
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E41" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="H41" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="G41" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="H41" s="64" t="s">
+      <c r="I41" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="J41" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="K41" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="K41" s="49" t="s">
+      <c r="L41" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="L41" s="50" t="s">
+      <c r="M41" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="M41" s="50" t="s">
+      <c r="N41" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="N41" s="50" t="s">
+      <c r="O41" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="O41" s="50" t="s">
-        <v>122</v>
-      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="130" t="s">
-        <v>102</v>
+      <c r="A42" s="131" t="s">
+        <v>101</v>
       </c>
       <c r="B42" s="43" t="s">
         <v>85</v>
@@ -2850,9 +3462,9 @@
       <c r="U42" s="8"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="131"/>
+      <c r="A43" s="132"/>
       <c r="B43" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -2891,9 +3503,9 @@
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="132"/>
+      <c r="A44" s="133"/>
       <c r="B44" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -2944,13 +3556,13 @@
     </row>
     <row r="45" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" s="82" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E45" s="67"/>
       <c r="F45" s="67"/>
@@ -2965,11 +3577,11 @@
       <c r="O45" s="57"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="130" t="s">
+      <c r="A46" s="131" t="s">
         <v>57</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C46" s="91"/>
       <c r="D46" s="82"/>
@@ -3019,9 +3631,9 @@
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="131"/>
+      <c r="A47" s="132"/>
       <c r="B47" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" s="92">
         <f>SUM(K47:O47)</f>
@@ -3077,9 +3689,9 @@
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="131"/>
+      <c r="A48" s="132"/>
       <c r="B48" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C48" s="92">
         <f>(C47)/(1+C47)</f>
@@ -3102,9 +3714,9 @@
       <c r="O48" s="54"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="132"/>
+      <c r="A49" s="133"/>
       <c r="B49" s="42" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" s="103">
         <f>0.2069215*C48*D42</f>
@@ -3127,11 +3739,11 @@
       <c r="O49" s="61"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="130" t="s">
+      <c r="A50" s="131" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50" s="91"/>
       <c r="D50" s="82"/>
@@ -3181,9 +3793,9 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="131"/>
+      <c r="A51" s="132"/>
       <c r="B51" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C51" s="92">
         <f>SUM(K51:O51)</f>
@@ -3239,9 +3851,9 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="131"/>
+      <c r="A52" s="132"/>
       <c r="B52" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52" s="92">
         <f>C51/(1+C51)</f>
@@ -3264,9 +3876,9 @@
       <c r="O52" s="54"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="132"/>
+      <c r="A53" s="133"/>
       <c r="B53" s="42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C53" s="100">
         <f>0.0115708*C52*D42</f>
@@ -3289,11 +3901,11 @@
       <c r="O53" s="61"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="130" t="s">
+      <c r="A54" s="131" t="s">
         <v>65</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="91"/>
       <c r="D54" s="82"/>
@@ -3343,9 +3955,9 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="131"/>
+      <c r="A55" s="132"/>
       <c r="B55" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C55" s="92">
         <f>SUM(K55:O55)</f>
@@ -3401,9 +4013,9 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="131"/>
+      <c r="A56" s="132"/>
       <c r="B56" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C56" s="92">
         <f>C55/(1+C55)</f>
@@ -3426,9 +4038,9 @@
       <c r="O56" s="54"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="132"/>
+      <c r="A57" s="133"/>
       <c r="B57" s="42" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C57" s="100">
         <f>0.0059261*C56*D42</f>
@@ -3451,11 +4063,11 @@
       <c r="O57" s="61"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="130" t="s">
+      <c r="A58" s="131" t="s">
         <v>69</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C58" s="94"/>
       <c r="D58" s="90"/>
@@ -3505,9 +4117,9 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="131"/>
+      <c r="A59" s="132"/>
       <c r="B59" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="95">
         <f>SUM(K59:O59)</f>
@@ -3563,9 +4175,9 @@
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="131"/>
+      <c r="A60" s="132"/>
       <c r="B60" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C60" s="95">
         <f>C59/(1+C59)</f>
@@ -3588,9 +4200,9 @@
       <c r="O60" s="54"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="132"/>
+      <c r="A61" s="133"/>
       <c r="B61" s="42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C61" s="99">
         <f>0.00127695*C60*D42</f>
@@ -3613,11 +4225,11 @@
       <c r="O61" s="61"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="128" t="s">
+      <c r="A62" s="129" t="s">
         <v>45</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C62" s="96"/>
       <c r="D62" s="85"/>
@@ -3667,9 +4279,9 @@
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="129"/>
+      <c r="A63" s="130"/>
       <c r="B63" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C63" s="96">
         <f>SUM(K63:O63)</f>
@@ -3725,9 +4337,9 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="127"/>
+      <c r="A64" s="128"/>
       <c r="B64" s="44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C64" s="89">
         <f>C63*$J$30*D42</f>
@@ -3771,20 +4383,20 @@
       <c r="B66" s="23"/>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
-      <c r="E66" s="123" t="s">
+      <c r="E66" s="124" t="s">
+        <v>92</v>
+      </c>
+      <c r="F66" s="124"/>
+      <c r="G66" s="124"/>
+      <c r="H66" s="124"/>
+      <c r="I66" s="124"/>
+      <c r="J66" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="F66" s="123"/>
-      <c r="G66" s="123"/>
-      <c r="H66" s="123"/>
-      <c r="I66" s="123"/>
-      <c r="J66" s="124" t="s">
-        <v>94</v>
-      </c>
-      <c r="K66" s="125"/>
-      <c r="L66" s="125"/>
-      <c r="M66" s="125"/>
-      <c r="N66" s="125"/>
+      <c r="K66" s="126"/>
+      <c r="L66" s="126"/>
+      <c r="M66" s="126"/>
+      <c r="N66" s="126"/>
       <c r="O66" s="24"/>
     </row>
     <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -3792,43 +4404,43 @@
       <c r="B67" s="23"/>
       <c r="C67" s="23"/>
       <c r="D67" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E67" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="F67" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="G67" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="H67" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="F67" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="G67" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="H67" s="64" t="s">
+      <c r="I67" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="I67" s="64" t="s">
-        <v>116</v>
-      </c>
       <c r="J67" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="K67" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="K67" s="50" t="s">
+      <c r="L67" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="L67" s="50" t="s">
+      <c r="M67" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="M67" s="50" t="s">
+      <c r="N67" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="N67" s="50" t="s">
-        <v>127</v>
-      </c>
       <c r="O67" s="15"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="130" t="s">
-        <v>102</v>
+      <c r="A68" s="131" t="s">
+        <v>101</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>85</v>
@@ -3881,9 +4493,9 @@
       <c r="O68" s="15"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="131"/>
+      <c r="A69" s="132"/>
       <c r="B69" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
@@ -3920,9 +4532,9 @@
       <c r="O69" s="15"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="132"/>
+      <c r="A70" s="133"/>
       <c r="B70" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="26"/>
@@ -3970,14 +4582,14 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="87" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="97" t="s">
         <v>100</v>
-      </c>
-      <c r="D71" s="97" t="s">
-        <v>101</v>
       </c>
       <c r="E71" s="74"/>
       <c r="F71" s="74"/>
@@ -3992,11 +4604,11 @@
       <c r="O71" s="15"/>
     </row>
     <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="126" t="s">
+      <c r="A72" s="127" t="s">
         <v>53</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C72" s="88"/>
       <c r="D72" s="98"/>
@@ -4042,9 +4654,9 @@
       </c>
     </row>
     <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="126"/>
+      <c r="A73" s="127"/>
       <c r="B73" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C73" s="88">
         <f>SUM(J73:N73)</f>
@@ -4096,9 +4708,9 @@
       </c>
     </row>
     <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="127"/>
+      <c r="A74" s="128"/>
       <c r="B74" s="44" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C74" s="89">
         <f>J31*C73*D68</f>
@@ -4122,26 +4734,26 @@
     </row>
     <row r="77" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E78" t="s">
-        <v>106</v>
-      </c>
-      <c r="F78" t="s">
-        <v>138</v>
+        <v>105</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B79" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C79" s="40">
         <f>C61+C64+C74</f>
@@ -4158,57 +4770,72 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B80" s="33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C80" s="41">
-        <f>C79*70000</f>
+        <f>C79*C86</f>
         <v>1919460130.0296605</v>
       </c>
       <c r="D80" s="41">
-        <f>D79*70000</f>
+        <f>D79*C86</f>
         <v>21603841169.787403</v>
       </c>
       <c r="E80" s="35">
         <f>D80-C80</f>
         <v>19684381039.757744</v>
       </c>
-      <c r="F80" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="133" t="s">
+      <c r="B82" s="117" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" s="40">
+        <f>(C79/C87)*100000</f>
+        <v>106.86035636315063</v>
+      </c>
+      <c r="D82" s="40">
+        <f>(D79/C87)*100000</f>
+        <v>1202.730981539436</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B83" s="117" t="s">
         <v>153</v>
       </c>
-      <c r="C82" s="40">
-        <f>(C79/C85)*100000</f>
-        <v>106.86035636315063</v>
-      </c>
-      <c r="D82" s="40">
-        <f>(D79/C85)*100000</f>
-        <v>1202.730981539436</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B83" s="133" t="s">
-        <v>154</v>
-      </c>
-      <c r="C83" s="134">
-        <f>C80/C85*100000</f>
-        <v>7480224.9454205437</v>
-      </c>
-      <c r="D83" s="134">
-        <f>(D80/C85)*100000</f>
-        <v>84191168.707760513</v>
+      <c r="C83" s="118">
+        <f>C80/C87</f>
+        <v>74.802249454205437</v>
+      </c>
+      <c r="D83" s="118">
+        <f>(D80/C87)</f>
+        <v>841.91168707760517</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C85" s="8">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B86" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" s="118">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B87" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C87" s="8">
         <v>25660460</v>
       </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B88" s="33"/>
+      <c r="C88" s="45"/>
+      <c r="D88" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4230,7 +4857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4241,13 +4868,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4255,10 +4882,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -4266,10 +4893,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -4277,10 +4904,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4288,10 +4915,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,10 +4926,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4310,35 +4937,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4543,8 +5147,8 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B738CEAF-BA8D-46A4-B41F-A105DC1BD636}">
-  <sheetPr codeName="Tabelle4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
+  <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63AA3E00-C5FC-4679-9AD1-7FA2B893E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{41815500-741B-4B57-AAD1-8BBFC958AFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="299" uniqueCount="158">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="300" uniqueCount="159">
   <si>
     <t>L_den</t>
   </si>
@@ -611,6 +611,9 @@
   </si>
   <si>
     <t>END Model + Imputation</t>
+  </si>
+  <si>
+    <t>TEST GitHub 26.05.2026</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2258,6 +2261,11 @@
       <c r="D40" s="127">
         <f>'Agglomeration road'!D80</f>
         <v>21603841169.787403</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2821,14 +2829,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{41815500-741B-4B57-AAD1-8BBFC958AFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{93FB480C-37F5-41CF-835B-58E2367956AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="300" uniqueCount="159">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="301" uniqueCount="160">
   <si>
     <t>L_den</t>
   </si>
@@ -613,7 +613,10 @@
     <t>END Model + Imputation</t>
   </si>
   <si>
-    <t>TEST GitHub 26.05.2026</t>
+    <t>TEST 2 GitHub 26.05.2026</t>
+  </si>
+  <si>
+    <t>TEST 1 GitHub 26.05.2026</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C7D27E-13C9-40A4-936B-06BBF9BE4E35}">
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2265,6 +2268,11 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2829,14 +2837,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{93FB480C-37F5-41CF-835B-58E2367956AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0D73070A-8A7B-471E-8AC1-9BB322884F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="301" uniqueCount="160">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="300" uniqueCount="160">
   <si>
     <t>L_den</t>
   </si>
@@ -243,9 +243,6 @@
     <t>road</t>
   </si>
   <si>
-    <t>78.9270 - 3.1162 * c + 0.0342 * c^2</t>
-  </si>
-  <si>
     <t>lden</t>
   </si>
   <si>
@@ -255,9 +252,6 @@
     <t>High sleep disturbance</t>
   </si>
   <si>
-    <t>19.4312 - 0.9336 * c + 0.0126 * c^2</t>
-  </si>
-  <si>
     <t>lnight</t>
   </si>
   <si>
@@ -273,27 +267,18 @@
     <t>incidence</t>
   </si>
   <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.055,0)</t>
-  </si>
-  <si>
     <t>Engelmann et al. (2025), ch. 3.3.1</t>
   </si>
   <si>
     <t>Cardiovascular disease</t>
   </si>
   <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.032,0)</t>
-  </si>
-  <si>
     <t>Engelmann et al. (2025), ch. 3.3.2</t>
   </si>
   <si>
     <t>Diabetes</t>
   </si>
   <si>
-    <t>ifelse(c&gt;threshold,(c-threshold)*1.062,0)</t>
-  </si>
-  <si>
     <t>Engelmann et al. (2025), ch. 3.3.3</t>
   </si>
   <si>
@@ -307,9 +292,6 @@
   </si>
   <si>
     <t>END Annex III</t>
-  </si>
-  <si>
-    <t>ifelse(c&gt;threshold, e^((ln(1,08)/10)*(c-threshold)), 1)</t>
   </si>
   <si>
     <t>Lden</t>
@@ -613,10 +595,140 @@
     <t>END Model + Imputation</t>
   </si>
   <si>
-    <t>TEST 2 GitHub 26.05.2026</t>
-  </si>
-  <si>
-    <t>TEST 1 GitHub 26.05.2026</t>
+    <t xml:space="preserve">Modellvergleiche: ULR vs ULR-WHO vs ETC HE Report </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(78.9270 - 3.1162 * c + 0.0342 * c^2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(19.4312 - 0.9336 * c + 0.0126 * c^2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 100</t>
+    </r>
+  </si>
+  <si>
+    <t>ERF - vollständige Formel wie in G35 ergänzen, Formeln prüfen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.062) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , 0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.055) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , 0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.032) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , 0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , e^((ln(1,08) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)*(c-threshold)) , 1)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1766,20 +1878,20 @@
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="134" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B10" s="134"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D12" s="136" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E12" s="136"/>
       <c r="F12" s="136"/>
@@ -1787,7 +1899,7 @@
       <c r="H12" s="136"/>
       <c r="I12" s="136"/>
       <c r="K12" s="132" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L12" s="132"/>
       <c r="M12" s="132"/>
@@ -1799,40 +1911,40 @@
       <c r="A13" s="110"/>
       <c r="B13" s="110"/>
       <c r="D13" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="104" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="104" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="M13" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="N13" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="O13" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="104" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="105" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="107" t="s">
-        <v>122</v>
-      </c>
-      <c r="L13" s="107" t="s">
-        <v>123</v>
-      </c>
-      <c r="M13" s="107" t="s">
-        <v>124</v>
-      </c>
-      <c r="N13" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="O13" s="107" t="s">
-        <v>126</v>
-      </c>
       <c r="P13" s="108" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1840,7 +1952,7 @@
         <v>49</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D14" s="106">
         <v>3725500</v>
@@ -1885,7 +1997,7 @@
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="135"/>
       <c r="B15" s="119" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="120">
@@ -1964,10 +2076,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="135" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B18" s="110" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D18" s="106">
         <v>716500</v>
@@ -2012,7 +2124,7 @@
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="135"/>
       <c r="B19" s="110" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D19" s="106">
         <v>1289300</v>
@@ -2090,10 +2202,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="135" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B22" s="110" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D22" s="106">
         <v>303900</v>
@@ -2138,7 +2250,7 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="135"/>
       <c r="B23" s="110" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D23" s="106">
         <v>419800</v>
@@ -2188,7 +2300,7 @@
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="134" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B32" s="134"/>
     </row>
@@ -2196,15 +2308,15 @@
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="110"/>
       <c r="C34" s="106" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D34" s="109" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="110" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C35" s="106">
         <f>I15</f>
@@ -2234,15 +2346,15 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C38" s="96" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D38" s="85" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C39" s="124">
         <f>'Agglomeration road'!C79</f>
@@ -2255,7 +2367,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="33" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C40" s="125">
         <f>'Agglomeration road'!C80</f>
@@ -2267,14 +2379,10 @@
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="4" t="s">
-        <v>159</v>
-      </c>
+      <c r="B44" s="4"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="4" t="s">
-        <v>158</v>
-      </c>
+      <c r="B45" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2339,20 +2447,20 @@
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="134" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B10" s="134"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D12" s="136" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E12" s="136"/>
       <c r="F12" s="136"/>
@@ -2360,7 +2468,7 @@
       <c r="H12" s="136"/>
       <c r="I12" s="136"/>
       <c r="K12" s="132" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L12" s="132"/>
       <c r="M12" s="132"/>
@@ -2372,40 +2480,40 @@
       <c r="A13" s="110"/>
       <c r="B13" s="110"/>
       <c r="D13" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="104" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="104" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="M13" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="N13" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="O13" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="104" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="105" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="107" t="s">
-        <v>122</v>
-      </c>
-      <c r="L13" s="107" t="s">
-        <v>123</v>
-      </c>
-      <c r="M13" s="107" t="s">
-        <v>124</v>
-      </c>
-      <c r="N13" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="O13" s="107" t="s">
-        <v>126</v>
-      </c>
       <c r="P13" s="108" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2413,7 +2521,7 @@
         <v>49</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D14" s="106">
         <v>3725500</v>
@@ -2458,7 +2566,7 @@
     <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="135"/>
       <c r="B15" s="111" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C15" s="112"/>
       <c r="D15" s="113">
@@ -2537,10 +2645,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="135" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B18" s="110" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D18" s="106">
         <v>716500</v>
@@ -2585,7 +2693,7 @@
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="135"/>
       <c r="B19" s="110" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D19" s="106">
         <v>1289300</v>
@@ -2663,10 +2771,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="135" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B22" s="110" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D22" s="106">
         <v>303900</v>
@@ -2711,7 +2819,7 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="135"/>
       <c r="B23" s="110" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D23" s="106">
         <v>419800</v>
@@ -2761,7 +2869,7 @@
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="134" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B32" s="134"/>
     </row>
@@ -2769,15 +2877,15 @@
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="110"/>
       <c r="C34" s="106" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D34" s="109" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="110" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C35" s="106">
         <f>I15</f>
@@ -2807,44 +2915,44 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C38" s="96" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D38" s="85" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C39" s="128" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D39" s="129" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="33" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C40" s="130" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D40" s="131" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2863,7 +2971,7 @@
     <col min="4" max="4" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="39.7109375" customWidth="1"/>
+    <col min="7" max="7" width="49" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
     <col min="9" max="9" width="20.5703125" customWidth="1"/>
     <col min="10" max="10" width="19.140625" customWidth="1"/>
@@ -2912,7 +3020,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2">
         <v>1.4250000000000001E-3</v>
@@ -2935,7 +3043,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2">
         <v>8.5990000000000007E-3</v>
@@ -2971,30 +3079,30 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C13" s="6">
         <f>Frontend!$I$15*C8</f>
@@ -3027,7 +3135,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C14" s="6">
         <f>Frontend!$P$15*C9</f>
@@ -3069,7 +3177,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C18" s="8">
         <f>Frontend!$I$15+I13</f>
@@ -3078,7 +3186,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C19" s="8">
         <f>Frontend!$P$15+I14</f>
@@ -3093,7 +3201,7 @@
     <row r="23" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -3118,14 +3226,14 @@
       <c r="F29" t="s">
         <v>40</v>
       </c>
-      <c r="G29" t="s">
-        <v>35</v>
+      <c r="G29" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="H29" t="s">
         <v>41</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s">
         <v>43</v>
@@ -3134,7 +3242,7 @@
         <v>44</v>
       </c>
       <c r="L29" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M29" t="s">
         <v>42</v>
@@ -3142,7 +3250,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -3157,10 +3265,10 @@
         <v>49</v>
       </c>
       <c r="G30" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" t="s">
         <v>50</v>
-      </c>
-      <c r="H30" t="s">
-        <v>51</v>
       </c>
       <c r="I30" s="27">
         <v>45</v>
@@ -3175,12 +3283,12 @@
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -3195,10 +3303,10 @@
         <v>49</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I31" s="27">
         <v>40</v>
@@ -3213,18 +3321,18 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
         <v>57</v>
-      </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" t="s">
-        <v>59</v>
       </c>
       <c r="E32" t="s">
         <v>48</v>
@@ -3233,10 +3341,10 @@
         <v>49</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I32" s="27">
         <v>45</v>
@@ -3248,18 +3356,18 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s">
         <v>48</v>
@@ -3268,10 +3376,10 @@
         <v>49</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="H33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I33">
         <v>45</v>
@@ -3283,18 +3391,18 @@
         <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
         <v>48</v>
@@ -3303,10 +3411,10 @@
         <v>49</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I34">
         <v>45</v>
@@ -3318,18 +3426,18 @@
         <v>1</v>
       </c>
       <c r="M34" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E35" t="s">
         <v>48</v>
@@ -3338,10 +3446,10 @@
         <v>49</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I35">
         <v>53</v>
@@ -3353,19 +3461,19 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
       <c r="E40" s="137" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F40" s="137"/>
       <c r="G40" s="137"/>
@@ -3373,7 +3481,7 @@
       <c r="I40" s="137"/>
       <c r="J40" s="137"/>
       <c r="K40" s="138" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L40" s="139"/>
       <c r="M40" s="139"/>
@@ -3382,48 +3490,48 @@
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E41" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="H41" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="J41" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="K41" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="L41" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="M41" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="64" t="s">
-        <v>112</v>
-      </c>
-      <c r="G41" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="H41" s="64" t="s">
+      <c r="N41" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="O41" s="50" t="s">
         <v>115</v>
-      </c>
-      <c r="J41" s="64" t="s">
-        <v>116</v>
-      </c>
-      <c r="K41" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="L41" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="M41" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="N41" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="O41" s="50" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="144" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="29">
@@ -3483,7 +3591,7 @@
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="145"/>
       <c r="B43" s="15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -3524,7 +3632,7 @@
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="146"/>
       <c r="B44" s="19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -3575,13 +3683,13 @@
     </row>
     <row r="45" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C45" s="93" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D45" s="82" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E45" s="67"/>
       <c r="F45" s="67"/>
@@ -3597,10 +3705,10 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="144" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C46" s="91"/>
       <c r="D46" s="82"/>
@@ -3613,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="67">
-        <f t="shared" si="2"/>
+        <f>IF(G43&gt;$I$32, EXP((LN(1.055)/10)*(G43-$I$32)),1)</f>
         <v>1</v>
       </c>
       <c r="H46" s="67">
@@ -3652,7 +3760,7 @@
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="145"/>
       <c r="B47" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C47" s="92">
         <f>SUM(K47:O47)</f>
@@ -3710,7 +3818,7 @@
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="145"/>
       <c r="B48" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C48" s="92">
         <f>(C47)/(1+C47)</f>
@@ -3735,7 +3843,7 @@
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="146"/>
       <c r="B49" s="42" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C49" s="103">
         <f>0.2069215*C48*D42</f>
@@ -3759,10 +3867,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="144" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C50" s="91"/>
       <c r="D50" s="82"/>
@@ -3814,7 +3922,7 @@
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="145"/>
       <c r="B51" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C51" s="92">
         <f>SUM(K51:O51)</f>
@@ -3872,7 +3980,7 @@
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="145"/>
       <c r="B52" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C52" s="92">
         <f>C51/(1+C51)</f>
@@ -3897,7 +4005,7 @@
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="146"/>
       <c r="B53" s="42" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C53" s="100">
         <f>0.0115708*C52*D42</f>
@@ -3921,10 +4029,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="144" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C54" s="91"/>
       <c r="D54" s="82"/>
@@ -3976,7 +4084,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="145"/>
       <c r="B55" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C55" s="92">
         <f>SUM(K55:O55)</f>
@@ -4034,7 +4142,7 @@
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="145"/>
       <c r="B56" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C56" s="92">
         <f>C55/(1+C55)</f>
@@ -4059,7 +4167,7 @@
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="146"/>
       <c r="B57" s="42" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C57" s="100">
         <f>0.0059261*C56*D42</f>
@@ -4083,10 +4191,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="144" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C58" s="94"/>
       <c r="D58" s="90"/>
@@ -4138,7 +4246,7 @@
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="145"/>
       <c r="B59" s="15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C59" s="95">
         <f>SUM(K59:O59)</f>
@@ -4196,7 +4304,7 @@
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="145"/>
       <c r="B60" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C60" s="95">
         <f>C59/(1+C59)</f>
@@ -4221,7 +4329,7 @@
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="146"/>
       <c r="B61" s="42" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C61" s="99">
         <f>0.00127695*C60*D42</f>
@@ -4248,7 +4356,7 @@
         <v>45</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C62" s="96"/>
       <c r="D62" s="85"/>
@@ -4300,7 +4408,7 @@
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="143"/>
       <c r="B63" s="27" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C63" s="96">
         <f>SUM(K63:O63)</f>
@@ -4358,7 +4466,7 @@
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="141"/>
       <c r="B64" s="44" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C64" s="89">
         <f>C63*$J$30*D42</f>
@@ -4403,14 +4511,14 @@
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
       <c r="E66" s="137" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F66" s="137"/>
       <c r="G66" s="137"/>
       <c r="H66" s="137"/>
       <c r="I66" s="137"/>
       <c r="J66" s="138" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K66" s="139"/>
       <c r="L66" s="139"/>
@@ -4423,46 +4531,46 @@
       <c r="B67" s="23"/>
       <c r="C67" s="23"/>
       <c r="D67" s="25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E67" s="64" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F67" s="64" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G67" s="64" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H67" s="64" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I67" s="64" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J67" s="49" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L67" s="50" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="M67" s="50" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N67" s="50" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="O67" s="15"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="144" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C68" s="18"/>
       <c r="D68" s="29">
@@ -4514,7 +4622,7 @@
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
@@ -4553,7 +4661,7 @@
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="146"/>
       <c r="B70" s="19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="26"/>
@@ -4601,14 +4709,14 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="31" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="87" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D71" s="97" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E71" s="74"/>
       <c r="F71" s="74"/>
@@ -4624,10 +4732,10 @@
     </row>
     <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="140" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C72" s="88"/>
       <c r="D72" s="98"/>
@@ -4675,7 +4783,7 @@
     <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="140"/>
       <c r="B73" s="27" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C73" s="88">
         <f>SUM(J73:N73)</f>
@@ -4729,7 +4837,7 @@
     <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="141"/>
       <c r="B74" s="44" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C74" s="89">
         <f>J31*C73*D68</f>
@@ -4753,26 +4861,29 @@
     </row>
     <row r="77" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="20" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" t="s">
+        <v>129</v>
+      </c>
+      <c r="E78" t="s">
         <v>99</v>
       </c>
-      <c r="D78" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" t="s">
-        <v>105</v>
-      </c>
       <c r="F78" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B79" s="33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C79" s="40">
         <f>C61+C64+C74</f>
@@ -4789,7 +4900,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B80" s="33" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C80" s="41">
         <f>C79*C86</f>
@@ -4806,7 +4917,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="117" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C82" s="40">
         <f>(C79/C87)*100000</f>
@@ -4819,7 +4930,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="117" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C83" s="118">
         <f>C80/C87</f>
@@ -4832,12 +4943,12 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="33" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="33" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C86" s="118">
         <v>70000</v>
@@ -4845,7 +4956,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="33" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C87" s="8">
         <v>25660460</v>
@@ -4887,13 +4998,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +5012,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -4912,10 +5023,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -4923,10 +5034,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +5045,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +5056,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0D73070A-8A7B-471E-8AC1-9BB322884F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{735E44AF-7170-462E-A1F5-E70D606806F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,9 +216,6 @@
     <t>source</t>
   </si>
   <si>
-    <t>metric</t>
-  </si>
-  <si>
     <t>reference</t>
   </si>
   <si>
@@ -729,6 +726,9 @@
       </rPr>
       <t>)*(c-threshold)) , 1)</t>
     </r>
+  </si>
+  <si>
+    <t>metric ("c")</t>
   </si>
 </sst>
 </file>
@@ -1878,20 +1878,20 @@
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="134" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B10" s="134"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="136" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="136"/>
       <c r="F12" s="136"/>
@@ -1899,7 +1899,7 @@
       <c r="H12" s="136"/>
       <c r="I12" s="136"/>
       <c r="K12" s="132" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L12" s="132"/>
       <c r="M12" s="132"/>
@@ -1911,48 +1911,48 @@
       <c r="A13" s="110"/>
       <c r="B13" s="110"/>
       <c r="D13" s="104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="F13" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="G13" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="H13" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="104" t="s">
+      <c r="I13" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="I13" s="105" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" s="107" t="s">
+      <c r="L13" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="107" t="s">
+      <c r="M13" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="M13" s="107" t="s">
+      <c r="N13" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="N13" s="107" t="s">
+      <c r="O13" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="O13" s="107" t="s">
-        <v>120</v>
-      </c>
       <c r="P13" s="108" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="135" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="106">
         <v>3725500</v>
@@ -1997,7 +1997,7 @@
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="135"/>
       <c r="B15" s="119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="120">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="135" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="110" t="s">
         <v>72</v>
-      </c>
-      <c r="B18" s="110" t="s">
-        <v>73</v>
       </c>
       <c r="D18" s="106">
         <v>716500</v>
@@ -2124,7 +2124,7 @@
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="135"/>
       <c r="B19" s="110" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="106">
         <v>1289300</v>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="135" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="110" t="s">
         <v>75</v>
-      </c>
-      <c r="B22" s="110" t="s">
-        <v>76</v>
       </c>
       <c r="D22" s="106">
         <v>303900</v>
@@ -2250,7 +2250,7 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="135"/>
       <c r="B23" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="106">
         <v>419800</v>
@@ -2300,7 +2300,7 @@
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="134"/>
     </row>
@@ -2308,15 +2308,15 @@
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="110"/>
       <c r="C34" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="109" t="s">
         <v>67</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="110" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" s="106">
         <f>I15</f>
@@ -2346,15 +2346,15 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C38" s="96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D38" s="85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C39" s="124">
         <f>'Agglomeration road'!C79</f>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C40" s="125">
         <f>'Agglomeration road'!C80</f>
@@ -2447,20 +2447,20 @@
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="134" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B10" s="134"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="136" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="136"/>
       <c r="F12" s="136"/>
@@ -2468,7 +2468,7 @@
       <c r="H12" s="136"/>
       <c r="I12" s="136"/>
       <c r="K12" s="132" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L12" s="132"/>
       <c r="M12" s="132"/>
@@ -2480,48 +2480,48 @@
       <c r="A13" s="110"/>
       <c r="B13" s="110"/>
       <c r="D13" s="104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="F13" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="G13" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="H13" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="104" t="s">
+      <c r="I13" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="I13" s="105" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" s="107" t="s">
+      <c r="L13" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="107" t="s">
+      <c r="M13" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="M13" s="107" t="s">
+      <c r="N13" s="107" t="s">
         <v>118</v>
       </c>
-      <c r="N13" s="107" t="s">
+      <c r="O13" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="O13" s="107" t="s">
-        <v>120</v>
-      </c>
       <c r="P13" s="108" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="135" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="106">
         <v>3725500</v>
@@ -2566,7 +2566,7 @@
     <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="135"/>
       <c r="B15" s="111" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="112"/>
       <c r="D15" s="113">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="135" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="110" t="s">
         <v>72</v>
-      </c>
-      <c r="B18" s="110" t="s">
-        <v>73</v>
       </c>
       <c r="D18" s="106">
         <v>716500</v>
@@ -2693,7 +2693,7 @@
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="135"/>
       <c r="B19" s="110" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="106">
         <v>1289300</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="135" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="110" t="s">
         <v>75</v>
-      </c>
-      <c r="B22" s="110" t="s">
-        <v>76</v>
       </c>
       <c r="D22" s="106">
         <v>303900</v>
@@ -2819,7 +2819,7 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="135"/>
       <c r="B23" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="106">
         <v>419800</v>
@@ -2869,7 +2869,7 @@
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="134"/>
     </row>
@@ -2877,15 +2877,15 @@
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="110"/>
       <c r="C34" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="109" t="s">
         <v>67</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="110" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" s="106">
         <f>I15</f>
@@ -2915,44 +2915,44 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C38" s="96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D38" s="85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C39" s="128" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" s="129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C40" s="130" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="131" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2">
         <v>1.4250000000000001E-3</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2">
         <v>8.5990000000000007E-3</v>
@@ -3079,30 +3079,30 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" s="6">
         <f>Frontend!$I$15*C8</f>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="6">
         <f>Frontend!$P$15*C9</f>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" s="8">
         <f>Frontend!$I$15+I13</f>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="8">
         <f>Frontend!$P$15+I14</f>
@@ -3201,7 +3201,7 @@
     <row r="23" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -3227,48 +3227,48 @@
         <v>40</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H29" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" t="s">
         <v>41</v>
-      </c>
-      <c r="I29" t="s">
-        <v>80</v>
-      </c>
-      <c r="J29" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
         <v>46</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>47</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>48</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" t="s">
         <v>49</v>
-      </c>
-      <c r="G30" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" t="s">
-        <v>50</v>
       </c>
       <c r="I30" s="27">
         <v>45</v>
@@ -3283,30 +3283,30 @@
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" t="s">
         <v>46</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>47</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>48</v>
       </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
       <c r="G31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I31" s="27">
         <v>40</v>
@@ -3321,30 +3321,30 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
         <v>55</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>56</v>
       </c>
-      <c r="D32" t="s">
-        <v>57</v>
-      </c>
       <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
         <v>48</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H32" t="s">
         <v>49</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H32" t="s">
-        <v>50</v>
       </c>
       <c r="I32" s="27">
         <v>45</v>
@@ -3356,30 +3356,30 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" t="s">
         <v>56</v>
       </c>
-      <c r="D33" t="s">
-        <v>57</v>
-      </c>
       <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
         <v>48</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" t="s">
         <v>49</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" t="s">
-        <v>50</v>
       </c>
       <c r="I33">
         <v>45</v>
@@ -3391,30 +3391,30 @@
         <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" t="s">
         <v>56</v>
       </c>
-      <c r="D34" t="s">
-        <v>57</v>
-      </c>
       <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" t="s">
         <v>48</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" t="s">
         <v>49</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="H34" t="s">
-        <v>50</v>
       </c>
       <c r="I34">
         <v>45</v>
@@ -3426,30 +3426,30 @@
         <v>1</v>
       </c>
       <c r="M34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
         <v>56</v>
       </c>
-      <c r="D35" t="s">
-        <v>57</v>
-      </c>
       <c r="E35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" t="s">
         <v>48</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H35" t="s">
         <v>49</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H35" t="s">
-        <v>50</v>
       </c>
       <c r="I35">
         <v>53</v>
@@ -3461,19 +3461,19 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C40" s="15"/>
       <c r="E40" s="137" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F40" s="137"/>
       <c r="G40" s="137"/>
@@ -3481,7 +3481,7 @@
       <c r="I40" s="137"/>
       <c r="J40" s="137"/>
       <c r="K40" s="138" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L40" s="139"/>
       <c r="M40" s="139"/>
@@ -3490,48 +3490,48 @@
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E41" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="H41" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="F41" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="G41" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="H41" s="64" t="s">
+      <c r="I41" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="J41" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="K41" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="K41" s="49" t="s">
+      <c r="L41" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="L41" s="50" t="s">
+      <c r="M41" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="M41" s="50" t="s">
+      <c r="N41" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="N41" s="50" t="s">
+      <c r="O41" s="50" t="s">
         <v>114</v>
-      </c>
-      <c r="O41" s="50" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="29">
@@ -3591,7 +3591,7 @@
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="145"/>
       <c r="B43" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -3632,7 +3632,7 @@
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="146"/>
       <c r="B44" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
@@ -3683,13 +3683,13 @@
     </row>
     <row r="45" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C45" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D45" s="82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45" s="67"/>
       <c r="F45" s="67"/>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="144" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C46" s="91"/>
       <c r="D46" s="82"/>
@@ -3760,7 +3760,7 @@
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="145"/>
       <c r="B47" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="92">
         <f>SUM(K47:O47)</f>
@@ -3818,7 +3818,7 @@
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="145"/>
       <c r="B48" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="92">
         <f>(C47)/(1+C47)</f>
@@ -3843,7 +3843,7 @@
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="146"/>
       <c r="B49" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C49" s="103">
         <f>0.2069215*C48*D42</f>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="144" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C50" s="91"/>
       <c r="D50" s="82"/>
@@ -3922,7 +3922,7 @@
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="145"/>
       <c r="B51" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C51" s="92">
         <f>SUM(K51:O51)</f>
@@ -3980,7 +3980,7 @@
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="145"/>
       <c r="B52" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" s="92">
         <f>C51/(1+C51)</f>
@@ -4005,7 +4005,7 @@
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="146"/>
       <c r="B53" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C53" s="100">
         <f>0.0115708*C52*D42</f>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="144" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C54" s="91"/>
       <c r="D54" s="82"/>
@@ -4084,7 +4084,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="145"/>
       <c r="B55" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C55" s="92">
         <f>SUM(K55:O55)</f>
@@ -4142,7 +4142,7 @@
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="145"/>
       <c r="B56" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C56" s="92">
         <f>C55/(1+C55)</f>
@@ -4167,7 +4167,7 @@
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="146"/>
       <c r="B57" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C57" s="100">
         <f>0.0059261*C56*D42</f>
@@ -4191,10 +4191,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="144" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C58" s="94"/>
       <c r="D58" s="90"/>
@@ -4246,7 +4246,7 @@
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="145"/>
       <c r="B59" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="95">
         <f>SUM(K59:O59)</f>
@@ -4304,7 +4304,7 @@
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="145"/>
       <c r="B60" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C60" s="95">
         <f>C59/(1+C59)</f>
@@ -4329,7 +4329,7 @@
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="146"/>
       <c r="B61" s="42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C61" s="99">
         <f>0.00127695*C60*D42</f>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="142" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C62" s="96"/>
       <c r="D62" s="85"/>
@@ -4408,7 +4408,7 @@
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="143"/>
       <c r="B63" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C63" s="96">
         <f>SUM(K63:O63)</f>
@@ -4466,7 +4466,7 @@
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="141"/>
       <c r="B64" s="44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C64" s="89">
         <f>C63*$J$30*D42</f>
@@ -4511,14 +4511,14 @@
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
       <c r="E66" s="137" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F66" s="137"/>
       <c r="G66" s="137"/>
       <c r="H66" s="137"/>
       <c r="I66" s="137"/>
       <c r="J66" s="138" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K66" s="139"/>
       <c r="L66" s="139"/>
@@ -4531,46 +4531,46 @@
       <c r="B67" s="23"/>
       <c r="C67" s="23"/>
       <c r="D67" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="G67" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="H67" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="F67" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="G67" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="H67" s="64" t="s">
+      <c r="I67" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="I67" s="64" t="s">
-        <v>109</v>
-      </c>
       <c r="J67" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="K67" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="K67" s="50" t="s">
+      <c r="L67" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="L67" s="50" t="s">
+      <c r="M67" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="M67" s="50" t="s">
+      <c r="N67" s="50" t="s">
         <v>119</v>
-      </c>
-      <c r="N67" s="50" t="s">
-        <v>120</v>
       </c>
       <c r="O67" s="15"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="18"/>
       <c r="D68" s="29">
@@ -4622,7 +4622,7 @@
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
@@ -4661,7 +4661,7 @@
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="146"/>
       <c r="B70" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="26"/>
@@ -4709,14 +4709,14 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" s="97" t="s">
         <v>93</v>
-      </c>
-      <c r="D71" s="97" t="s">
-        <v>94</v>
       </c>
       <c r="E71" s="74"/>
       <c r="F71" s="74"/>
@@ -4732,10 +4732,10 @@
     </row>
     <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="140" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C72" s="88"/>
       <c r="D72" s="98"/>
@@ -4783,7 +4783,7 @@
     <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="140"/>
       <c r="B73" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C73" s="88">
         <f>SUM(J73:N73)</f>
@@ -4837,7 +4837,7 @@
     <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="141"/>
       <c r="B74" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C74" s="89">
         <f>J31*C73*D68</f>
@@ -4861,29 +4861,29 @@
     </row>
     <row r="77" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B79" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C79" s="40">
         <f>C61+C64+C74</f>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B80" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C80" s="41">
         <f>C79*C86</f>
@@ -4917,7 +4917,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C82" s="40">
         <f>(C79/C87)*100000</f>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="117" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C83" s="118">
         <f>C80/C87</f>
@@ -4943,12 +4943,12 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C86" s="118">
         <v>70000</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C87" s="8">
         <v>25660460</v>
@@ -4998,13 +4998,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5012,10 +5012,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5023,10 +5023,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5034,10 +5034,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="37" t="s">
         <v>134</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5045,10 +5045,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5056,10 +5056,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{735E44AF-7170-462E-A1F5-E70D606806F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{04F7E2C0-BFFE-4F33-A779-849762DC0B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
@@ -629,81 +629,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.062) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/ 10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> , 0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.055) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/ 10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> , 0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.032) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/ 10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> , 0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">ifelse(c&gt;threshold , e^((ln(1,08) </t>
     </r>
     <r>
@@ -729,6 +654,141 @@
   </si>
   <si>
     <t>metric ("c")</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.055) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.032) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ifelse(c&gt;threshold , ((c-threshold)*1.062) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/ 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2945,14 +3005,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D12:I12"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3230,7 +3290,7 @@
         <v>154</v>
       </c>
       <c r="H29" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I29" t="s">
         <v>79</v>
@@ -3341,7 +3401,7 @@
         <v>48</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H32" t="s">
         <v>49</v>
@@ -3376,7 +3436,7 @@
         <v>48</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H33" t="s">
         <v>49</v>
@@ -3411,7 +3471,7 @@
         <v>48</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H34" t="s">
         <v>49</v>
@@ -3446,7 +3506,7 @@
         <v>48</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H35" t="s">
         <v>49</v>

--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{04F7E2C0-BFFE-4F33-A779-849762DC0B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AB833211-344A-486E-A156-EB0F2C039A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
     <sheet name="Frontend" sheetId="8" r:id="rId2"/>
-    <sheet name="Frontend DEMO DAGA" sheetId="13" r:id="rId3"/>
-    <sheet name="Agglomeration road" sheetId="1" r:id="rId4"/>
-    <sheet name="Fragen" sheetId="11" r:id="rId5"/>
-    <sheet name="ERF HRA" sheetId="10" r:id="rId6"/>
-    <sheet name="Agglomeration rail" sheetId="2" r:id="rId7"/>
-    <sheet name="Agglomeration air" sheetId="3" r:id="rId8"/>
-    <sheet name="Major roads " sheetId="5" r:id="rId9"/>
-    <sheet name="Major railways " sheetId="6" r:id="rId10"/>
-    <sheet name="Major airports" sheetId="7" r:id="rId11"/>
-    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId12"/>
+    <sheet name="Frontend DEMO DE" sheetId="13" r:id="rId3"/>
+    <sheet name="Frontend DEMO ENG" sheetId="14" r:id="rId4"/>
+    <sheet name="Agglomeration road" sheetId="1" r:id="rId5"/>
+    <sheet name="Abb DALY agg road" sheetId="15" r:id="rId6"/>
+    <sheet name="Fragen" sheetId="11" r:id="rId7"/>
+    <sheet name="ERF HRA" sheetId="10" r:id="rId8"/>
+    <sheet name="Agglomeration rail" sheetId="2" r:id="rId9"/>
+    <sheet name="Agglomeration air" sheetId="3" r:id="rId10"/>
+    <sheet name="Major roads " sheetId="5" r:id="rId11"/>
+    <sheet name="Major railways " sheetId="6" r:id="rId12"/>
+    <sheet name="Major airports" sheetId="7" r:id="rId13"/>
+    <sheet name="5dB to 1dB refinement" sheetId="9" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="300" uniqueCount="160">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="397" uniqueCount="173">
   <si>
     <t>L_den</t>
   </si>
@@ -174,9 +176,6 @@
     <t>Ausgabe</t>
   </si>
   <si>
-    <t>Anzahl belasteter Personen ab 25 dB</t>
-  </si>
-  <si>
     <t>estimate the number of people exposed below the END thresholds for road noise inside agglomerations</t>
   </si>
   <si>
@@ -374,9 +373,6 @@
     <t>END model</t>
   </si>
   <si>
-    <t>EEA model</t>
-  </si>
-  <si>
     <t>General</t>
   </si>
   <si>
@@ -387,9 +383,6 @@
   </si>
   <si>
     <t>EURO</t>
-  </si>
-  <si>
-    <t>EEA-END</t>
   </si>
   <si>
     <t>ERF[Ni] = product of the ERF of the all noise exposure categories</t>
@@ -529,33 +522,6 @@
     <t>Sum exposed</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">YLL = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>YLLnat (= 0,2069215)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ∙ AFtot * Summe der Exponierten</t>
-    </r>
-  </si>
-  <si>
     <t>Sum p[i]*ERF[Ni]</t>
   </si>
   <si>
@@ -587,12 +553,6 @@
   </si>
   <si>
     <t>- tba -</t>
-  </si>
-  <si>
-    <t>END Model + Imputation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modellvergleiche: ULR vs ULR-WHO vs ETC HE Report </t>
   </si>
   <si>
     <r>
@@ -789,6 +749,85 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Modellvergleiche: ULR vs ULR-WHO vs ULR+Imputation vs ETC HE Report </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Anzahl </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>belasteter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Personen ab 25 dB</t>
+    </r>
+  </si>
+  <si>
+    <t>Number of exposed persons according to END</t>
+  </si>
+  <si>
+    <t>Number of people exposed to noise levels of 25 dB or higher</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Exposure area</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Number of people exposed according to END</t>
+  </si>
+  <si>
+    <t>Quantification of Noise Damage Costs</t>
+  </si>
+  <si>
+    <t>END</t>
+  </si>
+  <si>
+    <t>END-WHO</t>
+  </si>
+  <si>
+    <t>ETC HE Report 2023/11v3</t>
+  </si>
+  <si>
+    <t>END+Imputation</t>
+  </si>
+  <si>
+    <t>EURO/Person</t>
+  </si>
+  <si>
+    <t>DALY/100k</t>
+  </si>
+  <si>
+    <t>YLL = YLLnat (= 0,2069215) ∙ AFtot * Summe der Exponierten</t>
+  </si>
+  <si>
+    <t>YLL</t>
+  </si>
+  <si>
+    <t>YLD</t>
   </si>
 </sst>
 </file>
@@ -914,7 +953,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -960,6 +999,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1118,7 +1187,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1151,9 +1220,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1187,8 +1253,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1208,39 +1272,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1259,31 +1301,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1327,6 +1352,9 @@
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1368,6 +1396,121 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="9" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="9" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="9" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="12" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="13" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="11" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1849,6 +1992,26 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
+  <sheetPr codeName="Tabelle3"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
+  <sheetPr codeName="Tabelle5"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D784C34-E246-472E-88D5-CA0D5063A3C9}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1"/>
@@ -1858,7 +2021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D71C91-7A22-40CF-B195-068A9D60F08B}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1"/>
@@ -1868,7 +2031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AA0BE1-EB71-4657-B503-300F880C587F}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1881,7 +2044,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -1920,15 +2083,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="133"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -1937,417 +2100,417 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="134" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="134"/>
+      <c r="A10" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="103"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="110" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="110" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="136" t="s">
+      <c r="A12" s="78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="K12" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="136"/>
-      <c r="K12" s="132" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="132"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
-      <c r="B13" s="110"/>
-      <c r="D13" s="104" t="s">
+      <c r="A13" s="78"/>
+      <c r="B13" s="78"/>
+      <c r="D13" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="H13" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="I13" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="L13" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="104" t="s">
+      <c r="M13" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="105" t="s">
+      <c r="N13" s="75" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="P13" s="76" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="107" t="s">
-        <v>115</v>
-      </c>
-      <c r="L13" s="107" t="s">
-        <v>116</v>
-      </c>
-      <c r="M13" s="107" t="s">
-        <v>117</v>
-      </c>
-      <c r="N13" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="O13" s="107" t="s">
-        <v>119</v>
-      </c>
-      <c r="P13" s="108" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="135" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="106">
+      <c r="D14" s="74">
         <v>3725500</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="74">
         <v>1643600</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="74">
         <v>998600</v>
       </c>
-      <c r="G14" s="106">
+      <c r="G14" s="74">
         <v>481900</v>
       </c>
-      <c r="H14" s="106">
+      <c r="H14" s="74">
         <v>33500</v>
       </c>
-      <c r="I14" s="106">
+      <c r="I14" s="74">
         <f>SUM(D14:H14)</f>
         <v>6883100</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="109">
+      <c r="K14" s="77">
         <v>2411700</v>
       </c>
-      <c r="L14" s="109">
+      <c r="L14" s="77">
         <v>1244300</v>
       </c>
-      <c r="M14" s="109">
+      <c r="M14" s="77">
         <v>574000</v>
       </c>
-      <c r="N14" s="109">
+      <c r="N14" s="77">
         <v>54400</v>
       </c>
-      <c r="O14" s="109">
+      <c r="O14" s="77">
         <v>2100</v>
       </c>
-      <c r="P14" s="109">
+      <c r="P14" s="77">
         <f>SUM(K14:O14)</f>
         <v>4286500</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="135"/>
-      <c r="B15" s="119" t="s">
-        <v>77</v>
+      <c r="A15" s="104"/>
+      <c r="B15" s="87" t="s">
+        <v>76</v>
       </c>
       <c r="C15" s="15"/>
-      <c r="D15" s="120">
+      <c r="D15" s="88">
         <v>3762100</v>
       </c>
-      <c r="E15" s="120">
+      <c r="E15" s="88">
         <v>3050900</v>
       </c>
-      <c r="F15" s="120">
+      <c r="F15" s="88">
         <v>2479000</v>
       </c>
-      <c r="G15" s="120">
+      <c r="G15" s="88">
         <v>1006400</v>
       </c>
-      <c r="H15" s="120">
+      <c r="H15" s="88">
         <v>99800</v>
       </c>
-      <c r="I15" s="120">
+      <c r="I15" s="88">
         <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
         <v>10398200</v>
       </c>
-      <c r="J15" s="121"/>
-      <c r="K15" s="122">
+      <c r="J15" s="89"/>
+      <c r="K15" s="90">
         <v>3383500</v>
       </c>
-      <c r="L15" s="122">
+      <c r="L15" s="90">
         <v>2682400</v>
       </c>
-      <c r="M15" s="122">
+      <c r="M15" s="90">
         <v>1283500</v>
       </c>
-      <c r="N15" s="122">
+      <c r="N15" s="90">
         <v>156200</v>
       </c>
-      <c r="O15" s="122">
+      <c r="O15" s="90">
         <v>4900</v>
       </c>
-      <c r="P15" s="122">
+      <c r="P15" s="90">
         <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
         <v>7510500</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="110"/>
-      <c r="B16" s="110"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="78"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="109"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
-      <c r="B17" s="110"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
+      <c r="A17" s="78"/>
+      <c r="B17" s="78"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="109"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="109"/>
-      <c r="O17" s="109"/>
-      <c r="P17" s="109"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="135" t="s">
+      <c r="A18" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="110" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="106">
+      <c r="D18" s="74">
         <v>716500</v>
       </c>
-      <c r="E18" s="106">
+      <c r="E18" s="74">
         <v>340700</v>
       </c>
-      <c r="F18" s="106">
+      <c r="F18" s="74">
         <v>141700</v>
       </c>
-      <c r="G18" s="106">
+      <c r="G18" s="74">
         <v>36000</v>
       </c>
-      <c r="H18" s="106">
+      <c r="H18" s="74">
         <v>4600</v>
       </c>
-      <c r="I18" s="106">
+      <c r="I18" s="74">
         <f t="shared" si="0"/>
         <v>1239500</v>
       </c>
       <c r="J18" s="8"/>
-      <c r="K18" s="109">
+      <c r="K18" s="77">
         <v>568900</v>
       </c>
-      <c r="L18" s="109">
+      <c r="L18" s="77">
         <v>258600</v>
       </c>
-      <c r="M18" s="109">
+      <c r="M18" s="77">
         <v>93100</v>
       </c>
-      <c r="N18" s="109">
+      <c r="N18" s="77">
         <v>21100</v>
       </c>
-      <c r="O18" s="109">
+      <c r="O18" s="77">
         <v>2200</v>
       </c>
-      <c r="P18" s="109">
+      <c r="P18" s="77">
         <f t="shared" si="1"/>
         <v>943900</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="135"/>
-      <c r="B19" s="110" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="106">
+      <c r="A19" s="104"/>
+      <c r="B19" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="74">
         <v>1289300</v>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="74">
         <v>787600</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="74">
         <v>383200</v>
       </c>
-      <c r="G19" s="106">
+      <c r="G19" s="74">
         <v>74300</v>
       </c>
-      <c r="H19" s="106">
+      <c r="H19" s="74">
         <v>13200</v>
       </c>
-      <c r="I19" s="106">
+      <c r="I19" s="74">
         <f t="shared" si="0"/>
         <v>2547600</v>
       </c>
       <c r="J19" s="8"/>
-      <c r="K19" s="109">
+      <c r="K19" s="77">
         <v>1058400</v>
       </c>
-      <c r="L19" s="109">
+      <c r="L19" s="77">
         <v>609100</v>
       </c>
-      <c r="M19" s="109">
+      <c r="M19" s="77">
         <v>175500</v>
       </c>
-      <c r="N19" s="109">
+      <c r="N19" s="77">
         <v>32000</v>
       </c>
-      <c r="O19" s="109">
+      <c r="O19" s="77">
         <v>7700</v>
       </c>
-      <c r="P19" s="109">
+      <c r="P19" s="77">
         <f t="shared" si="1"/>
         <v>1882700</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="78"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="109"/>
-      <c r="P20" s="109"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="110"/>
-      <c r="B21" s="110"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="78"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="135" t="s">
+      <c r="A22" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="110" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="106">
+      <c r="D22" s="74">
         <v>303900</v>
       </c>
-      <c r="E22" s="106">
+      <c r="E22" s="74">
         <v>69900</v>
       </c>
-      <c r="F22" s="106">
+      <c r="F22" s="74">
         <v>3900</v>
       </c>
-      <c r="G22" s="106">
+      <c r="G22" s="74">
         <v>0</v>
       </c>
-      <c r="H22" s="106">
+      <c r="H22" s="74">
         <v>0</v>
       </c>
-      <c r="I22" s="106">
+      <c r="I22" s="74">
         <f t="shared" si="0"/>
         <v>377700</v>
       </c>
       <c r="J22" s="8"/>
-      <c r="K22" s="109">
+      <c r="K22" s="77">
         <v>123200</v>
       </c>
-      <c r="L22" s="109">
+      <c r="L22" s="77">
         <v>17600</v>
       </c>
-      <c r="M22" s="109">
+      <c r="M22" s="77">
         <v>400</v>
       </c>
-      <c r="N22" s="109">
+      <c r="N22" s="77">
         <v>0</v>
       </c>
-      <c r="O22" s="109">
+      <c r="O22" s="77">
         <v>0</v>
       </c>
-      <c r="P22" s="109">
+      <c r="P22" s="77">
         <f t="shared" si="1"/>
         <v>141200</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="135"/>
-      <c r="B23" s="110" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="106">
+      <c r="A23" s="104"/>
+      <c r="B23" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="74">
         <v>419800</v>
       </c>
-      <c r="E23" s="106">
+      <c r="E23" s="74">
         <v>51900</v>
       </c>
-      <c r="F23" s="106">
+      <c r="F23" s="74">
         <v>3000</v>
       </c>
-      <c r="G23" s="106">
+      <c r="G23" s="74">
         <v>700</v>
       </c>
-      <c r="H23" s="106">
+      <c r="H23" s="74">
         <v>0</v>
       </c>
-      <c r="I23" s="106">
+      <c r="I23" s="74">
         <f t="shared" si="0"/>
         <v>475400</v>
       </c>
       <c r="J23" s="8"/>
-      <c r="K23" s="109">
+      <c r="K23" s="77">
         <v>121500</v>
       </c>
-      <c r="L23" s="109">
+      <c r="L23" s="77">
         <v>10900</v>
       </c>
-      <c r="M23" s="109">
+      <c r="M23" s="77">
         <v>400</v>
       </c>
-      <c r="N23" s="109">
+      <c r="N23" s="77">
         <v>0</v>
       </c>
-      <c r="O23" s="109">
+      <c r="O23" s="77">
         <v>0</v>
       </c>
-      <c r="P23" s="109">
+      <c r="P23" s="77">
         <f t="shared" si="1"/>
         <v>132800</v>
       </c>
@@ -2359,43 +2522,43 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="134" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="134"/>
+      <c r="A32" s="103" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="103"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="110"/>
-      <c r="C34" s="106" t="s">
+      <c r="B34" s="78"/>
+      <c r="C34" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="109" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="110" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="106">
+      <c r="B35" s="78" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="74">
         <f>I15</f>
         <v>10398200</v>
       </c>
-      <c r="D35" s="109">
+      <c r="D35" s="77">
         <f>P15</f>
         <v>7510500</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="106">
+      <c r="B36" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="74">
         <f>'Agglomeration road'!C18</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="D36" s="109">
+      <c r="D36" s="77">
         <f>'Agglomeration road'!C19</f>
         <v>15021000</v>
       </c>
@@ -2405,36 +2568,36 @@
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="96" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" s="85" t="s">
-        <v>128</v>
+      <c r="C38" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="124">
+      <c r="B39" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="92">
         <f>'Agglomeration road'!C79</f>
         <v>27420.859000423719</v>
       </c>
-      <c r="D39" s="126">
-        <f>'Agglomeration road'!D79</f>
+      <c r="D39" s="94">
+        <f>'Agglomeration road'!F79</f>
         <v>308626.30242553435</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="125">
+      <c r="B40" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="93">
         <f>'Agglomeration road'!C80</f>
         <v>1919460130.0296605</v>
       </c>
-      <c r="D40" s="127">
-        <f>'Agglomeration road'!D80</f>
+      <c r="D40" s="95">
+        <f>'Agglomeration road'!F80</f>
         <v>21603841169.787403</v>
       </c>
     </row>
@@ -2489,15 +2652,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="133"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -2506,417 +2669,417 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="134" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="134"/>
+      <c r="A10" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="103"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="110" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="110" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="136" t="s">
+      <c r="A12" s="78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="K12" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="136"/>
-      <c r="K12" s="132" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="132"/>
-      <c r="O12" s="132"/>
-      <c r="P12" s="132"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
-      <c r="B13" s="110"/>
-      <c r="D13" s="104" t="s">
+      <c r="A13" s="78"/>
+      <c r="B13" s="78"/>
+      <c r="D13" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="104" t="s">
+      <c r="H13" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="104" t="s">
+      <c r="I13" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="G13" s="104" t="s">
+      <c r="L13" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="104" t="s">
+      <c r="M13" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="105" t="s">
+      <c r="N13" s="75" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="P13" s="76" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="107" t="s">
-        <v>115</v>
-      </c>
-      <c r="L13" s="107" t="s">
-        <v>116</v>
-      </c>
-      <c r="M13" s="107" t="s">
-        <v>117</v>
-      </c>
-      <c r="N13" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="O13" s="107" t="s">
-        <v>119</v>
-      </c>
-      <c r="P13" s="108" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="135" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="106">
+      <c r="D14" s="74">
         <v>3725500</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="74">
         <v>1643600</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="74">
         <v>998600</v>
       </c>
-      <c r="G14" s="106">
+      <c r="G14" s="74">
         <v>481900</v>
       </c>
-      <c r="H14" s="106">
+      <c r="H14" s="74">
         <v>33500</v>
       </c>
-      <c r="I14" s="106">
+      <c r="I14" s="74">
         <f>SUM(D14:H14)</f>
         <v>6883100</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="109">
+      <c r="K14" s="77">
         <v>2411700</v>
       </c>
-      <c r="L14" s="109">
+      <c r="L14" s="77">
         <v>1244300</v>
       </c>
-      <c r="M14" s="109">
+      <c r="M14" s="77">
         <v>574000</v>
       </c>
-      <c r="N14" s="109">
+      <c r="N14" s="77">
         <v>54400</v>
       </c>
-      <c r="O14" s="109">
+      <c r="O14" s="77">
         <v>2100</v>
       </c>
-      <c r="P14" s="109">
+      <c r="P14" s="77">
         <f>SUM(K14:O14)</f>
         <v>4286500</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="135"/>
-      <c r="B15" s="111" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="113">
+      <c r="A15" s="104"/>
+      <c r="B15" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="80"/>
+      <c r="D15" s="81">
         <v>3762100</v>
       </c>
-      <c r="E15" s="113">
+      <c r="E15" s="81">
         <v>3050900</v>
       </c>
-      <c r="F15" s="113">
+      <c r="F15" s="81">
         <v>2479000</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="81">
         <v>1006400</v>
       </c>
-      <c r="H15" s="113">
+      <c r="H15" s="81">
         <v>99800</v>
       </c>
-      <c r="I15" s="113">
+      <c r="I15" s="81">
         <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
         <v>10398200</v>
       </c>
-      <c r="J15" s="114"/>
-      <c r="K15" s="115">
+      <c r="J15" s="82"/>
+      <c r="K15" s="83">
         <v>3383500</v>
       </c>
-      <c r="L15" s="115">
+      <c r="L15" s="83">
         <v>2682400</v>
       </c>
-      <c r="M15" s="115">
+      <c r="M15" s="83">
         <v>1283500</v>
       </c>
-      <c r="N15" s="115">
+      <c r="N15" s="83">
         <v>156200</v>
       </c>
-      <c r="O15" s="115">
+      <c r="O15" s="83">
         <v>4900</v>
       </c>
-      <c r="P15" s="116">
+      <c r="P15" s="84">
         <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
         <v>7510500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="110"/>
-      <c r="B16" s="110"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="78"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="109"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
-      <c r="B17" s="110"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
+      <c r="A17" s="78"/>
+      <c r="B17" s="78"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="109"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="109"/>
-      <c r="O17" s="109"/>
-      <c r="P17" s="109"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="135" t="s">
+      <c r="A18" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="110" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="106">
+      <c r="D18" s="74">
         <v>716500</v>
       </c>
-      <c r="E18" s="106">
+      <c r="E18" s="74">
         <v>340700</v>
       </c>
-      <c r="F18" s="106">
+      <c r="F18" s="74">
         <v>141700</v>
       </c>
-      <c r="G18" s="106">
+      <c r="G18" s="74">
         <v>36000</v>
       </c>
-      <c r="H18" s="106">
+      <c r="H18" s="74">
         <v>4600</v>
       </c>
-      <c r="I18" s="106">
+      <c r="I18" s="74">
         <f t="shared" si="0"/>
         <v>1239500</v>
       </c>
       <c r="J18" s="8"/>
-      <c r="K18" s="109">
+      <c r="K18" s="77">
         <v>568900</v>
       </c>
-      <c r="L18" s="109">
+      <c r="L18" s="77">
         <v>258600</v>
       </c>
-      <c r="M18" s="109">
+      <c r="M18" s="77">
         <v>93100</v>
       </c>
-      <c r="N18" s="109">
+      <c r="N18" s="77">
         <v>21100</v>
       </c>
-      <c r="O18" s="109">
+      <c r="O18" s="77">
         <v>2200</v>
       </c>
-      <c r="P18" s="109">
+      <c r="P18" s="77">
         <f t="shared" si="1"/>
         <v>943900</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="135"/>
-      <c r="B19" s="110" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="106">
+      <c r="A19" s="104"/>
+      <c r="B19" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="74">
         <v>1289300</v>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="74">
         <v>787600</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="74">
         <v>383200</v>
       </c>
-      <c r="G19" s="106">
+      <c r="G19" s="74">
         <v>74300</v>
       </c>
-      <c r="H19" s="106">
+      <c r="H19" s="74">
         <v>13200</v>
       </c>
-      <c r="I19" s="106">
+      <c r="I19" s="74">
         <f t="shared" si="0"/>
         <v>2547600</v>
       </c>
       <c r="J19" s="8"/>
-      <c r="K19" s="109">
+      <c r="K19" s="77">
         <v>1058400</v>
       </c>
-      <c r="L19" s="109">
+      <c r="L19" s="77">
         <v>609100</v>
       </c>
-      <c r="M19" s="109">
+      <c r="M19" s="77">
         <v>175500</v>
       </c>
-      <c r="N19" s="109">
+      <c r="N19" s="77">
         <v>32000</v>
       </c>
-      <c r="O19" s="109">
+      <c r="O19" s="77">
         <v>7700</v>
       </c>
-      <c r="P19" s="109">
+      <c r="P19" s="77">
         <f t="shared" si="1"/>
         <v>1882700</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="110"/>
-      <c r="B20" s="110"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="78"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="109"/>
-      <c r="P20" s="109"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="110"/>
-      <c r="B21" s="110"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="78"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="135" t="s">
+      <c r="A22" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="110" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="106">
+      <c r="D22" s="74">
         <v>303900</v>
       </c>
-      <c r="E22" s="106">
+      <c r="E22" s="74">
         <v>69900</v>
       </c>
-      <c r="F22" s="106">
+      <c r="F22" s="74">
         <v>3900</v>
       </c>
-      <c r="G22" s="106">
+      <c r="G22" s="74">
         <v>0</v>
       </c>
-      <c r="H22" s="106">
+      <c r="H22" s="74">
         <v>0</v>
       </c>
-      <c r="I22" s="106">
+      <c r="I22" s="74">
         <f t="shared" si="0"/>
         <v>377700</v>
       </c>
       <c r="J22" s="8"/>
-      <c r="K22" s="109">
+      <c r="K22" s="77">
         <v>123200</v>
       </c>
-      <c r="L22" s="109">
+      <c r="L22" s="77">
         <v>17600</v>
       </c>
-      <c r="M22" s="109">
+      <c r="M22" s="77">
         <v>400</v>
       </c>
-      <c r="N22" s="109">
+      <c r="N22" s="77">
         <v>0</v>
       </c>
-      <c r="O22" s="109">
+      <c r="O22" s="77">
         <v>0</v>
       </c>
-      <c r="P22" s="109">
+      <c r="P22" s="77">
         <f t="shared" si="1"/>
         <v>141200</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="135"/>
-      <c r="B23" s="110" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="106">
+      <c r="A23" s="104"/>
+      <c r="B23" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="74">
         <v>419800</v>
       </c>
-      <c r="E23" s="106">
+      <c r="E23" s="74">
         <v>51900</v>
       </c>
-      <c r="F23" s="106">
+      <c r="F23" s="74">
         <v>3000</v>
       </c>
-      <c r="G23" s="106">
+      <c r="G23" s="74">
         <v>700</v>
       </c>
-      <c r="H23" s="106">
+      <c r="H23" s="74">
         <v>0</v>
       </c>
-      <c r="I23" s="106">
+      <c r="I23" s="74">
         <f t="shared" si="0"/>
         <v>475400</v>
       </c>
       <c r="J23" s="8"/>
-      <c r="K23" s="109">
+      <c r="K23" s="77">
         <v>121500</v>
       </c>
-      <c r="L23" s="109">
+      <c r="L23" s="77">
         <v>10900</v>
       </c>
-      <c r="M23" s="109">
+      <c r="M23" s="77">
         <v>400</v>
       </c>
-      <c r="N23" s="109">
+      <c r="N23" s="77">
         <v>0</v>
       </c>
-      <c r="O23" s="109">
+      <c r="O23" s="77">
         <v>0</v>
       </c>
-      <c r="P23" s="109">
+      <c r="P23" s="77">
         <f t="shared" si="1"/>
         <v>132800</v>
       </c>
@@ -2928,43 +3091,43 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="134" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="134"/>
+      <c r="A32" s="103" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="103"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="110"/>
-      <c r="C34" s="106" t="s">
+      <c r="B34" s="78"/>
+      <c r="C34" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="109" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="110" t="s">
-        <v>148</v>
-      </c>
-      <c r="C35" s="106">
+      <c r="B35" s="78" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="74">
         <f>I15</f>
         <v>10398200</v>
       </c>
-      <c r="D35" s="109">
+      <c r="D35" s="77">
         <f>P15</f>
         <v>7510500</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="106">
+      <c r="B36" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="74">
         <f>'Agglomeration road'!C18</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="D36" s="109">
+      <c r="D36" s="77">
         <f>'Agglomeration road'!C19</f>
         <v>15021000</v>
       </c>
@@ -2974,45 +3137,45 @@
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="96" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" s="85" t="s">
-        <v>128</v>
+      <c r="C38" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="128" t="s">
-        <v>149</v>
-      </c>
-      <c r="D39" s="129" t="s">
-        <v>149</v>
+      <c r="B39" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="96" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" s="97" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="130" t="s">
-        <v>149</v>
-      </c>
-      <c r="D40" s="131" t="s">
-        <v>149</v>
+      <c r="B40" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="98" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="99" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3020,9 +3183,622 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15698A58-3E8E-41FA-BD4E-8629DEE5CB3E}">
+  <dimension ref="A1:P38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="117"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="K12" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+    </row>
+    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="78"/>
+      <c r="B13" s="78"/>
+      <c r="D13" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="75" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="N13" s="75" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="P13" s="76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="74">
+        <v>3725500</v>
+      </c>
+      <c r="E14" s="74">
+        <v>1643600</v>
+      </c>
+      <c r="F14" s="74">
+        <v>998600</v>
+      </c>
+      <c r="G14" s="74">
+        <v>481900</v>
+      </c>
+      <c r="H14" s="74">
+        <v>33500</v>
+      </c>
+      <c r="I14" s="74">
+        <f>SUM(D14:H14)</f>
+        <v>6883100</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="77">
+        <v>2411700</v>
+      </c>
+      <c r="L14" s="77">
+        <v>1244300</v>
+      </c>
+      <c r="M14" s="77">
+        <v>574000</v>
+      </c>
+      <c r="N14" s="77">
+        <v>54400</v>
+      </c>
+      <c r="O14" s="77">
+        <v>2100</v>
+      </c>
+      <c r="P14" s="77">
+        <f>SUM(K14:O14)</f>
+        <v>4286500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="104"/>
+      <c r="B15" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="80"/>
+      <c r="D15" s="81">
+        <v>3762100</v>
+      </c>
+      <c r="E15" s="81">
+        <v>3050900</v>
+      </c>
+      <c r="F15" s="81">
+        <v>2479000</v>
+      </c>
+      <c r="G15" s="81">
+        <v>1006400</v>
+      </c>
+      <c r="H15" s="81">
+        <v>99800</v>
+      </c>
+      <c r="I15" s="81">
+        <f t="shared" ref="I15:I23" si="0">SUM(D15:H15)</f>
+        <v>10398200</v>
+      </c>
+      <c r="J15" s="82"/>
+      <c r="K15" s="83">
+        <v>3383500</v>
+      </c>
+      <c r="L15" s="83">
+        <v>2682400</v>
+      </c>
+      <c r="M15" s="83">
+        <v>1283500</v>
+      </c>
+      <c r="N15" s="83">
+        <v>156200</v>
+      </c>
+      <c r="O15" s="83">
+        <v>4900</v>
+      </c>
+      <c r="P15" s="84">
+        <f t="shared" ref="P15:P23" si="1">SUM(K15:O15)</f>
+        <v>7510500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="78"/>
+      <c r="B16" s="78"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="78"/>
+      <c r="B17" s="78"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="74">
+        <v>716500</v>
+      </c>
+      <c r="E18" s="74">
+        <v>340700</v>
+      </c>
+      <c r="F18" s="74">
+        <v>141700</v>
+      </c>
+      <c r="G18" s="74">
+        <v>36000</v>
+      </c>
+      <c r="H18" s="74">
+        <v>4600</v>
+      </c>
+      <c r="I18" s="74">
+        <f t="shared" si="0"/>
+        <v>1239500</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="77">
+        <v>568900</v>
+      </c>
+      <c r="L18" s="77">
+        <v>258600</v>
+      </c>
+      <c r="M18" s="77">
+        <v>93100</v>
+      </c>
+      <c r="N18" s="77">
+        <v>21100</v>
+      </c>
+      <c r="O18" s="77">
+        <v>2200</v>
+      </c>
+      <c r="P18" s="77">
+        <f t="shared" si="1"/>
+        <v>943900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="104"/>
+      <c r="B19" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="74">
+        <v>1289300</v>
+      </c>
+      <c r="E19" s="74">
+        <v>787600</v>
+      </c>
+      <c r="F19" s="74">
+        <v>383200</v>
+      </c>
+      <c r="G19" s="74">
+        <v>74300</v>
+      </c>
+      <c r="H19" s="74">
+        <v>13200</v>
+      </c>
+      <c r="I19" s="74">
+        <f t="shared" si="0"/>
+        <v>2547600</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="77">
+        <v>1058400</v>
+      </c>
+      <c r="L19" s="77">
+        <v>609100</v>
+      </c>
+      <c r="M19" s="77">
+        <v>175500</v>
+      </c>
+      <c r="N19" s="77">
+        <v>32000</v>
+      </c>
+      <c r="O19" s="77">
+        <v>7700</v>
+      </c>
+      <c r="P19" s="77">
+        <f t="shared" si="1"/>
+        <v>1882700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="78"/>
+      <c r="B20" s="78"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="78"/>
+      <c r="B21" s="78"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="74">
+        <v>303900</v>
+      </c>
+      <c r="E22" s="74">
+        <v>69900</v>
+      </c>
+      <c r="F22" s="74">
+        <v>3900</v>
+      </c>
+      <c r="G22" s="74">
+        <v>0</v>
+      </c>
+      <c r="H22" s="74">
+        <v>0</v>
+      </c>
+      <c r="I22" s="74">
+        <f t="shared" si="0"/>
+        <v>377700</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="77">
+        <v>123200</v>
+      </c>
+      <c r="L22" s="77">
+        <v>17600</v>
+      </c>
+      <c r="M22" s="77">
+        <v>400</v>
+      </c>
+      <c r="N22" s="77">
+        <v>0</v>
+      </c>
+      <c r="O22" s="77">
+        <v>0</v>
+      </c>
+      <c r="P22" s="77">
+        <f t="shared" si="1"/>
+        <v>141200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="104"/>
+      <c r="B23" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="74">
+        <v>419800</v>
+      </c>
+      <c r="E23" s="74">
+        <v>51900</v>
+      </c>
+      <c r="F23" s="74">
+        <v>3000</v>
+      </c>
+      <c r="G23" s="74">
+        <v>700</v>
+      </c>
+      <c r="H23" s="74">
+        <v>0</v>
+      </c>
+      <c r="I23" s="74">
+        <f t="shared" si="0"/>
+        <v>475400</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="77">
+        <v>121500</v>
+      </c>
+      <c r="L23" s="77">
+        <v>10900</v>
+      </c>
+      <c r="M23" s="77">
+        <v>400</v>
+      </c>
+      <c r="N23" s="77">
+        <v>0</v>
+      </c>
+      <c r="O23" s="77">
+        <v>0</v>
+      </c>
+      <c r="P23" s="77">
+        <f t="shared" si="1"/>
+        <v>132800</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="103"/>
+    </row>
+    <row r="29" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="78"/>
+      <c r="B30" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="77" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="189" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="74">
+        <f>I15</f>
+        <v>10398200</v>
+      </c>
+      <c r="C31" s="77">
+        <f>P15</f>
+        <v>7510500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="189" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="74">
+        <f>'Agglomeration road'!C18</f>
+        <v>20796420.796399999</v>
+      </c>
+      <c r="C32" s="77">
+        <f>'Agglomeration road'!C19</f>
+        <v>15021000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="188" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="187" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="187" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="187" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="187" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="188" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" s="186" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="188" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="D36" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="186" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="188" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="186" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="188" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="186" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:U88"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -3049,13 +3825,13 @@
     <row r="2" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3080,7 +3856,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2">
         <v>1.4250000000000001E-3</v>
@@ -3103,7 +3879,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2">
         <v>8.5990000000000007E-3</v>
@@ -3134,35 +3910,35 @@
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" s="6">
         <f>Frontend!$I$15*C8</f>
@@ -3195,7 +3971,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="6">
         <f>Frontend!$P$15*C9</f>
@@ -3227,17 +4003,17 @@
     </row>
     <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="8">
         <f>Frontend!$I$15+I13</f>
@@ -3246,7 +4022,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="8">
         <f>Frontend!$P$15+I14</f>
@@ -3255,82 +4031,82 @@
     </row>
     <row r="22" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
         <v>36</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>37</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>38</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>39</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" t="s">
+        <v>41</v>
+      </c>
+      <c r="K29" t="s">
+        <v>42</v>
+      </c>
+      <c r="L29" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" t="s">
         <v>40</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H29" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29" t="s">
-        <v>79</v>
-      </c>
-      <c r="J29" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" t="s">
-        <v>43</v>
-      </c>
-      <c r="L29" t="s">
-        <v>64</v>
-      </c>
-      <c r="M29" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
         <v>45</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>46</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>47</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" t="s">
         <v>48</v>
       </c>
-      <c r="G30" t="s">
-        <v>152</v>
-      </c>
-      <c r="H30" t="s">
-        <v>49</v>
-      </c>
-      <c r="I30" s="27">
+      <c r="I30" s="26">
         <v>45</v>
       </c>
       <c r="J30">
@@ -3343,32 +4119,32 @@
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
         <v>45</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>46</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>47</v>
       </c>
-      <c r="F31" t="s">
-        <v>48</v>
-      </c>
       <c r="G31" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H31" t="s">
-        <v>52</v>
-      </c>
-      <c r="I31" s="27">
+        <v>51</v>
+      </c>
+      <c r="I31" s="26">
         <v>40</v>
       </c>
       <c r="J31">
@@ -3381,32 +4157,32 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
         <v>54</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>55</v>
       </c>
-      <c r="D32" t="s">
-        <v>56</v>
-      </c>
       <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" t="s">
         <v>47</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" t="s">
         <v>48</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H32" t="s">
-        <v>49</v>
-      </c>
-      <c r="I32" s="27">
+      <c r="I32" s="26">
         <v>45</v>
       </c>
       <c r="K32">
@@ -3416,30 +4192,30 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" t="s">
         <v>55</v>
       </c>
-      <c r="D33" t="s">
-        <v>56</v>
-      </c>
       <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
         <v>47</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H33" t="s">
         <v>48</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" t="s">
-        <v>49</v>
       </c>
       <c r="I33">
         <v>45</v>
@@ -3451,30 +4227,30 @@
         <v>1</v>
       </c>
       <c r="M33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>60</v>
-      </c>
       <c r="C34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" t="s">
         <v>55</v>
       </c>
-      <c r="D34" t="s">
-        <v>56</v>
-      </c>
       <c r="E34" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" t="s">
         <v>47</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="H34" t="s">
         <v>48</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H34" t="s">
-        <v>49</v>
       </c>
       <c r="I34">
         <v>45</v>
@@ -3486,30 +4262,30 @@
         <v>1</v>
       </c>
       <c r="M34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" t="s">
         <v>55</v>
       </c>
-      <c r="D35" t="s">
-        <v>56</v>
-      </c>
       <c r="E35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" t="s">
         <v>47</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H35" t="s">
         <v>48</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H35" t="s">
-        <v>49</v>
       </c>
       <c r="I35">
         <v>53</v>
@@ -3521,1040 +4297,1122 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="G40" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="136"/>
+      <c r="I40" s="136"/>
+      <c r="J40" s="136"/>
+      <c r="K40" s="136"/>
+      <c r="L40" s="136"/>
+      <c r="M40" s="126" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C40" s="15"/>
-      <c r="E40" s="137" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="137"/>
-      <c r="I40" s="137"/>
-      <c r="J40" s="137"/>
-      <c r="K40" s="138" t="s">
-        <v>83</v>
-      </c>
-      <c r="L40" s="139"/>
-      <c r="M40" s="139"/>
-      <c r="N40" s="139"/>
-      <c r="O40" s="139"/>
-    </row>
-    <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="D41" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="64" t="s">
+      <c r="N40" s="106"/>
+      <c r="O40" s="106"/>
+      <c r="P40" s="106"/>
+      <c r="Q40" s="106"/>
+    </row>
+    <row r="41" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="F41" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="I41" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="72" t="s">
+        <v>104</v>
+      </c>
+      <c r="K41" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="L41" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="F41" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="H41" s="64" t="s">
+      <c r="M41" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="N41" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="O41" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="K41" s="49" t="s">
+      <c r="P41" s="128" t="s">
         <v>110</v>
       </c>
-      <c r="L41" s="50" t="s">
+      <c r="Q41" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="M41" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="N41" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="O41" s="50" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="144" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="43" t="s">
-        <v>78</v>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A42" s="113" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>77</v>
       </c>
       <c r="C42" s="18"/>
-      <c r="D42" s="29">
-        <f>SUM(E42:O42)</f>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="28">
+        <f>SUM(G42:Q42)</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="E42" s="65">
-        <f t="shared" ref="E42:J42" si="0">C13</f>
+      <c r="G42" s="137">
+        <f>C13</f>
         <v>14817.435000000001</v>
       </c>
-      <c r="F42" s="65">
-        <f t="shared" si="0"/>
+      <c r="H42" s="137">
+        <f>D13</f>
         <v>43360.493999999999</v>
       </c>
-      <c r="G42" s="65">
-        <f t="shared" si="0"/>
+      <c r="I42" s="137">
+        <f>E13</f>
         <v>175282.45740000001</v>
       </c>
-      <c r="H42" s="65">
-        <f t="shared" si="0"/>
+      <c r="J42" s="137">
+        <f>F13</f>
         <v>708356.57860000001</v>
       </c>
-      <c r="I42" s="65">
-        <f t="shared" si="0"/>
+      <c r="K42" s="137">
+        <f>G13</f>
         <v>2895888.3018</v>
       </c>
-      <c r="J42" s="65">
-        <f t="shared" si="0"/>
+      <c r="L42" s="137">
+        <f>H13</f>
         <v>6560515.5296</v>
       </c>
-      <c r="K42" s="51">
+      <c r="M42" s="129">
         <f>Frontend!D15</f>
         <v>3762100</v>
       </c>
-      <c r="L42" s="52">
+      <c r="N42" s="53">
         <f>Frontend!E15</f>
         <v>3050900</v>
       </c>
-      <c r="M42" s="52">
+      <c r="O42" s="53">
         <f>Frontend!F15</f>
         <v>2479000</v>
       </c>
-      <c r="N42" s="52">
+      <c r="P42" s="53">
         <f>Frontend!G15</f>
         <v>1006400</v>
       </c>
-      <c r="O42" s="52">
+      <c r="Q42" s="53">
         <f>Frontend!H15</f>
         <v>99800</v>
       </c>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
       <c r="S42" s="8"/>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="145"/>
+      <c r="V42" s="8"/>
+      <c r="W42" s="8"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A43" s="114"/>
       <c r="B43" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="66">
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="138">
         <v>27</v>
       </c>
-      <c r="F43" s="66">
+      <c r="H43" s="138">
         <v>32</v>
       </c>
-      <c r="G43" s="66">
+      <c r="I43" s="138">
         <v>37</v>
       </c>
-      <c r="H43" s="66">
+      <c r="J43" s="138">
         <v>42</v>
       </c>
-      <c r="I43" s="66">
+      <c r="K43" s="138">
         <v>47</v>
       </c>
-      <c r="J43" s="66">
+      <c r="L43" s="138">
         <v>52</v>
       </c>
-      <c r="K43" s="53">
+      <c r="M43" s="130">
         <v>57</v>
       </c>
-      <c r="L43" s="54">
+      <c r="N43" s="54">
         <v>62</v>
       </c>
-      <c r="M43" s="54">
+      <c r="O43" s="54">
         <v>67</v>
       </c>
-      <c r="N43" s="54">
+      <c r="P43" s="54">
         <v>72</v>
       </c>
-      <c r="O43" s="55">
+      <c r="Q43" s="131">
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="146"/>
-      <c r="B44" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="66">
-        <f>E42/$D$42</f>
+    <row r="44" spans="1:23" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="115"/>
+      <c r="B44" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="139">
+        <f>G42/$F$42</f>
         <v>7.1249928750071259E-4</v>
       </c>
-      <c r="F44" s="66">
-        <f t="shared" ref="F44:O44" si="1">F42/$D$42</f>
+      <c r="H44" s="139">
+        <f t="shared" ref="H44:Q44" si="0">H42/$F$42</f>
         <v>2.0849979150020848E-3</v>
       </c>
-      <c r="G44" s="66">
-        <f t="shared" si="1"/>
+      <c r="I44" s="139">
+        <f t="shared" si="0"/>
         <v>8.4284915715084289E-3</v>
       </c>
-      <c r="H44" s="66">
-        <f t="shared" si="1"/>
+      <c r="J44" s="139">
+        <f t="shared" si="0"/>
         <v>3.4061465938534062E-2</v>
       </c>
-      <c r="I44" s="66">
-        <f t="shared" si="1"/>
+      <c r="K44" s="139">
+        <f t="shared" si="0"/>
         <v>0.13924936075063926</v>
       </c>
-      <c r="J44" s="66">
-        <f t="shared" si="1"/>
+      <c r="L44" s="139">
+        <f t="shared" si="0"/>
         <v>0.31546368453631546</v>
       </c>
-      <c r="K44" s="53">
-        <f t="shared" si="1"/>
+      <c r="M44" s="134">
+        <f t="shared" si="0"/>
         <v>0.18090132128174888</v>
       </c>
-      <c r="L44" s="54">
-        <f t="shared" si="1"/>
+      <c r="N44" s="57">
+        <f t="shared" si="0"/>
         <v>0.14670312886379619</v>
       </c>
-      <c r="M44" s="54">
-        <f t="shared" si="1"/>
+      <c r="O44" s="57">
+        <f t="shared" si="0"/>
         <v>0.11920320444896612</v>
       </c>
-      <c r="N44" s="54">
-        <f t="shared" si="1"/>
+      <c r="P44" s="57">
+        <f t="shared" si="0"/>
         <v>4.8392942701669828E-2</v>
       </c>
-      <c r="O44" s="54">
-        <f t="shared" si="1"/>
+      <c r="Q44" s="57">
+        <f t="shared" si="0"/>
         <v>4.7989027043190075E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="93" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="82" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
-      <c r="H45" s="67"/>
-      <c r="I45" s="67"/>
-      <c r="J45" s="67"/>
-      <c r="K45" s="56"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="57"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="57"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="144" t="s">
-        <v>54</v>
+    <row r="45" spans="1:23" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="100" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="118" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="160" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="161" t="s">
+        <v>167</v>
+      </c>
+      <c r="F45" s="152" t="s">
+        <v>125</v>
+      </c>
+      <c r="G45" s="138"/>
+      <c r="H45" s="138"/>
+      <c r="I45" s="138"/>
+      <c r="J45" s="138"/>
+      <c r="K45" s="138"/>
+      <c r="L45" s="138"/>
+      <c r="M45" s="130"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="54"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="190" t="s">
+        <v>53</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="91"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="67">
-        <f>IF(E43&gt;$I$32, EXP((LN(1.055)/10)*(E43-$I$32)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="F46" s="67">
-        <f t="shared" ref="F46:O46" si="2">IF(F43&gt;$I$32, EXP((LN(1.055)/10)*(F43-$I$32)),1)</f>
-        <v>1</v>
-      </c>
-      <c r="G46" s="67">
+        <v>99</v>
+      </c>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="153"/>
+      <c r="G46" s="140">
         <f>IF(G43&gt;$I$32, EXP((LN(1.055)/10)*(G43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="H46" s="67">
-        <f t="shared" si="2"/>
+      <c r="H46" s="140">
+        <f>IF(H43&gt;$I$32, EXP((LN(1.055)/10)*(H43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="I46" s="67">
-        <f t="shared" si="2"/>
+      <c r="I46" s="140">
+        <f>IF(I43&gt;$I$32, EXP((LN(1.055)/10)*(I43-$I$32)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="J46" s="140">
+        <f>IF(J43&gt;$I$32, EXP((LN(1.055)/10)*(J43-$I$32)),1)</f>
+        <v>1</v>
+      </c>
+      <c r="K46" s="140">
+        <f>IF(K43&gt;$I$32, EXP((LN(1.055)/10)*(K43-$I$32)),1)</f>
         <v>1.0107656908500073</v>
       </c>
-      <c r="J46" s="67">
-        <f t="shared" si="2"/>
+      <c r="L46" s="140">
+        <f>IF(L43&gt;$I$32, EXP((LN(1.055)/10)*(L43-$I$32)),1)</f>
         <v>1.0381897140207395</v>
       </c>
-      <c r="K46" s="56">
-        <f t="shared" si="2"/>
+      <c r="M46" s="132">
+        <f>IF(M43&gt;$I$32, EXP((LN(1.055)/10)*(M43-$I$32)),1)</f>
         <v>1.0663578038467578</v>
       </c>
-      <c r="L46" s="57">
-        <f t="shared" si="2"/>
+      <c r="N46" s="55">
+        <f>IF(N43&gt;$I$32, EXP((LN(1.055)/10)*(N43-$I$32)),1)</f>
         <v>1.09529014829188</v>
       </c>
-      <c r="M46" s="57">
-        <f t="shared" si="2"/>
+      <c r="O46" s="55">
+        <f>IF(O43&gt;$I$32, EXP((LN(1.055)/10)*(O43-$I$32)),1)</f>
         <v>1.1250074830583294</v>
       </c>
-      <c r="N46" s="57">
-        <f t="shared" si="2"/>
+      <c r="P46" s="55">
+        <f>IF(P43&gt;$I$32, EXP((LN(1.055)/10)*(P43-$I$32)),1)</f>
         <v>1.1555311064479334</v>
       </c>
-      <c r="O46" s="57">
-        <f t="shared" si="2"/>
+      <c r="Q46" s="55">
+        <f>IF(Q43&gt;$I$32, EXP((LN(1.055)/10)*(Q43-$I$32)),1)</f>
         <v>1.1868828946265373</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="145"/>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="191"/>
       <c r="B47" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" s="92">
-        <f>SUM(K47:O47)</f>
+        <v>80</v>
+      </c>
+      <c r="C47" s="68">
+        <f>SUM(M47:Q47)</f>
         <v>4.9308310609276644E-2</v>
       </c>
-      <c r="D47" s="83">
-        <f>SUM(E47:O47)</f>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="152">
+        <f>SUM(G47:Q47)</f>
         <v>6.2854894074549819E-2</v>
       </c>
-      <c r="E47" s="68">
-        <f>E44*(E46-1)</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="68">
-        <f t="shared" ref="F47:O47" si="3">F44*(F46-1)</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="68">
+      <c r="G47" s="141">
         <f>G44*(G46-1)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="68">
-        <f t="shared" si="3"/>
+      <c r="H47" s="141">
+        <f>H44*(H46-1)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="68">
-        <f t="shared" si="3"/>
+      <c r="I47" s="141">
+        <f>I44*(I46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="141">
+        <f>J44*(J46-1)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="141">
+        <f>K44*(K46-1)</f>
         <v>1.4991155689025278E-3</v>
       </c>
-      <c r="J47" s="68">
-        <f t="shared" si="3"/>
+      <c r="L47" s="141">
+        <f>L44*(L46-1)</f>
         <v>1.2047467896370654E-2</v>
       </c>
-      <c r="K47" s="58">
-        <f t="shared" si="3"/>
+      <c r="M47" s="133">
+        <f>M44*(M46-1)</f>
         <v>1.2004214393233608E-2</v>
       </c>
-      <c r="L47" s="59">
-        <f t="shared" si="3"/>
+      <c r="N47" s="56">
+        <f>N44*(N46-1)</f>
         <v>1.3979362904313918E-2</v>
       </c>
-      <c r="M47" s="59">
-        <f t="shared" si="3"/>
+      <c r="O47" s="56">
+        <f>O44*(O46-1)</f>
         <v>1.4901292560652712E-2</v>
       </c>
-      <c r="N47" s="59">
-        <f t="shared" si="3"/>
+      <c r="P47" s="56">
+        <f>P44*(P46-1)</f>
         <v>7.5266079226621535E-3</v>
       </c>
-      <c r="O47" s="59">
-        <f t="shared" si="3"/>
+      <c r="Q47" s="56">
+        <f>Q44*(Q46-1)</f>
         <v>8.9683282841425394E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="145"/>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="191"/>
       <c r="B48" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="92">
+        <v>100</v>
+      </c>
+      <c r="C48" s="68">
         <f>(C47)/(1+C47)</f>
         <v>4.6991251389828383E-2</v>
       </c>
-      <c r="D48" s="84">
-        <f>(D47)/(1+D47)</f>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="154">
+        <f>(F47)/(1+F47)</f>
         <v>5.9137794279320602E-2</v>
       </c>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="66"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="54"/>
+      <c r="G48" s="138"/>
+      <c r="H48" s="138"/>
+      <c r="I48" s="138"/>
+      <c r="J48" s="138"/>
+      <c r="K48" s="138"/>
+      <c r="L48" s="138"/>
+      <c r="M48" s="130"/>
       <c r="N48" s="54"/>
       <c r="O48" s="54"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="146"/>
-      <c r="B49" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="C49" s="103">
-        <f>0.2069215*C48*D42</f>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="192"/>
+      <c r="B49" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="151">
+        <f>0.2069215*C48*F42</f>
         <v>202214.00228176778</v>
       </c>
-      <c r="D49" s="102">
-        <f>0.2069215*D48*D42</f>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="155">
+        <f>0.2069215*F48*F42</f>
         <v>254483.32856966133</v>
       </c>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="60"/>
-      <c r="L49" s="61"/>
-      <c r="M49" s="61"/>
-      <c r="N49" s="61"/>
-      <c r="O49" s="61"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="144" t="s">
-        <v>58</v>
+      <c r="G49" s="139"/>
+      <c r="H49" s="139"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="139"/>
+      <c r="K49" s="139"/>
+      <c r="L49" s="139"/>
+      <c r="M49" s="134"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="57"/>
+      <c r="P49" s="57"/>
+      <c r="Q49" s="57"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="113" t="s">
+        <v>57</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="91"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="67">
-        <f>IF(E43&gt;$I$33, EXP((LN(1.032)/10)*(E43-$I$33)),1)</f>
+        <v>99</v>
+      </c>
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="153"/>
+      <c r="G50" s="140">
+        <f>IF(G43&gt;$I$33, EXP((LN(1.032)/10)*(G43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="F50" s="67">
-        <f t="shared" ref="F50:O50" si="4">IF(F43&gt;$I$33, EXP((LN(1.032)/10)*(F43-$I$33)),1)</f>
+      <c r="H50" s="140">
+        <f>IF(H43&gt;$I$33, EXP((LN(1.032)/10)*(H43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="G50" s="67">
-        <f t="shared" si="4"/>
+      <c r="I50" s="140">
+        <f>IF(I43&gt;$I$33, EXP((LN(1.032)/10)*(I43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="H50" s="67">
-        <f t="shared" si="4"/>
+      <c r="J50" s="140">
+        <f>IF(J43&gt;$I$33, EXP((LN(1.032)/10)*(J43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="I50" s="67">
-        <f t="shared" si="4"/>
+      <c r="K50" s="140">
+        <f>IF(K43&gt;$I$33, EXP((LN(1.032)/10)*(K43-$I$33)),1)</f>
         <v>1.0063196184673233</v>
       </c>
-      <c r="J50" s="67">
-        <f t="shared" si="4"/>
+      <c r="L50" s="140">
+        <f>IF(L43&gt;$I$33, EXP((LN(1.032)/10)*(L43-$I$33)),1)</f>
         <v>1.0222939440770498</v>
       </c>
-      <c r="K50" s="56">
-        <f t="shared" si="4"/>
+      <c r="M50" s="132">
+        <f>IF(M43&gt;$I$33, EXP((LN(1.032)/10)*(M43-$I$33)),1)</f>
         <v>1.0385218462582777</v>
       </c>
-      <c r="L50" s="57">
-        <f t="shared" si="4"/>
+      <c r="N50" s="55">
+        <f>IF(N43&gt;$I$33, EXP((LN(1.032)/10)*(N43-$I$33)),1)</f>
         <v>1.0550073502875155</v>
       </c>
-      <c r="M50" s="57">
-        <f t="shared" si="4"/>
+      <c r="O50" s="55">
+        <f>IF(O43&gt;$I$33, EXP((LN(1.032)/10)*(O43-$I$33)),1)</f>
         <v>1.0717545453385426</v>
       </c>
-      <c r="N50" s="57">
-        <f t="shared" si="4"/>
+      <c r="P50" s="55">
+        <f>IF(P43&gt;$I$33, EXP((LN(1.032)/10)*(P43-$I$33)),1)</f>
         <v>1.088767585496716</v>
       </c>
-      <c r="O50" s="57">
-        <f t="shared" si="4"/>
+      <c r="Q50" s="55">
+        <f>IF(Q43&gt;$I$33, EXP((LN(1.032)/10)*(Q43-$I$33)),1)</f>
         <v>1.1060506907893759</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="145"/>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="114"/>
       <c r="B51" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" s="92">
-        <f>SUM(K51:O51)</f>
+        <v>80</v>
+      </c>
+      <c r="C51" s="68">
+        <f>SUM(M51:Q51)</f>
         <v>2.8396426647685286E-2</v>
       </c>
-      <c r="D51" s="83">
-        <f>SUM(E51:O51)</f>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="152">
+        <f>SUM(G51:Q51)</f>
         <v>3.6309359220840685E-2</v>
       </c>
-      <c r="E51" s="66">
-        <f>E44*(E50-1)</f>
+      <c r="G51" s="138">
+        <f>G44*(G50-1)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="66">
-        <f t="shared" ref="F51:O51" si="5">F44*(F50-1)</f>
+      <c r="H51" s="138">
+        <f>H44*(H50-1)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="66">
-        <f t="shared" si="5"/>
+      <c r="I51" s="138">
+        <f>I44*(I50-1)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="66">
-        <f t="shared" si="5"/>
+      <c r="J51" s="138">
+        <f>J44*(J50-1)</f>
         <v>0</v>
       </c>
-      <c r="I51" s="66">
-        <f t="shared" si="5"/>
+      <c r="K51" s="138">
+        <f>K44*(K50-1)</f>
         <v>8.8000283176270673E-4</v>
       </c>
-      <c r="J51" s="66">
-        <f t="shared" si="5"/>
+      <c r="L51" s="138">
+        <f>L44*(L50-1)</f>
         <v>7.0329297413926854E-3</v>
       </c>
-      <c r="K51" s="53">
-        <f t="shared" si="5"/>
+      <c r="M51" s="130">
+        <f>M44*(M50-1)</f>
         <v>6.9686528863348307E-3</v>
       </c>
-      <c r="L51" s="54">
-        <f t="shared" si="5"/>
+      <c r="N51" s="54">
+        <f>N44*(N50-1)</f>
         <v>8.0697503976853574E-3</v>
       </c>
-      <c r="M51" s="54">
-        <f t="shared" si="5"/>
+      <c r="O51" s="54">
+        <f>O44*(O50-1)</f>
         <v>8.5533717381329078E-3</v>
       </c>
-      <c r="N51" s="54">
-        <f t="shared" si="5"/>
+      <c r="P51" s="54">
+        <f>P44*(P50-1)</f>
         <v>4.2957246787081573E-3</v>
       </c>
-      <c r="O51" s="54">
-        <f t="shared" si="5"/>
+      <c r="Q51" s="54">
+        <f>Q44*(Q50-1)</f>
         <v>5.0892694682403491E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="145"/>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="114"/>
       <c r="B52" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="92">
+        <v>100</v>
+      </c>
+      <c r="C52" s="68">
         <f>C51/(1+C51)</f>
         <v>2.7612335002223338E-2</v>
       </c>
-      <c r="D52" s="83">
-        <f>D51/(1+D51)</f>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="152">
+        <f>F51/(1+F51)</f>
         <v>3.503718160775874E-2</v>
       </c>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="66"/>
-      <c r="I52" s="66"/>
-      <c r="J52" s="66"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="54"/>
-      <c r="M52" s="54"/>
+      <c r="G52" s="138"/>
+      <c r="H52" s="138"/>
+      <c r="I52" s="138"/>
+      <c r="J52" s="138"/>
+      <c r="K52" s="138"/>
+      <c r="L52" s="138"/>
+      <c r="M52" s="130"/>
       <c r="N52" s="54"/>
       <c r="O52" s="54"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="146"/>
-      <c r="B53" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="100">
-        <f>0.0115708*C52*D42</f>
+      <c r="P52" s="54"/>
+      <c r="Q52" s="54"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="115"/>
+      <c r="B53" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="70">
+        <f>0.0115708*C52*F42</f>
         <v>6644.3900174318323</v>
       </c>
-      <c r="D53" s="101">
-        <f>0.0115708*D52*D42</f>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="156">
+        <f>0.0115708*F52*F42</f>
         <v>8431.0399571348571</v>
       </c>
-      <c r="E53" s="69"/>
-      <c r="F53" s="69"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="69"/>
-      <c r="I53" s="69"/>
-      <c r="J53" s="69"/>
-      <c r="K53" s="60"/>
-      <c r="L53" s="61"/>
-      <c r="M53" s="61"/>
-      <c r="N53" s="61"/>
-      <c r="O53" s="61"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="144" t="s">
-        <v>60</v>
+      <c r="G53" s="139"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
+      <c r="J53" s="139"/>
+      <c r="K53" s="139"/>
+      <c r="L53" s="139"/>
+      <c r="M53" s="134"/>
+      <c r="N53" s="57"/>
+      <c r="O53" s="57"/>
+      <c r="P53" s="57"/>
+      <c r="Q53" s="57"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="113" t="s">
+        <v>59</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="91"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="67">
-        <f>IF(E43&gt;$I$34, EXP((LN(1.062)/10)*(E43-$I$34)),1)</f>
+        <v>99</v>
+      </c>
+      <c r="C54" s="67"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="67"/>
+      <c r="F54" s="153"/>
+      <c r="G54" s="140">
+        <f>IF(G43&gt;$I$34, EXP((LN(1.062)/10)*(G43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="F54" s="67">
-        <f t="shared" ref="F54:O54" si="6">IF(F43&gt;$I$34, EXP((LN(1.062)/10)*(F43-$I$34)),1)</f>
+      <c r="H54" s="140">
+        <f>IF(H43&gt;$I$34, EXP((LN(1.062)/10)*(H43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="G54" s="67">
-        <f t="shared" si="6"/>
+      <c r="I54" s="140">
+        <f>IF(I43&gt;$I$34, EXP((LN(1.062)/10)*(I43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="H54" s="67">
-        <f t="shared" si="6"/>
+      <c r="J54" s="140">
+        <f>IF(J43&gt;$I$34, EXP((LN(1.062)/10)*(J43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="I54" s="67">
-        <f t="shared" si="6"/>
+      <c r="K54" s="140">
+        <f>IF(K43&gt;$I$34, EXP((LN(1.062)/10)*(K43-$I$34)),1)</f>
         <v>1.0121034455497457</v>
       </c>
-      <c r="J54" s="67">
-        <f t="shared" si="6"/>
+      <c r="L54" s="140">
+        <f>IF(L43&gt;$I$34, EXP((LN(1.062)/10)*(L43-$I$34)),1)</f>
         <v>1.043006852485771</v>
       </c>
-      <c r="K54" s="56">
-        <f t="shared" si="6"/>
+      <c r="M54" s="132">
+        <f>IF(M43&gt;$I$34, EXP((LN(1.062)/10)*(M43-$I$34)),1)</f>
         <v>1.0748538591738301</v>
       </c>
-      <c r="L54" s="57">
-        <f t="shared" si="6"/>
+      <c r="N54" s="55">
+        <f>IF(N43&gt;$I$34, EXP((LN(1.062)/10)*(N43-$I$34)),1)</f>
         <v>1.1076732773398887</v>
       </c>
-      <c r="M54" s="57">
-        <f t="shared" si="6"/>
+      <c r="O54" s="55">
+        <f>IF(O43&gt;$I$34, EXP((LN(1.062)/10)*(O43-$I$34)),1)</f>
         <v>1.1414947984426076</v>
       </c>
-      <c r="N54" s="57">
-        <f t="shared" si="6"/>
+      <c r="P54" s="55">
+        <f>IF(P43&gt;$I$34, EXP((LN(1.062)/10)*(P43-$I$34)),1)</f>
         <v>1.1763490205349618</v>
       </c>
-      <c r="O54" s="57">
-        <f t="shared" si="6"/>
+      <c r="Q54" s="55">
+        <f>IF(Q43&gt;$I$34, EXP((LN(1.062)/10)*(Q43-$I$34)),1)</f>
         <v>1.2122674759460494</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="145"/>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="114"/>
       <c r="B55" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="92">
-        <f>SUM(K55:O55)</f>
+        <v>80</v>
+      </c>
+      <c r="C55" s="68">
+        <f>SUM(M55:Q55)</f>
         <v>5.5756501106184665E-2</v>
       </c>
-      <c r="D55" s="83">
-        <f>SUM(E55:O55)</f>
+      <c r="D55" s="68"/>
+      <c r="E55" s="68"/>
+      <c r="F55" s="152">
+        <f>SUM(G55:Q55)</f>
         <v>7.1008998307338034E-2</v>
       </c>
-      <c r="E55" s="66">
-        <f>E44*(E54-1)</f>
+      <c r="G55" s="138">
+        <f>G44*(G54-1)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="66">
-        <f t="shared" ref="F55:O55" si="7">F44*(F54-1)</f>
+      <c r="H55" s="138">
+        <f>H44*(H54-1)</f>
         <v>0</v>
       </c>
-      <c r="G55" s="66">
-        <f t="shared" si="7"/>
+      <c r="I55" s="138">
+        <f>I44*(I54-1)</f>
         <v>0</v>
       </c>
-      <c r="H55" s="66">
-        <f t="shared" si="7"/>
+      <c r="J55" s="138">
+        <f>J44*(J54-1)</f>
         <v>0</v>
       </c>
-      <c r="I55" s="66">
-        <f t="shared" si="7"/>
+      <c r="K55" s="138">
+        <f>K44*(K54-1)</f>
         <v>1.6853970556822639E-3</v>
       </c>
-      <c r="J55" s="66">
-        <f t="shared" si="7"/>
+      <c r="L55" s="138">
+        <f>L44*(L54-1)</f>
         <v>1.3567100145471106E-2</v>
       </c>
-      <c r="K55" s="53">
-        <f t="shared" si="7"/>
+      <c r="M55" s="130">
+        <f>M44*(M54-1)</f>
         <v>1.3541162027583832E-2</v>
       </c>
-      <c r="L55" s="54">
-        <f t="shared" si="7"/>
+      <c r="N55" s="54">
+        <f>N44*(N54-1)</f>
         <v>1.5796006680780964E-2</v>
       </c>
-      <c r="M55" s="54">
-        <f t="shared" si="7"/>
+      <c r="O55" s="54">
+        <f>O44*(O54-1)</f>
         <v>1.6866633387219405E-2</v>
       </c>
-      <c r="N55" s="54">
-        <f t="shared" si="7"/>
+      <c r="P55" s="54">
+        <f>P44*(P54-1)</f>
         <v>8.5340480462440024E-3</v>
       </c>
-      <c r="O55" s="54">
-        <f t="shared" si="7"/>
+      <c r="Q55" s="54">
+        <f>Q44*(Q54-1)</f>
         <v>1.0186509643564665E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="145"/>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="114"/>
       <c r="B56" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" s="92">
+        <v>100</v>
+      </c>
+      <c r="C56" s="68">
         <f>C55/(1+C55)</f>
         <v>5.2811894644044302E-2</v>
       </c>
-      <c r="D56" s="83">
-        <f>D55/(1+D55)</f>
+      <c r="D56" s="68"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="152">
+        <f>F55/(1+F55)</f>
         <v>6.6301028674421281E-2</v>
       </c>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
-      <c r="J56" s="66"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="54"/>
-      <c r="M56" s="54"/>
+      <c r="G56" s="138"/>
+      <c r="H56" s="138"/>
+      <c r="I56" s="138"/>
+      <c r="J56" s="138"/>
+      <c r="K56" s="138"/>
+      <c r="L56" s="138"/>
+      <c r="M56" s="130"/>
       <c r="N56" s="54"/>
       <c r="O56" s="54"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="146"/>
-      <c r="B57" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" s="100">
-        <f>0.0059261*C56*D42</f>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="115"/>
+      <c r="B57" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="70">
+        <f>0.0059261*C56*F42</f>
         <v>6508.6260538531606</v>
       </c>
-      <c r="D57" s="101">
-        <f>0.0059261*D56*D42</f>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="156">
+        <f>0.0059261*F56*F42</f>
         <v>8171.0494489193279</v>
       </c>
-      <c r="E57" s="69"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="69"/>
-      <c r="J57" s="69"/>
-      <c r="K57" s="60"/>
-      <c r="L57" s="61"/>
-      <c r="M57" s="61"/>
-      <c r="N57" s="61"/>
-      <c r="O57" s="61"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="144" t="s">
-        <v>63</v>
+      <c r="G57" s="139"/>
+      <c r="H57" s="139"/>
+      <c r="I57" s="139"/>
+      <c r="J57" s="139"/>
+      <c r="K57" s="139"/>
+      <c r="L57" s="139"/>
+      <c r="M57" s="134"/>
+      <c r="N57" s="57"/>
+      <c r="O57" s="57"/>
+      <c r="P57" s="57"/>
+      <c r="Q57" s="57"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="113" t="s">
+        <v>62</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" s="94"/>
-      <c r="D58" s="90"/>
-      <c r="E58" s="67">
-        <f>IF(E43&gt;$I$35, EXP((LN(1.08)/10)*(E43-$I$35)),1)</f>
+        <v>99</v>
+      </c>
+      <c r="C58" s="150"/>
+      <c r="D58" s="162"/>
+      <c r="E58" s="168"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="140">
+        <f>IF(G43&gt;$I$35, EXP((LN(1.08)/10)*(G43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="F58" s="67">
-        <f t="shared" ref="F58:O58" si="8">IF(F43&gt;$I$35, EXP((LN(1.08)/10)*(F43-$I$35)),1)</f>
+      <c r="H58" s="140">
+        <f>IF(H43&gt;$I$35, EXP((LN(1.08)/10)*(H43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="G58" s="67">
-        <f t="shared" si="8"/>
+      <c r="I58" s="140">
+        <f>IF(I43&gt;$I$35, EXP((LN(1.08)/10)*(I43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="H58" s="67">
-        <f t="shared" si="8"/>
+      <c r="J58" s="140">
+        <f>IF(J43&gt;$I$35, EXP((LN(1.08)/10)*(J43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="I58" s="67">
-        <f t="shared" si="8"/>
+      <c r="K58" s="140">
+        <f>IF(K43&gt;$I$35, EXP((LN(1.08)/10)*(K43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="J58" s="67">
-        <f t="shared" si="8"/>
+      <c r="L58" s="140">
+        <f>IF(L43&gt;$I$35, EXP((LN(1.08)/10)*(L43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="K58" s="56">
-        <f t="shared" si="8"/>
+      <c r="M58" s="132">
+        <f>IF(M43&gt;$I$35, EXP((LN(1.08)/10)*(M43-$I$35)),1)</f>
         <v>1.0312631565524872</v>
       </c>
-      <c r="L58" s="57">
-        <f t="shared" si="8"/>
+      <c r="N58" s="55">
+        <f>IF(N43&gt;$I$35, EXP((LN(1.08)/10)*(N43-$I$35)),1)</f>
         <v>1.0717201098736591</v>
       </c>
-      <c r="M58" s="57">
-        <f t="shared" si="8"/>
+      <c r="O58" s="55">
+        <f>IF(O43&gt;$I$35, EXP((LN(1.08)/10)*(O43-$I$35)),1)</f>
         <v>1.1137642090766864</v>
       </c>
-      <c r="N58" s="57">
-        <f t="shared" si="8"/>
+      <c r="P58" s="55">
+        <f>IF(P43&gt;$I$35, EXP((LN(1.08)/10)*(P43-$I$35)),1)</f>
         <v>1.157457718663552</v>
       </c>
-      <c r="O58" s="57">
-        <f t="shared" si="8"/>
+      <c r="Q58" s="55">
+        <f>IF(Q43&gt;$I$35, EXP((LN(1.08)/10)*(Q43-$I$35)),1)</f>
         <v>1.2028653458028213</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="145"/>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="114"/>
       <c r="B59" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C59" s="95">
-        <f>SUM(K59:O59)</f>
+        <v>80</v>
+      </c>
+      <c r="C59" s="118">
+        <f>SUM(M59:Q59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="D59" s="92">
-        <f>SUM(E59:O59)</f>
+      <c r="D59" s="160">
+        <f>SUM(L59:Q59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="E59" s="66">
-        <f>E44*(E58-1)</f>
+      <c r="E59" s="161">
+        <f>SUM(G59:Q59)</f>
+        <v>3.8331542536053996E-2</v>
+      </c>
+      <c r="F59" s="68">
+        <f>SUM(G59:Q59)</f>
+        <v>3.8331542536053996E-2</v>
+      </c>
+      <c r="G59" s="138">
+        <f>G44*(G58-1)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="66">
-        <f t="shared" ref="F59:O59" si="9">F44*(F58-1)</f>
+      <c r="H59" s="138">
+        <f>H44*(H58-1)</f>
         <v>0</v>
       </c>
-      <c r="G59" s="66">
-        <f t="shared" si="9"/>
+      <c r="I59" s="138">
+        <f>I44*(I58-1)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="66">
-        <f t="shared" si="9"/>
+      <c r="J59" s="138">
+        <f>J44*(J58-1)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="66">
-        <f t="shared" si="9"/>
+      <c r="K59" s="138">
+        <f>K44*(K58-1)</f>
         <v>0</v>
       </c>
-      <c r="J59" s="66">
-        <f t="shared" si="9"/>
+      <c r="L59" s="138">
+        <f>L44*(L58-1)</f>
         <v>0</v>
       </c>
-      <c r="K59" s="53">
-        <f t="shared" si="9"/>
+      <c r="M59" s="130">
+        <f>M44*(M58-1)</f>
         <v>5.6555463277831062E-3</v>
       </c>
-      <c r="L59" s="54">
-        <f t="shared" si="9"/>
+      <c r="N59" s="54">
+        <f>N44*(N58-1)</f>
         <v>1.0521564520921027E-2</v>
       </c>
-      <c r="M59" s="54">
-        <f t="shared" si="9"/>
+      <c r="O59" s="54">
+        <f>O44*(O58-1)</f>
         <v>1.3561058273543175E-2</v>
       </c>
-      <c r="N59" s="54">
-        <f t="shared" si="9"/>
+      <c r="P59" s="54">
+        <f>P44*(P58-1)</f>
         <v>7.6198423572209177E-3</v>
       </c>
-      <c r="O59" s="54">
-        <f t="shared" si="9"/>
+      <c r="Q59" s="54">
+        <f>Q44*(Q58-1)</f>
         <v>9.7353105658576995E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="145"/>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="114"/>
       <c r="B60" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C60" s="95">
+        <v>100</v>
+      </c>
+      <c r="C60" s="118">
         <f>C59/(1+C59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="D60" s="92">
-        <f>D59/(1+D59)</f>
+      <c r="D60" s="160">
+        <f t="shared" ref="D60:E60" si="1">D59/(1+D59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="53"/>
-      <c r="L60" s="54"/>
-      <c r="M60" s="54"/>
+      <c r="E60" s="161">
+        <f t="shared" si="1"/>
+        <v>3.69164770266266E-2</v>
+      </c>
+      <c r="F60" s="68">
+        <f>F59/(1+F59)</f>
+        <v>3.69164770266266E-2</v>
+      </c>
+      <c r="G60" s="138"/>
+      <c r="H60" s="138"/>
+      <c r="I60" s="138"/>
+      <c r="J60" s="138"/>
+      <c r="K60" s="138"/>
+      <c r="L60" s="138"/>
+      <c r="M60" s="130"/>
       <c r="N60" s="54"/>
       <c r="O60" s="54"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="146"/>
-      <c r="B61" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="C61" s="99">
-        <f>0.00127695*C60*D42</f>
+      <c r="P60" s="54"/>
+      <c r="Q60" s="54"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="115"/>
+      <c r="B61" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" s="119">
+        <f>0.00127695*C60*$F$42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="D61" s="100">
-        <f>0.00127695*D60*D42</f>
+      <c r="D61" s="163">
+        <f t="shared" ref="D61:E61" si="2">0.00127695*D60*$F$42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="E61" s="69"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="60"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="61"/>
-      <c r="N61" s="61"/>
-      <c r="O61" s="61"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="142" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="96"/>
-      <c r="D62" s="85"/>
-      <c r="E62" s="70">
-        <f>IF(E43&gt;$I$30,((78.927 - 3.1162 * E43 + 0.0342 * E43^2)/100),0)</f>
+      <c r="E61" s="169">
+        <f t="shared" si="2"/>
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F61" s="70">
+        <f>0.00127695*F60*F42</f>
+        <v>980.35357762371382</v>
+      </c>
+      <c r="G61" s="139"/>
+      <c r="H61" s="139"/>
+      <c r="I61" s="139"/>
+      <c r="J61" s="139"/>
+      <c r="K61" s="139"/>
+      <c r="L61" s="139"/>
+      <c r="M61" s="134"/>
+      <c r="N61" s="57"/>
+      <c r="O61" s="57"/>
+      <c r="P61" s="57"/>
+      <c r="Q61" s="57"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="116"/>
+      <c r="D62" s="164"/>
+      <c r="E62" s="170"/>
+      <c r="F62" s="157"/>
+      <c r="G62" s="142">
+        <f>IF(G43&gt;$I$30,((78.927 - 3.1162 * G43 + 0.0342 * G43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="F62" s="70">
-        <f t="shared" ref="F62:O62" si="10">IF(F43&gt;$I$30,((78.927 - 3.1162 * F43 + 0.0342 * F43^2)/100),0)</f>
+      <c r="H62" s="142">
+        <f>IF(H43&gt;$I$30,((78.927 - 3.1162 * H43 + 0.0342 * H43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="G62" s="70">
-        <f t="shared" si="10"/>
+      <c r="I62" s="142">
+        <f>IF(I43&gt;$I$30,((78.927 - 3.1162 * I43 + 0.0342 * I43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="H62" s="70">
-        <f t="shared" si="10"/>
+      <c r="J62" s="142">
+        <f>IF(J43&gt;$I$30,((78.927 - 3.1162 * J43 + 0.0342 * J43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="I62" s="70">
-        <f t="shared" si="10"/>
+      <c r="K62" s="142">
+        <f>IF(K43&gt;$I$30,((78.927 - 3.1162 * K43 + 0.0342 * K43^2)/100),0)</f>
         <v>8.0134000000000191E-2</v>
       </c>
-      <c r="J62" s="70">
-        <f t="shared" si="10"/>
+      <c r="L62" s="142">
+        <f>IF(L43&gt;$I$30,((78.927 - 3.1162 * L43 + 0.0342 * L43^2)/100),0)</f>
         <v>9.3613999999999892E-2</v>
       </c>
-      <c r="K62" s="62">
-        <f t="shared" si="10"/>
+      <c r="M62" s="135">
+        <f>IF(M43&gt;$I$30,((78.927 - 3.1162 * M43 + 0.0342 * M43^2)/100),0)</f>
         <v>0.1241940000000001</v>
       </c>
-      <c r="L62" s="63">
-        <f t="shared" si="10"/>
+      <c r="N62" s="58">
+        <f>IF(N43&gt;$I$30,((78.927 - 3.1162 * N43 + 0.0342 * N43^2)/100),0)</f>
         <v>0.17187400000000011</v>
       </c>
-      <c r="M62" s="63">
-        <f t="shared" si="10"/>
+      <c r="O62" s="58">
+        <f>IF(O43&gt;$I$30,((78.927 - 3.1162 * O43 + 0.0342 * O43^2)/100),0)</f>
         <v>0.23665399999999978</v>
       </c>
-      <c r="N62" s="63">
-        <f t="shared" si="10"/>
+      <c r="P62" s="58">
+        <f>IF(P43&gt;$I$30,((78.927 - 3.1162 * P43 + 0.0342 * P43^2)/100),0)</f>
         <v>0.31853400000000021</v>
       </c>
-      <c r="O62" s="63">
-        <f t="shared" si="10"/>
+      <c r="Q62" s="58">
+        <f>IF(Q43&gt;$I$30,((78.927 - 3.1162 * Q43 + 0.0342 * Q43^2)/100),0)</f>
         <v>0.41751400000000016</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="143"/>
-      <c r="B63" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C63" s="96">
-        <f>SUM(K63:O63)</f>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="112"/>
+      <c r="B63" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" s="116">
+        <f>SUM(M63:Q63)</f>
         <v>9.3309634085492005E-2</v>
       </c>
-      <c r="D63" s="85">
-        <f>SUM(E63:O63)</f>
+      <c r="D63" s="164">
+        <f>SUM(L63:Q63)</f>
+        <v>0.12284145144967462</v>
+      </c>
+      <c r="E63" s="170">
+        <f>SUM(G63:Q63)</f>
         <v>0.13400005972406637</v>
       </c>
-      <c r="E63" s="71">
-        <f>E44*E62</f>
+      <c r="F63" s="157">
+        <f>SUM(G63:Q63)</f>
+        <v>0.13400005972406637</v>
+      </c>
+      <c r="G63" s="73">
+        <f>G44*G62</f>
         <v>0</v>
       </c>
-      <c r="F63" s="71">
-        <f t="shared" ref="F63:O63" si="11">F44*F62</f>
+      <c r="H63" s="73">
+        <f>H44*H62</f>
         <v>0</v>
       </c>
-      <c r="G63" s="71">
-        <f t="shared" si="11"/>
+      <c r="I63" s="73">
+        <f>I44*I62</f>
         <v>0</v>
       </c>
-      <c r="H63" s="71">
-        <f t="shared" si="11"/>
+      <c r="J63" s="73">
+        <f>J44*J62</f>
         <v>0</v>
       </c>
-      <c r="I63" s="71">
-        <f t="shared" si="11"/>
+      <c r="K63" s="73">
+        <f>K44*K62</f>
         <v>1.1158608274391753E-2</v>
       </c>
-      <c r="J63" s="71">
-        <f t="shared" si="11"/>
+      <c r="L63" s="73">
+        <f>L44*L62</f>
         <v>2.9531817364182603E-2</v>
       </c>
-      <c r="K63" s="53">
-        <f t="shared" si="11"/>
+      <c r="M63" s="130">
+        <f>M44*M62</f>
         <v>2.2466858695265539E-2</v>
       </c>
-      <c r="L63" s="54">
-        <f t="shared" si="11"/>
+      <c r="N63" s="54">
+        <f>N44*N62</f>
         <v>2.5214453570336123E-2</v>
       </c>
-      <c r="M63" s="54">
-        <f t="shared" si="11"/>
+      <c r="O63" s="54">
+        <f>O44*O62</f>
         <v>2.8209915145665603E-2</v>
       </c>
-      <c r="N63" s="54">
-        <f t="shared" si="11"/>
+      <c r="P63" s="54">
+        <f>P44*P62</f>
         <v>1.5414797610533706E-2</v>
       </c>
-      <c r="O63" s="54">
-        <f t="shared" si="11"/>
+      <c r="Q63" s="54">
+        <f>Q44*Q62</f>
         <v>2.0036090636910467E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="141"/>
-      <c r="B64" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" s="89">
-        <f>C63*$J$30*D42</f>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="110"/>
+      <c r="B64" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="120">
+        <f>C63*$J$30*$F$42</f>
         <v>21345.5705628</v>
       </c>
-      <c r="D64" s="86">
-        <f>J30*D63*D42</f>
+      <c r="D64" s="165">
+        <f t="shared" ref="D64:E64" si="3">D63*$J$30*$F$42</f>
+        <v>28101.287671467711</v>
+      </c>
+      <c r="E64" s="171">
+        <f t="shared" si="3"/>
         <v>30653.937916408569</v>
       </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F64" s="155">
+        <f>J30*F63*F42</f>
+        <v>30653.937916408569</v>
+      </c>
+      <c r="G64" s="139"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
+      <c r="J64" s="139"/>
+      <c r="K64" s="139"/>
+      <c r="L64" s="139"/>
+      <c r="M64" s="134"/>
+      <c r="N64" s="57"/>
+      <c r="O64" s="57"/>
+      <c r="P64" s="57"/>
+      <c r="Q64" s="57"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
       <c r="G65" s="15"/>
       <c r="H65" s="15"/>
       <c r="I65" s="15"/>
@@ -4564,475 +5422,542 @@
       <c r="M65" s="15"/>
       <c r="N65" s="15"/>
       <c r="O65" s="15"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="137" t="s">
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="123" t="s">
+        <v>84</v>
+      </c>
+      <c r="H66" s="123"/>
+      <c r="I66" s="123"/>
+      <c r="J66" s="123"/>
+      <c r="K66" s="123"/>
+      <c r="L66" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="F66" s="137"/>
-      <c r="G66" s="137"/>
-      <c r="H66" s="137"/>
-      <c r="I66" s="137"/>
-      <c r="J66" s="138" t="s">
-        <v>86</v>
-      </c>
-      <c r="K66" s="139"/>
-      <c r="L66" s="139"/>
-      <c r="M66" s="139"/>
-      <c r="N66" s="139"/>
-      <c r="O66" s="24"/>
-    </row>
-    <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="M66" s="108"/>
+      <c r="N66" s="108"/>
+      <c r="O66" s="108"/>
+      <c r="P66" s="108"/>
+      <c r="Q66" s="23"/>
+    </row>
+    <row r="67" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E67" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="F67" s="64" t="s">
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G67" s="124" t="s">
+        <v>103</v>
+      </c>
+      <c r="H67" s="124" t="s">
+        <v>102</v>
+      </c>
+      <c r="I67" s="124" t="s">
+        <v>101</v>
+      </c>
+      <c r="J67" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="K67" s="124" t="s">
         <v>105</v>
       </c>
-      <c r="G67" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="H67" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="I67" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="J67" s="49" t="s">
+      <c r="L67" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="M67" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="N67" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="O67" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="K67" s="50" t="s">
+      <c r="P67" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="L67" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="M67" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="N67" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="O67" s="15"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="144" t="s">
-        <v>94</v>
+      <c r="Q67" s="15"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="113" t="s">
+        <v>92</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68" s="18"/>
-      <c r="D68" s="29">
-        <f>SUM(E68:N68)</f>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="28">
+        <f>SUM(G68:P68)</f>
         <v>15021000</v>
       </c>
-      <c r="E68" s="72">
+      <c r="G68" s="143">
         <f>C14</f>
         <v>64582.789500000006</v>
       </c>
-      <c r="F68" s="72">
+      <c r="H68" s="143">
         <f>D14</f>
         <v>239111.78849999997</v>
       </c>
-      <c r="G68" s="72">
+      <c r="I68" s="143">
         <f>E14</f>
         <v>1126116.8595</v>
       </c>
-      <c r="H68" s="72">
+      <c r="J68" s="143">
         <f>F14</f>
         <v>2838600.9855</v>
       </c>
-      <c r="I68" s="72">
+      <c r="K68" s="143">
         <f>G14</f>
         <v>3242087.577</v>
       </c>
-      <c r="J68" s="79">
+      <c r="L68" s="62">
         <f>Frontend!K15</f>
         <v>3383500</v>
       </c>
-      <c r="K68" s="76">
+      <c r="M68" s="59">
         <f>Frontend!L15</f>
         <v>2682400</v>
       </c>
-      <c r="L68" s="76">
+      <c r="N68" s="59">
         <f>Frontend!M15</f>
         <v>1283500</v>
       </c>
-      <c r="M68" s="76">
+      <c r="O68" s="59">
         <f>Frontend!N15</f>
         <v>156200</v>
       </c>
-      <c r="N68" s="76">
+      <c r="P68" s="59">
         <f>Frontend!O15</f>
         <v>4900</v>
       </c>
-      <c r="O68" s="15"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="145"/>
+      <c r="Q68" s="15"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="114"/>
       <c r="B69" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
-      <c r="E69" s="66">
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="125">
         <v>27</v>
       </c>
-      <c r="F69" s="66">
+      <c r="H69" s="125">
         <v>32</v>
       </c>
-      <c r="G69" s="66">
+      <c r="I69" s="125">
         <v>37</v>
       </c>
-      <c r="H69" s="66">
+      <c r="J69" s="125">
         <v>42</v>
       </c>
-      <c r="I69" s="66">
+      <c r="K69" s="125">
         <v>47</v>
       </c>
-      <c r="J69" s="53">
+      <c r="L69" s="48">
         <v>52</v>
       </c>
-      <c r="K69" s="54">
+      <c r="M69" s="49">
         <v>57</v>
       </c>
-      <c r="L69" s="54">
+      <c r="N69" s="49">
         <v>62</v>
       </c>
-      <c r="M69" s="54">
+      <c r="O69" s="49">
         <v>67</v>
       </c>
-      <c r="N69" s="55">
+      <c r="P69" s="50">
         <v>72</v>
       </c>
-      <c r="O69" s="15"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="146"/>
+      <c r="Q69" s="15"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="115"/>
       <c r="B70" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C70" s="16"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="73">
-        <f>E68/$D$68</f>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="144">
+        <f>G68/$F$68</f>
         <v>4.2995000000000004E-3</v>
       </c>
-      <c r="F70" s="73">
-        <f t="shared" ref="F70:N70" si="12">F68/$D$68</f>
+      <c r="H70" s="144">
+        <f t="shared" ref="H70:P70" si="4">H68/$F$68</f>
         <v>1.5918499999999999E-2</v>
       </c>
-      <c r="G70" s="73">
-        <f t="shared" si="12"/>
+      <c r="I70" s="144">
+        <f t="shared" si="4"/>
         <v>7.4969499999999994E-2</v>
       </c>
-      <c r="H70" s="73">
-        <f t="shared" si="12"/>
+      <c r="J70" s="144">
+        <f t="shared" si="4"/>
         <v>0.18897549999999999</v>
       </c>
-      <c r="I70" s="73">
-        <f t="shared" si="12"/>
+      <c r="K70" s="144">
+        <f t="shared" si="4"/>
         <v>0.215837</v>
       </c>
-      <c r="J70" s="80">
-        <f t="shared" si="12"/>
+      <c r="L70" s="63">
+        <f t="shared" si="4"/>
         <v>0.2252513148259104</v>
       </c>
-      <c r="K70" s="77">
-        <f t="shared" si="12"/>
+      <c r="M70" s="60">
+        <f t="shared" si="4"/>
         <v>0.17857665934358566</v>
       </c>
-      <c r="L70" s="77">
-        <f t="shared" si="12"/>
+      <c r="N70" s="60">
+        <f t="shared" si="4"/>
         <v>8.5447040809533317E-2</v>
       </c>
-      <c r="M70" s="77">
-        <f t="shared" si="12"/>
+      <c r="O70" s="60">
+        <f t="shared" si="4"/>
         <v>1.0398775048265762E-2</v>
       </c>
-      <c r="N70" s="77">
-        <f t="shared" si="12"/>
+      <c r="P70" s="60">
+        <f t="shared" si="4"/>
         <v>3.2620997270487985E-4</v>
       </c>
-      <c r="O70" s="15"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B71" s="32"/>
-      <c r="C71" s="87" t="s">
-        <v>92</v>
-      </c>
-      <c r="D71" s="97" t="s">
+      <c r="Q70" s="15"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="74"/>
-      <c r="H71" s="74"/>
-      <c r="I71" s="74"/>
-      <c r="J71" s="81"/>
-      <c r="K71" s="78"/>
-      <c r="L71" s="78"/>
-      <c r="M71" s="78"/>
-      <c r="N71" s="78"/>
-      <c r="O71" s="15"/>
-    </row>
-    <row r="72" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="140" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C72" s="88"/>
-      <c r="D72" s="98"/>
-      <c r="E72" s="75">
-        <f>IF(E69&gt;$I$31,((19.4312 - 0.9336 *  E69 + 0.0126 *  E69^2)/100),0)</f>
+      <c r="B71" s="31"/>
+      <c r="C71" s="121" t="s">
+        <v>91</v>
+      </c>
+      <c r="D71" s="166" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" s="172" t="s">
+        <v>167</v>
+      </c>
+      <c r="F71" s="158" t="s">
+        <v>125</v>
+      </c>
+      <c r="G71" s="145"/>
+      <c r="H71" s="145"/>
+      <c r="I71" s="145"/>
+      <c r="J71" s="145"/>
+      <c r="K71" s="145"/>
+      <c r="L71" s="64"/>
+      <c r="M71" s="61"/>
+      <c r="N71" s="61"/>
+      <c r="O71" s="61"/>
+      <c r="P71" s="61"/>
+      <c r="Q71" s="15"/>
+    </row>
+    <row r="72" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="109" t="s">
+        <v>50</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" s="122"/>
+      <c r="D72" s="167"/>
+      <c r="E72" s="173"/>
+      <c r="F72" s="159"/>
+      <c r="G72" s="146">
+        <f>IF(G69&gt;$I$31,((19.4312 - 0.9336 *  G69 + 0.0126 *  G69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="F72" s="75">
-        <f t="shared" ref="F72:N72" si="13">IF(F69&gt;$I$31,((19.4312 - 0.9336 *  F69 + 0.0126 *  F69^2)/100),0)</f>
+      <c r="H72" s="146">
+        <f t="shared" ref="H72:P72" si="5">IF(H69&gt;$I$31,((19.4312 - 0.9336 *  H69 + 0.0126 *  H69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="G72" s="75">
-        <f t="shared" si="13"/>
+      <c r="I72" s="146">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H72" s="75">
-        <f t="shared" si="13"/>
+      <c r="J72" s="146">
+        <f t="shared" si="5"/>
         <v>2.4464000000000041E-2</v>
       </c>
-      <c r="I72" s="75">
-        <f t="shared" si="13"/>
+      <c r="K72" s="146">
+        <f t="shared" si="5"/>
         <v>3.3854000000000044E-2</v>
       </c>
-      <c r="J72" s="58">
-        <f t="shared" si="13"/>
+      <c r="L72" s="51">
+        <f t="shared" si="5"/>
         <v>4.9544000000000032E-2</v>
       </c>
-      <c r="K72" s="59">
-        <f t="shared" si="13"/>
+      <c r="M72" s="52">
+        <f t="shared" si="5"/>
         <v>7.1534000000000125E-2</v>
       </c>
-      <c r="L72" s="59">
-        <f t="shared" si="13"/>
+      <c r="N72" s="52">
+        <f t="shared" si="5"/>
         <v>9.9824000000000052E-2</v>
       </c>
-      <c r="M72" s="59">
-        <f t="shared" si="13"/>
+      <c r="O72" s="52">
+        <f t="shared" si="5"/>
         <v>0.13441399999999995</v>
       </c>
-      <c r="N72" s="59">
-        <f t="shared" si="13"/>
+      <c r="P72" s="52">
+        <f t="shared" si="5"/>
         <v>0.17530400000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="140"/>
-      <c r="B73" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C73" s="88">
-        <f>SUM(J73:N73)</f>
+    <row r="73" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="109"/>
+      <c r="B73" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="122">
+        <f>SUM(L73:P73)</f>
         <v>3.3918746155382498E-2</v>
       </c>
-      <c r="D73" s="98">
-        <f>SUM(E73:N73)</f>
+      <c r="D73" s="167">
+        <f>SUM(K73:P73)</f>
+        <v>4.1225691953382514E-2</v>
+      </c>
+      <c r="E73" s="173">
+        <f>SUM(G73:P73)</f>
         <v>4.5848788585382522E-2</v>
       </c>
-      <c r="E73" s="75">
-        <f>E72*E70</f>
+      <c r="F73" s="159">
+        <f>SUM(G73:P73)</f>
+        <v>4.5848788585382522E-2</v>
+      </c>
+      <c r="G73" s="146">
+        <f>G72*G70</f>
         <v>0</v>
       </c>
-      <c r="F73" s="75">
-        <f t="shared" ref="F73:N73" si="14">F72*F70</f>
+      <c r="H73" s="146">
+        <f t="shared" ref="H73:P73" si="6">H72*H70</f>
         <v>0</v>
       </c>
-      <c r="G73" s="75">
-        <f t="shared" si="14"/>
+      <c r="I73" s="146">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H73" s="75">
-        <f t="shared" si="14"/>
+      <c r="J73" s="146">
+        <f t="shared" si="6"/>
         <v>4.6230966320000072E-3</v>
       </c>
-      <c r="I73" s="75">
-        <f t="shared" si="14"/>
+      <c r="K73" s="146">
+        <f t="shared" si="6"/>
         <v>7.3069457980000094E-3</v>
       </c>
-      <c r="J73" s="58">
-        <f t="shared" si="14"/>
+      <c r="L73" s="51">
+        <f t="shared" si="6"/>
         <v>1.1159851141734912E-2</v>
       </c>
-      <c r="K73" s="59">
-        <f t="shared" si="14"/>
+      <c r="M73" s="52">
+        <f t="shared" si="6"/>
         <v>1.2774302749484078E-2</v>
       </c>
-      <c r="L73" s="59">
-        <f t="shared" si="14"/>
+      <c r="N73" s="52">
+        <f t="shared" si="6"/>
         <v>8.5296654017708584E-3</v>
       </c>
-      <c r="M73" s="59">
-        <f t="shared" si="14"/>
+      <c r="O73" s="52">
+        <f t="shared" si="6"/>
         <v>1.3977409493375935E-3</v>
       </c>
-      <c r="N73" s="59">
-        <f t="shared" si="14"/>
+      <c r="P73" s="52">
+        <f t="shared" si="6"/>
         <v>5.718591305505626E-5</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="141"/>
-      <c r="B74" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C74" s="89">
-        <f>J31*C73*D68</f>
+    <row r="74" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="110"/>
+      <c r="B74" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="120">
+        <f>$J$31*C73*$F$68</f>
         <v>5094.9348600000048</v>
       </c>
-      <c r="D74" s="86">
-        <f>J31*D73*D68</f>
+      <c r="D74" s="165">
+        <f t="shared" ref="D74:E74" si="7">$J$31*D73*$F$68</f>
+        <v>6192.5111883175869</v>
+      </c>
+      <c r="E74" s="171">
+        <f t="shared" si="7"/>
         <v>6886.9465334103088</v>
       </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
-      <c r="G74" s="28"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28"/>
-      <c r="J74" s="28"/>
-      <c r="K74" s="28"/>
-      <c r="L74" s="28"/>
-      <c r="M74" s="28"/>
-      <c r="N74" s="28"/>
-      <c r="O74" s="19"/>
-    </row>
-    <row r="77" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F74" s="155">
+        <f>J31*F73*F68</f>
+        <v>6886.9465334103088</v>
+      </c>
+      <c r="G74" s="147"/>
+      <c r="H74" s="147"/>
+      <c r="I74" s="147"/>
+      <c r="J74" s="147"/>
+      <c r="K74" s="147"/>
+      <c r="L74" s="149"/>
+      <c r="M74" s="148"/>
+      <c r="N74" s="148"/>
+      <c r="O74" s="148"/>
+      <c r="P74" s="148"/>
+      <c r="Q74" s="19"/>
+    </row>
+    <row r="77" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C78" t="s">
-        <v>92</v>
-      </c>
-      <c r="D78" t="s">
-        <v>128</v>
-      </c>
-      <c r="E78" t="s">
-        <v>98</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B79" s="33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="C79" s="40">
+      <c r="D78" s="164" t="s">
+        <v>165</v>
+      </c>
+      <c r="E78" s="170" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" s="157" t="s">
+        <v>125</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B79" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" s="174">
         <f>C61+C64+C74</f>
         <v>27420.859000423719</v>
       </c>
-      <c r="D79" s="40">
-        <f>D49+D53+D57+D64+D74</f>
+      <c r="D79" s="177">
+        <f t="shared" ref="D79" si="8">D61+D64+D74</f>
+        <v>35274.152437409015</v>
+      </c>
+      <c r="E79" s="180">
+        <f>E61+E64+E74</f>
+        <v>38521.238027442596</v>
+      </c>
+      <c r="F79" s="183">
+        <f>F49+F53+F57+F64+F74</f>
         <v>308626.30242553435</v>
       </c>
-      <c r="E79" s="34">
-        <f>D79-C79</f>
-        <v>281205.44342511066</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B80" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C80" s="41">
-        <f>C79*C86</f>
+      <c r="G79" s="33"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B80" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" s="175">
+        <f>C79*$C$85</f>
         <v>1919460130.0296605</v>
       </c>
-      <c r="D80" s="41">
-        <f>D79*C86</f>
+      <c r="D80" s="178">
+        <f t="shared" ref="D80:E80" si="9">D79*$C$85</f>
+        <v>2469190670.6186309</v>
+      </c>
+      <c r="E80" s="181">
+        <f t="shared" si="9"/>
+        <v>2696486661.9209819</v>
+      </c>
+      <c r="F80" s="184">
+        <f>F79*C85</f>
         <v>21603841169.787403</v>
       </c>
-      <c r="E80" s="35">
-        <f>D80-C80</f>
-        <v>19684381039.757744</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="117" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" s="40">
-        <f>(C79/C87)*100000</f>
+      <c r="G80" s="34"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B81" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="C81" s="174">
+        <f>(C79/$C$86)*100000</f>
         <v>106.86035636315063</v>
       </c>
-      <c r="D82" s="40">
-        <f>(D79/C87)*100000</f>
+      <c r="D81" s="177">
+        <f t="shared" ref="D81:E81" si="10">(D79/$C$86)*100000</f>
+        <v>137.46500428055077</v>
+      </c>
+      <c r="E81" s="180">
+        <f t="shared" si="10"/>
+        <v>150.11904707648497</v>
+      </c>
+      <c r="F81" s="183">
+        <f>(F79/C86)*100000</f>
         <v>1202.730981539436</v>
       </c>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B83" s="117" t="s">
-        <v>146</v>
-      </c>
-      <c r="C83" s="118">
-        <f>C80/C87</f>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B82" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="C82" s="176">
+        <f>C80/$C$86</f>
         <v>74.802249454205437</v>
       </c>
-      <c r="D83" s="118">
-        <f>(D80/C87)</f>
+      <c r="D82" s="179">
+        <f t="shared" ref="D82:E82" si="11">D80/$C$86</f>
+        <v>96.225502996385529</v>
+      </c>
+      <c r="E82" s="182">
+        <f t="shared" si="11"/>
+        <v>105.08333295353948</v>
+      </c>
+      <c r="F82" s="185">
+        <f>(F80/C86)</f>
         <v>841.91168707760517</v>
       </c>
     </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B85" s="33" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B86" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C86" s="118">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B84" s="32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B85" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C85" s="86">
         <v>70000</v>
       </c>
-    </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B87" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="C87" s="8">
+      <c r="D85" s="86"/>
+      <c r="E85" s="86"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B86" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C86" s="8">
         <v>25660460</v>
       </c>
-    </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B88" s="33"/>
-      <c r="C88" s="45"/>
-      <c r="D88" s="45"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B87" s="32"/>
+      <c r="C87" s="42"/>
+      <c r="D87" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="E40:J40"/>
-    <mergeCell ref="K40:O40"/>
-    <mergeCell ref="E66:I66"/>
-    <mergeCell ref="J66:N66"/>
+    <mergeCell ref="G40:L40"/>
+    <mergeCell ref="M40:Q40"/>
+    <mergeCell ref="G66:K66"/>
+    <mergeCell ref="L66:P66"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="A62:A64"/>
     <mergeCell ref="A46:A49"/>
@@ -5047,7 +5972,245 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E626FF22-8137-4E66-B950-E8DCA56124BF}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2">
+        <v>27420.859000423719</v>
+      </c>
+      <c r="C2">
+        <v>35274.152437409015</v>
+      </c>
+      <c r="D2">
+        <v>38521.238027442596</v>
+      </c>
+      <c r="E2">
+        <v>308626.30242553435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7">
+        <v>254483.32856966133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8">
+        <v>8431.0399571348571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9">
+        <v>8171.0494489193279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="D10">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="E10">
+        <v>980.35357762371382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11">
+        <v>21345.5705628</v>
+      </c>
+      <c r="D11">
+        <v>28101.287671467711</v>
+      </c>
+      <c r="E11">
+        <v>30653.937916408569</v>
+      </c>
+      <c r="F11">
+        <v>30653.937916408569</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12">
+        <v>5094.9348600000048</v>
+      </c>
+      <c r="D12">
+        <v>6192.5111883175869</v>
+      </c>
+      <c r="E12">
+        <v>6886.9465334103088</v>
+      </c>
+      <c r="F12">
+        <v>6886.9465334103088</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F16">
+        <v>21345.5705628</v>
+      </c>
+      <c r="G16">
+        <v>5094.9348600000048</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F17">
+        <v>28101.287671467711</v>
+      </c>
+      <c r="G17">
+        <v>6192.5111883175869</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F18">
+        <v>30653.937916408569</v>
+      </c>
+      <c r="G18">
+        <v>6886.9465334103088</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19">
+        <v>254483.32856966133</v>
+      </c>
+      <c r="C19">
+        <v>8431.0399571348571</v>
+      </c>
+      <c r="D19">
+        <v>8171.0494489193279</v>
+      </c>
+      <c r="F19">
+        <v>30653.937916408569</v>
+      </c>
+      <c r="G19">
+        <v>6886.9465334103088</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1B57BF-B5FC-49D0-8C1C-84AA1C3FC65A}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5057,69 +6220,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>122</v>
+      <c r="A1" s="29" t="s">
+        <v>119</v>
       </c>
       <c r="B1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="35">
+        <v>1</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="35">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="35">
+        <v>3</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="35">
+        <v>4</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="38">
+        <v>5</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="C1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="36">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="36">
-        <v>2</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="36">
-        <v>3</v>
-      </c>
-      <c r="B4" s="48" t="s">
+      <c r="C6" t="s">
         <v>133</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="36">
-        <v>4</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
-        <v>5</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -5127,7 +6290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A8C717-7812-4473-9D8B-3495A5B0BB7F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5137,7 +6300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3BA502-77FB-4AA9-A654-F467290EB112}">
   <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G13"/>
@@ -5324,24 +6487,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601D2B11-F41E-4CFB-A90C-BC8CA1A15B8D}">
-  <sheetPr codeName="Tabelle3"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15C0212-0B91-4E6B-BA83-4D03E3220F57}">
-  <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
+++ b/Lärmschadenstool_EXCEL/Lärmschadenstool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente_lokal\GitHub Repository\END2DALY\Lärmschadenstool_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AB833211-344A-486E-A156-EB0F2C039A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7AD7D26A-39A3-4446-A6D6-E1C3699E3D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hinweise" sheetId="12" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="397" uniqueCount="173">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="402" uniqueCount="173">
   <si>
     <t>L_den</t>
   </si>
@@ -834,11 +834,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -1179,15 +1180,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1355,49 +1357,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1405,16 +1364,10 @@
     <xf numFmtId="4" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1428,9 +1381,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1504,6 +1454,49 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1513,14 +1506,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Überschrift" xfId="1" builtinId="15"/>
     <cellStyle name="Überschrift 1" xfId="2" builtinId="16"/>
     <cellStyle name="Überschrift 2" xfId="3" builtinId="17"/>
     <cellStyle name="Überschrift 3" xfId="4" builtinId="18"/>
     <cellStyle name="Währung" xfId="5" builtinId="4"/>
+    <cellStyle name="Währung 2" xfId="6" xr:uid="{9CC6AAD4-D7B9-41B8-94C1-514B90919213}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2083,15 +2087,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -2100,10 +2104,10 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="174" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="103"/>
+      <c r="B10" s="174"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -2113,22 +2117,22 @@
       <c r="B12" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="176" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="K12" s="101" t="s">
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="K12" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="78"/>
@@ -2171,7 +2175,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="175" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="78" t="s">
@@ -2218,7 +2222,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="104"/>
+      <c r="A15" s="175"/>
       <c r="B15" s="87" t="s">
         <v>76</v>
       </c>
@@ -2298,7 +2302,7 @@
       <c r="P17" s="77"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="175" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="78" t="s">
@@ -2345,7 +2349,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
+      <c r="A19" s="175"/>
       <c r="B19" s="78" t="s">
         <v>72</v>
       </c>
@@ -2424,7 +2428,7 @@
       <c r="P21" s="77"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="175" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="78" t="s">
@@ -2471,7 +2475,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="104"/>
+      <c r="A23" s="175"/>
       <c r="B23" s="78" t="s">
         <v>75</v>
       </c>
@@ -2522,10 +2526,10 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="103" t="s">
+      <c r="A32" s="174" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="103"/>
+      <c r="B32" s="174"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2652,15 +2656,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -2669,10 +2673,10 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="174" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="103"/>
+      <c r="B10" s="174"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -2682,22 +2686,22 @@
       <c r="B12" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="176" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="K12" s="101" t="s">
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="K12" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="78"/>
@@ -2740,7 +2744,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="175" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="78" t="s">
@@ -2787,7 +2791,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="104"/>
+      <c r="A15" s="175"/>
       <c r="B15" s="79" t="s">
         <v>76</v>
       </c>
@@ -2867,7 +2871,7 @@
       <c r="P17" s="77"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="175" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="78" t="s">
@@ -2914,7 +2918,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
+      <c r="A19" s="175"/>
       <c r="B19" s="78" t="s">
         <v>72</v>
       </c>
@@ -2993,7 +2997,7 @@
       <c r="P21" s="77"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="175" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="78" t="s">
@@ -3040,7 +3044,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="104"/>
+      <c r="A23" s="175"/>
       <c r="B23" s="78" t="s">
         <v>75</v>
       </c>
@@ -3091,10 +3095,10 @@
     </row>
     <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="103" t="s">
+      <c r="A32" s="174" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="103"/>
+      <c r="B32" s="174"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -3168,14 +3172,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3209,15 +3213,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="74.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
     </row>
     <row r="8" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
@@ -3226,12 +3230,12 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="117" t="s">
+      <c r="A10" s="102" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -3241,22 +3245,22 @@
       <c r="B12" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="105" t="s">
+      <c r="D12" s="176" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="K12" s="101" t="s">
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="K12" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172"/>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="78"/>
@@ -3299,7 +3303,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="175" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="78" t="s">
@@ -3346,7 +3350,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="104"/>
+      <c r="A15" s="175"/>
       <c r="B15" s="79" t="s">
         <v>76</v>
       </c>
@@ -3426,7 +3430,7 @@
       <c r="P17" s="77"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="175" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="78" t="s">
@@ -3473,7 +3477,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
+      <c r="A19" s="175"/>
       <c r="B19" s="78" t="s">
         <v>72</v>
       </c>
@@ -3552,7 +3556,7 @@
       <c r="P21" s="77"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="104" t="s">
+      <c r="A22" s="175" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="78" t="s">
@@ -3599,7 +3603,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="104"/>
+      <c r="A23" s="175"/>
       <c r="B23" s="78" t="s">
         <v>75</v>
       </c>
@@ -3650,10 +3654,10 @@
     </row>
     <row r="27" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="174" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="103"/>
+      <c r="B28" s="174"/>
     </row>
     <row r="29" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -3666,7 +3670,7 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="189" t="s">
+      <c r="A31" s="171" t="s">
         <v>156</v>
       </c>
       <c r="B31" s="74">
@@ -3679,7 +3683,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="189" t="s">
+      <c r="A32" s="171" t="s">
         <v>157</v>
       </c>
       <c r="B32" s="74">
@@ -3696,99 +3700,99 @@
       <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="188" t="s">
+      <c r="A34" s="170" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="187" t="s">
+      <c r="B34" s="169" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="187" t="s">
+      <c r="C34" s="169" t="s">
         <v>169</v>
       </c>
-      <c r="D34" s="187" t="s">
+      <c r="D34" s="169" t="s">
         <v>95</v>
       </c>
-      <c r="E34" s="187" t="s">
+      <c r="E34" s="169" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="188" t="s">
+      <c r="A35" s="170" t="s">
         <v>164</v>
       </c>
-      <c r="B35" s="186" t="s">
+      <c r="B35" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="186" t="s">
+      <c r="C35" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="186" t="s">
+      <c r="D35" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="186" t="s">
+      <c r="E35" s="168" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="188" t="s">
+      <c r="A36" s="170" t="s">
         <v>165</v>
       </c>
-      <c r="B36" s="186" t="s">
+      <c r="B36" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="C36" s="186" t="s">
+      <c r="C36" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="186" t="s">
+      <c r="D36" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="E36" s="186" t="s">
+      <c r="E36" s="168" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="188" t="s">
+      <c r="A37" s="170" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="186" t="s">
+      <c r="B37" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="C37" s="186" t="s">
+      <c r="C37" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="186" t="s">
+      <c r="D37" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="E37" s="186" t="s">
+      <c r="E37" s="168" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="188" t="s">
+      <c r="A38" s="170" t="s">
         <v>166</v>
       </c>
-      <c r="B38" s="186" t="s">
+      <c r="B38" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="C38" s="186" t="s">
+      <c r="C38" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="186" t="s">
+      <c r="D38" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="E38" s="186" t="s">
+      <c r="E38" s="168" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="K12:P12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4310,21 +4314,21 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
       <c r="E40" s="15"/>
-      <c r="G40" s="136" t="s">
+      <c r="G40" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="H40" s="136"/>
-      <c r="I40" s="136"/>
-      <c r="J40" s="136"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="136"/>
-      <c r="M40" s="126" t="s">
+      <c r="H40" s="177"/>
+      <c r="I40" s="177"/>
+      <c r="J40" s="177"/>
+      <c r="K40" s="177"/>
+      <c r="L40" s="177"/>
+      <c r="M40" s="178" t="s">
         <v>82</v>
       </c>
-      <c r="N40" s="106"/>
-      <c r="O40" s="106"/>
-      <c r="P40" s="106"/>
-      <c r="Q40" s="106"/>
+      <c r="N40" s="179"/>
+      <c r="O40" s="179"/>
+      <c r="P40" s="179"/>
+      <c r="Q40" s="179"/>
     </row>
     <row r="41" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="F41" s="15" t="s">
@@ -4348,24 +4352,24 @@
       <c r="L41" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="M41" s="127" t="s">
+      <c r="M41" s="110" t="s">
         <v>107</v>
       </c>
-      <c r="N41" s="128" t="s">
+      <c r="N41" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="O41" s="128" t="s">
+      <c r="O41" s="111" t="s">
         <v>109</v>
       </c>
-      <c r="P41" s="128" t="s">
+      <c r="P41" s="111" t="s">
         <v>110</v>
       </c>
-      <c r="Q41" s="128" t="s">
+      <c r="Q41" s="111" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="113" t="s">
+      <c r="A42" s="190" t="s">
         <v>92</v>
       </c>
       <c r="B42" s="40" t="s">
@@ -4378,31 +4382,31 @@
         <f>SUM(G42:Q42)</f>
         <v>20796420.796399999</v>
       </c>
-      <c r="G42" s="137">
-        <f>C13</f>
+      <c r="G42" s="119">
+        <f t="shared" ref="G42:L42" si="0">C13</f>
         <v>14817.435000000001</v>
       </c>
-      <c r="H42" s="137">
-        <f>D13</f>
+      <c r="H42" s="119">
+        <f t="shared" si="0"/>
         <v>43360.493999999999</v>
       </c>
-      <c r="I42" s="137">
-        <f>E13</f>
+      <c r="I42" s="119">
+        <f t="shared" si="0"/>
         <v>175282.45740000001</v>
       </c>
-      <c r="J42" s="137">
-        <f>F13</f>
+      <c r="J42" s="119">
+        <f t="shared" si="0"/>
         <v>708356.57860000001</v>
       </c>
-      <c r="K42" s="137">
-        <f>G13</f>
+      <c r="K42" s="119">
+        <f t="shared" si="0"/>
         <v>2895888.3018</v>
       </c>
-      <c r="L42" s="137">
-        <f>H13</f>
+      <c r="L42" s="119">
+        <f t="shared" si="0"/>
         <v>6560515.5296</v>
       </c>
-      <c r="M42" s="129">
+      <c r="M42" s="112">
         <f>Frontend!D15</f>
         <v>3762100</v>
       </c>
@@ -4429,7 +4433,7 @@
       <c r="W42" s="8"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="114"/>
+      <c r="A43" s="191"/>
       <c r="B43" s="15" t="s">
         <v>97</v>
       </c>
@@ -4437,25 +4441,25 @@
       <c r="D43" s="15"/>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
-      <c r="G43" s="138">
+      <c r="G43" s="120">
         <v>27</v>
       </c>
-      <c r="H43" s="138">
+      <c r="H43" s="120">
         <v>32</v>
       </c>
-      <c r="I43" s="138">
+      <c r="I43" s="120">
         <v>37</v>
       </c>
-      <c r="J43" s="138">
+      <c r="J43" s="120">
         <v>42</v>
       </c>
-      <c r="K43" s="138">
+      <c r="K43" s="120">
         <v>47</v>
       </c>
-      <c r="L43" s="138">
+      <c r="L43" s="120">
         <v>52</v>
       </c>
-      <c r="M43" s="130">
+      <c r="M43" s="113">
         <v>57</v>
       </c>
       <c r="N43" s="54">
@@ -4467,12 +4471,12 @@
       <c r="P43" s="54">
         <v>72</v>
       </c>
-      <c r="Q43" s="131">
+      <c r="Q43" s="114">
         <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:23" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="115"/>
+      <c r="A44" s="192"/>
       <c r="B44" s="27" t="s">
         <v>98</v>
       </c>
@@ -4480,48 +4484,48 @@
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
-      <c r="G44" s="139">
+      <c r="G44" s="121">
         <f>G42/$F$42</f>
         <v>7.1249928750071259E-4</v>
       </c>
-      <c r="H44" s="139">
-        <f t="shared" ref="H44:Q44" si="0">H42/$F$42</f>
+      <c r="H44" s="121">
+        <f t="shared" ref="H44:Q44" si="1">H42/$F$42</f>
         <v>2.0849979150020848E-3</v>
       </c>
-      <c r="I44" s="139">
-        <f t="shared" si="0"/>
+      <c r="I44" s="121">
+        <f t="shared" si="1"/>
         <v>8.4284915715084289E-3</v>
       </c>
-      <c r="J44" s="139">
-        <f t="shared" si="0"/>
+      <c r="J44" s="121">
+        <f t="shared" si="1"/>
         <v>3.4061465938534062E-2</v>
       </c>
-      <c r="K44" s="139">
-        <f t="shared" si="0"/>
+      <c r="K44" s="121">
+        <f t="shared" si="1"/>
         <v>0.13924936075063926</v>
       </c>
-      <c r="L44" s="139">
-        <f t="shared" si="0"/>
+      <c r="L44" s="121">
+        <f t="shared" si="1"/>
         <v>0.31546368453631546</v>
       </c>
-      <c r="M44" s="134">
-        <f t="shared" si="0"/>
+      <c r="M44" s="117">
+        <f t="shared" si="1"/>
         <v>0.18090132128174888</v>
       </c>
       <c r="N44" s="57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.14670312886379619</v>
       </c>
       <c r="O44" s="57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11920320444896612</v>
       </c>
       <c r="P44" s="57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.8392942701669828E-2</v>
       </c>
       <c r="Q44" s="57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.7989027043190075E-3</v>
       </c>
     </row>
@@ -4529,32 +4533,32 @@
       <c r="A45" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="118" t="s">
+      <c r="C45" s="103" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="160" t="s">
+      <c r="D45" s="142" t="s">
         <v>165</v>
       </c>
-      <c r="E45" s="161" t="s">
+      <c r="E45" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="152" t="s">
+      <c r="F45" s="134" t="s">
         <v>125</v>
       </c>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="130"/>
+      <c r="G45" s="120"/>
+      <c r="H45" s="120"/>
+      <c r="I45" s="120"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="120"/>
+      <c r="L45" s="120"/>
+      <c r="M45" s="113"/>
       <c r="N45" s="54"/>
       <c r="O45" s="54"/>
       <c r="P45" s="54"/>
       <c r="Q45" s="54"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="190" t="s">
+      <c r="A46" s="187" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="17" t="s">
@@ -4563,54 +4567,54 @@
       <c r="C46" s="67"/>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
-      <c r="F46" s="153"/>
-      <c r="G46" s="140">
-        <f>IF(G43&gt;$I$32, EXP((LN(1.055)/10)*(G43-$I$32)),1)</f>
+      <c r="F46" s="135"/>
+      <c r="G46" s="122">
+        <f t="shared" ref="G46:Q46" si="2">IF(G43&gt;$I$32, EXP((LN(1.055)/10)*(G43-$I$32)),1)</f>
         <v>1</v>
       </c>
-      <c r="H46" s="140">
-        <f>IF(H43&gt;$I$32, EXP((LN(1.055)/10)*(H43-$I$32)),1)</f>
+      <c r="H46" s="122">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I46" s="140">
-        <f>IF(I43&gt;$I$32, EXP((LN(1.055)/10)*(I43-$I$32)),1)</f>
+      <c r="I46" s="122">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J46" s="140">
-        <f>IF(J43&gt;$I$32, EXP((LN(1.055)/10)*(J43-$I$32)),1)</f>
+      <c r="J46" s="122">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K46" s="140">
-        <f>IF(K43&gt;$I$32, EXP((LN(1.055)/10)*(K43-$I$32)),1)</f>
+      <c r="K46" s="122">
+        <f t="shared" si="2"/>
         <v>1.0107656908500073</v>
       </c>
-      <c r="L46" s="140">
-        <f>IF(L43&gt;$I$32, EXP((LN(1.055)/10)*(L43-$I$32)),1)</f>
+      <c r="L46" s="122">
+        <f t="shared" si="2"/>
         <v>1.0381897140207395</v>
       </c>
-      <c r="M46" s="132">
-        <f>IF(M43&gt;$I$32, EXP((LN(1.055)/10)*(M43-$I$32)),1)</f>
+      <c r="M46" s="115">
+        <f t="shared" si="2"/>
         <v>1.0663578038467578</v>
       </c>
       <c r="N46" s="55">
-        <f>IF(N43&gt;$I$32, EXP((LN(1.055)/10)*(N43-$I$32)),1)</f>
+        <f t="shared" si="2"/>
         <v>1.09529014829188</v>
       </c>
       <c r="O46" s="55">
-        <f>IF(O43&gt;$I$32, EXP((LN(1.055)/10)*(O43-$I$32)),1)</f>
+        <f t="shared" si="2"/>
         <v>1.1250074830583294</v>
       </c>
       <c r="P46" s="55">
-        <f>IF(P43&gt;$I$32, EXP((LN(1.055)/10)*(P43-$I$32)),1)</f>
+        <f t="shared" si="2"/>
         <v>1.1555311064479334</v>
       </c>
       <c r="Q46" s="55">
-        <f>IF(Q43&gt;$I$32, EXP((LN(1.055)/10)*(Q43-$I$32)),1)</f>
+        <f t="shared" si="2"/>
         <v>1.1868828946265373</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="191"/>
+      <c r="A47" s="188"/>
       <c r="B47" s="15" t="s">
         <v>80</v>
       </c>
@@ -4620,57 +4624,57 @@
       </c>
       <c r="D47" s="68"/>
       <c r="E47" s="68"/>
-      <c r="F47" s="152">
+      <c r="F47" s="134">
         <f>SUM(G47:Q47)</f>
         <v>6.2854894074549819E-2</v>
       </c>
-      <c r="G47" s="141">
-        <f>G44*(G46-1)</f>
+      <c r="G47" s="123">
+        <f t="shared" ref="G47:Q47" si="3">G44*(G46-1)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="141">
-        <f>H44*(H46-1)</f>
+      <c r="H47" s="123">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I47" s="141">
-        <f>I44*(I46-1)</f>
+      <c r="I47" s="123">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J47" s="141">
-        <f>J44*(J46-1)</f>
+      <c r="J47" s="123">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K47" s="141">
-        <f>K44*(K46-1)</f>
+      <c r="K47" s="123">
+        <f t="shared" si="3"/>
         <v>1.4991155689025278E-3</v>
       </c>
-      <c r="L47" s="141">
-        <f>L44*(L46-1)</f>
+      <c r="L47" s="123">
+        <f t="shared" si="3"/>
         <v>1.2047467896370654E-2</v>
       </c>
-      <c r="M47" s="133">
-        <f>M44*(M46-1)</f>
+      <c r="M47" s="116">
+        <f t="shared" si="3"/>
         <v>1.2004214393233608E-2</v>
       </c>
       <c r="N47" s="56">
-        <f>N44*(N46-1)</f>
+        <f t="shared" si="3"/>
         <v>1.3979362904313918E-2</v>
       </c>
       <c r="O47" s="56">
-        <f>O44*(O46-1)</f>
+        <f t="shared" si="3"/>
         <v>1.4901292560652712E-2</v>
       </c>
       <c r="P47" s="56">
-        <f>P44*(P46-1)</f>
+        <f t="shared" si="3"/>
         <v>7.5266079226621535E-3</v>
       </c>
       <c r="Q47" s="56">
-        <f>Q44*(Q46-1)</f>
+        <f t="shared" si="3"/>
         <v>8.9683282841425394E-4</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="191"/>
+      <c r="A48" s="188"/>
       <c r="B48" s="15" t="s">
         <v>100</v>
       </c>
@@ -4680,51 +4684,51 @@
       </c>
       <c r="D48" s="68"/>
       <c r="E48" s="68"/>
-      <c r="F48" s="154">
+      <c r="F48" s="136">
         <f>(F47)/(1+F47)</f>
         <v>5.9137794279320602E-2</v>
       </c>
-      <c r="G48" s="138"/>
-      <c r="H48" s="138"/>
-      <c r="I48" s="138"/>
-      <c r="J48" s="138"/>
-      <c r="K48" s="138"/>
-      <c r="L48" s="138"/>
-      <c r="M48" s="130"/>
+      <c r="G48" s="120"/>
+      <c r="H48" s="120"/>
+      <c r="I48" s="120"/>
+      <c r="J48" s="120"/>
+      <c r="K48" s="120"/>
+      <c r="L48" s="120"/>
+      <c r="M48" s="113"/>
       <c r="N48" s="54"/>
       <c r="O48" s="54"/>
       <c r="P48" s="54"/>
       <c r="Q48" s="54"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="192"/>
+      <c r="A49" s="189"/>
       <c r="B49" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="C49" s="151">
+      <c r="C49" s="133">
         <f>0.2069215*C48*F42</f>
         <v>202214.00228176778</v>
       </c>
       <c r="D49" s="71"/>
       <c r="E49" s="71"/>
-      <c r="F49" s="155">
+      <c r="F49" s="137">
         <f>0.2069215*F48*F42</f>
         <v>254483.32856966133</v>
       </c>
-      <c r="G49" s="139"/>
-      <c r="H49" s="139"/>
-      <c r="I49" s="139"/>
-      <c r="J49" s="139"/>
-      <c r="K49" s="139"/>
-      <c r="L49" s="139"/>
-      <c r="M49" s="134"/>
+      <c r="G49" s="121"/>
+      <c r="H49" s="121"/>
+      <c r="I49" s="121"/>
+      <c r="J49" s="121"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="117"/>
       <c r="N49" s="57"/>
       <c r="O49" s="57"/>
       <c r="P49" s="57"/>
       <c r="Q49" s="57"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="113" t="s">
+      <c r="A50" s="190" t="s">
         <v>57</v>
       </c>
       <c r="B50" s="17" t="s">
@@ -4733,54 +4737,54 @@
       <c r="C50" s="67"/>
       <c r="D50" s="67"/>
       <c r="E50" s="67"/>
-      <c r="F50" s="153"/>
-      <c r="G50" s="140">
-        <f>IF(G43&gt;$I$33, EXP((LN(1.032)/10)*(G43-$I$33)),1)</f>
+      <c r="F50" s="135"/>
+      <c r="G50" s="122">
+        <f t="shared" ref="G50:Q50" si="4">IF(G43&gt;$I$33, EXP((LN(1.032)/10)*(G43-$I$33)),1)</f>
         <v>1</v>
       </c>
-      <c r="H50" s="140">
-        <f>IF(H43&gt;$I$33, EXP((LN(1.032)/10)*(H43-$I$33)),1)</f>
+      <c r="H50" s="122">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I50" s="140">
-        <f>IF(I43&gt;$I$33, EXP((LN(1.032)/10)*(I43-$I$33)),1)</f>
+      <c r="I50" s="122">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J50" s="140">
-        <f>IF(J43&gt;$I$33, EXP((LN(1.032)/10)*(J43-$I$33)),1)</f>
+      <c r="J50" s="122">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K50" s="140">
-        <f>IF(K43&gt;$I$33, EXP((LN(1.032)/10)*(K43-$I$33)),1)</f>
+      <c r="K50" s="122">
+        <f t="shared" si="4"/>
         <v>1.0063196184673233</v>
       </c>
-      <c r="L50" s="140">
-        <f>IF(L43&gt;$I$33, EXP((LN(1.032)/10)*(L43-$I$33)),1)</f>
+      <c r="L50" s="122">
+        <f t="shared" si="4"/>
         <v>1.0222939440770498</v>
       </c>
-      <c r="M50" s="132">
-        <f>IF(M43&gt;$I$33, EXP((LN(1.032)/10)*(M43-$I$33)),1)</f>
+      <c r="M50" s="115">
+        <f t="shared" si="4"/>
         <v>1.0385218462582777</v>
       </c>
       <c r="N50" s="55">
-        <f>IF(N43&gt;$I$33, EXP((LN(1.032)/10)*(N43-$I$33)),1)</f>
+        <f t="shared" si="4"/>
         <v>1.0550073502875155</v>
       </c>
       <c r="O50" s="55">
-        <f>IF(O43&gt;$I$33, EXP((LN(1.032)/10)*(O43-$I$33)),1)</f>
+        <f t="shared" si="4"/>
         <v>1.0717545453385426</v>
       </c>
       <c r="P50" s="55">
-        <f>IF(P43&gt;$I$33, EXP((LN(1.032)/10)*(P43-$I$33)),1)</f>
+        <f t="shared" si="4"/>
         <v>1.088767585496716</v>
       </c>
       <c r="Q50" s="55">
-        <f>IF(Q43&gt;$I$33, EXP((LN(1.032)/10)*(Q43-$I$33)),1)</f>
+        <f t="shared" si="4"/>
         <v>1.1060506907893759</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="114"/>
+      <c r="A51" s="191"/>
       <c r="B51" s="15" t="s">
         <v>80</v>
       </c>
@@ -4790,57 +4794,57 @@
       </c>
       <c r="D51" s="68"/>
       <c r="E51" s="68"/>
-      <c r="F51" s="152">
+      <c r="F51" s="134">
         <f>SUM(G51:Q51)</f>
         <v>3.6309359220840685E-2</v>
       </c>
-      <c r="G51" s="138">
-        <f>G44*(G50-1)</f>
+      <c r="G51" s="120">
+        <f t="shared" ref="G51:Q51" si="5">G44*(G50-1)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="138">
-        <f>H44*(H50-1)</f>
+      <c r="H51" s="120">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I51" s="138">
-        <f>I44*(I50-1)</f>
+      <c r="I51" s="120">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J51" s="138">
-        <f>J44*(J50-1)</f>
+      <c r="J51" s="120">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K51" s="138">
-        <f>K44*(K50-1)</f>
+      <c r="K51" s="120">
+        <f t="shared" si="5"/>
         <v>8.8000283176270673E-4</v>
       </c>
-      <c r="L51" s="138">
-        <f>L44*(L50-1)</f>
+      <c r="L51" s="120">
+        <f t="shared" si="5"/>
         <v>7.0329297413926854E-3</v>
       </c>
-      <c r="M51" s="130">
-        <f>M44*(M50-1)</f>
+      <c r="M51" s="113">
+        <f t="shared" si="5"/>
         <v>6.9686528863348307E-3</v>
       </c>
       <c r="N51" s="54">
-        <f>N44*(N50-1)</f>
+        <f t="shared" si="5"/>
         <v>8.0697503976853574E-3</v>
       </c>
       <c r="O51" s="54">
-        <f>O44*(O50-1)</f>
+        <f t="shared" si="5"/>
         <v>8.5533717381329078E-3</v>
       </c>
       <c r="P51" s="54">
-        <f>P44*(P50-1)</f>
+        <f t="shared" si="5"/>
         <v>4.2957246787081573E-3</v>
       </c>
       <c r="Q51" s="54">
-        <f>Q44*(Q50-1)</f>
+        <f t="shared" si="5"/>
         <v>5.0892694682403491E-4</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="114"/>
+      <c r="A52" s="191"/>
       <c r="B52" s="15" t="s">
         <v>100</v>
       </c>
@@ -4850,24 +4854,24 @@
       </c>
       <c r="D52" s="68"/>
       <c r="E52" s="68"/>
-      <c r="F52" s="152">
+      <c r="F52" s="134">
         <f>F51/(1+F51)</f>
         <v>3.503718160775874E-2</v>
       </c>
-      <c r="G52" s="138"/>
-      <c r="H52" s="138"/>
-      <c r="I52" s="138"/>
-      <c r="J52" s="138"/>
-      <c r="K52" s="138"/>
-      <c r="L52" s="138"/>
-      <c r="M52" s="130"/>
+      <c r="G52" s="120"/>
+      <c r="H52" s="120"/>
+      <c r="I52" s="120"/>
+      <c r="J52" s="120"/>
+      <c r="K52" s="120"/>
+      <c r="L52" s="120"/>
+      <c r="M52" s="113"/>
       <c r="N52" s="54"/>
       <c r="O52" s="54"/>
       <c r="P52" s="54"/>
       <c r="Q52" s="54"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="115"/>
+      <c r="A53" s="192"/>
       <c r="B53" s="39" t="s">
         <v>122</v>
       </c>
@@ -4877,24 +4881,24 @@
       </c>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
-      <c r="F53" s="156">
+      <c r="F53" s="138">
         <f>0.0115708*F52*F42</f>
         <v>8431.0399571348571</v>
       </c>
-      <c r="G53" s="139"/>
-      <c r="H53" s="139"/>
-      <c r="I53" s="139"/>
-      <c r="J53" s="139"/>
-      <c r="K53" s="139"/>
-      <c r="L53" s="139"/>
-      <c r="M53" s="134"/>
+      <c r="G53" s="121"/>
+      <c r="H53" s="121"/>
+      <c r="I53" s="121"/>
+      <c r="J53" s="121"/>
+      <c r="K53" s="121"/>
+      <c r="L53" s="121"/>
+      <c r="M53" s="117"/>
       <c r="N53" s="57"/>
       <c r="O53" s="57"/>
       <c r="P53" s="57"/>
       <c r="Q53" s="57"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="113" t="s">
+      <c r="A54" s="190" t="s">
         <v>59</v>
       </c>
       <c r="B54" s="17" t="s">
@@ -4903,54 +4907,54 @@
       <c r="C54" s="67"/>
       <c r="D54" s="67"/>
       <c r="E54" s="67"/>
-      <c r="F54" s="153"/>
-      <c r="G54" s="140">
-        <f>IF(G43&gt;$I$34, EXP((LN(1.062)/10)*(G43-$I$34)),1)</f>
+      <c r="F54" s="135"/>
+      <c r="G54" s="122">
+        <f t="shared" ref="G54:Q54" si="6">IF(G43&gt;$I$34, EXP((LN(1.062)/10)*(G43-$I$34)),1)</f>
         <v>1</v>
       </c>
-      <c r="H54" s="140">
-        <f>IF(H43&gt;$I$34, EXP((LN(1.062)/10)*(H43-$I$34)),1)</f>
+      <c r="H54" s="122">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="I54" s="140">
-        <f>IF(I43&gt;$I$34, EXP((LN(1.062)/10)*(I43-$I$34)),1)</f>
+      <c r="I54" s="122">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="J54" s="140">
-        <f>IF(J43&gt;$I$34, EXP((LN(1.062)/10)*(J43-$I$34)),1)</f>
+      <c r="J54" s="122">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K54" s="140">
-        <f>IF(K43&gt;$I$34, EXP((LN(1.062)/10)*(K43-$I$34)),1)</f>
+      <c r="K54" s="122">
+        <f t="shared" si="6"/>
         <v>1.0121034455497457</v>
       </c>
-      <c r="L54" s="140">
-        <f>IF(L43&gt;$I$34, EXP((LN(1.062)/10)*(L43-$I$34)),1)</f>
+      <c r="L54" s="122">
+        <f t="shared" si="6"/>
         <v>1.043006852485771</v>
       </c>
-      <c r="M54" s="132">
-        <f>IF(M43&gt;$I$34, EXP((LN(1.062)/10)*(M43-$I$34)),1)</f>
+      <c r="M54" s="115">
+        <f t="shared" si="6"/>
         <v>1.0748538591738301</v>
       </c>
       <c r="N54" s="55">
-        <f>IF(N43&gt;$I$34, EXP((LN(1.062)/10)*(N43-$I$34)),1)</f>
+        <f t="shared" si="6"/>
         <v>1.1076732773398887</v>
       </c>
       <c r="O54" s="55">
-        <f>IF(O43&gt;$I$34, EXP((LN(1.062)/10)*(O43-$I$34)),1)</f>
+        <f t="shared" si="6"/>
         <v>1.1414947984426076</v>
       </c>
       <c r="P54" s="55">
-        <f>IF(P43&gt;$I$34, EXP((LN(1.062)/10)*(P43-$I$34)),1)</f>
+        <f t="shared" si="6"/>
         <v>1.1763490205349618</v>
       </c>
       <c r="Q54" s="55">
-        <f>IF(Q43&gt;$I$34, EXP((LN(1.062)/10)*(Q43-$I$34)),1)</f>
+        <f t="shared" si="6"/>
         <v>1.2122674759460494</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="114"/>
+      <c r="A55" s="191"/>
       <c r="B55" s="15" t="s">
         <v>80</v>
       </c>
@@ -4960,57 +4964,57 @@
       </c>
       <c r="D55" s="68"/>
       <c r="E55" s="68"/>
-      <c r="F55" s="152">
+      <c r="F55" s="134">
         <f>SUM(G55:Q55)</f>
         <v>7.1008998307338034E-2</v>
       </c>
-      <c r="G55" s="138">
-        <f>G44*(G54-1)</f>
+      <c r="G55" s="120">
+        <f t="shared" ref="G55:Q55" si="7">G44*(G54-1)</f>
         <v>0</v>
       </c>
-      <c r="H55" s="138">
-        <f>H44*(H54-1)</f>
+      <c r="H55" s="120">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I55" s="138">
-        <f>I44*(I54-1)</f>
+      <c r="I55" s="120">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J55" s="138">
-        <f>J44*(J54-1)</f>
+      <c r="J55" s="120">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K55" s="138">
-        <f>K44*(K54-1)</f>
+      <c r="K55" s="120">
+        <f t="shared" si="7"/>
         <v>1.6853970556822639E-3</v>
       </c>
-      <c r="L55" s="138">
-        <f>L44*(L54-1)</f>
+      <c r="L55" s="120">
+        <f t="shared" si="7"/>
         <v>1.3567100145471106E-2</v>
       </c>
-      <c r="M55" s="130">
-        <f>M44*(M54-1)</f>
+      <c r="M55" s="113">
+        <f t="shared" si="7"/>
         <v>1.3541162027583832E-2</v>
       </c>
       <c r="N55" s="54">
-        <f>N44*(N54-1)</f>
+        <f t="shared" si="7"/>
         <v>1.5796006680780964E-2</v>
       </c>
       <c r="O55" s="54">
-        <f>O44*(O54-1)</f>
+        <f t="shared" si="7"/>
         <v>1.6866633387219405E-2</v>
       </c>
       <c r="P55" s="54">
-        <f>P44*(P54-1)</f>
+        <f t="shared" si="7"/>
         <v>8.5340480462440024E-3</v>
       </c>
       <c r="Q55" s="54">
-        <f>Q44*(Q54-1)</f>
+        <f t="shared" si="7"/>
         <v>1.0186509643564665E-3</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="114"/>
+      <c r="A56" s="191"/>
       <c r="B56" s="15" t="s">
         <v>100</v>
       </c>
@@ -5020,24 +5024,24 @@
       </c>
       <c r="D56" s="68"/>
       <c r="E56" s="68"/>
-      <c r="F56" s="152">
+      <c r="F56" s="134">
         <f>F55/(1+F55)</f>
         <v>6.6301028674421281E-2</v>
       </c>
-      <c r="G56" s="138"/>
-      <c r="H56" s="138"/>
-      <c r="I56" s="138"/>
-      <c r="J56" s="138"/>
-      <c r="K56" s="138"/>
-      <c r="L56" s="138"/>
-      <c r="M56" s="130"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="120"/>
+      <c r="I56" s="120"/>
+      <c r="J56" s="120"/>
+      <c r="K56" s="120"/>
+      <c r="L56" s="120"/>
+      <c r="M56" s="113"/>
       <c r="N56" s="54"/>
       <c r="O56" s="54"/>
       <c r="P56" s="54"/>
       <c r="Q56" s="54"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="115"/>
+      <c r="A57" s="192"/>
       <c r="B57" s="39" t="s">
         <v>123</v>
       </c>
@@ -5047,92 +5051,92 @@
       </c>
       <c r="D57" s="70"/>
       <c r="E57" s="70"/>
-      <c r="F57" s="156">
+      <c r="F57" s="138">
         <f>0.0059261*F56*F42</f>
         <v>8171.0494489193279</v>
       </c>
-      <c r="G57" s="139"/>
-      <c r="H57" s="139"/>
-      <c r="I57" s="139"/>
-      <c r="J57" s="139"/>
-      <c r="K57" s="139"/>
-      <c r="L57" s="139"/>
-      <c r="M57" s="134"/>
+      <c r="G57" s="121"/>
+      <c r="H57" s="121"/>
+      <c r="I57" s="121"/>
+      <c r="J57" s="121"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="117"/>
       <c r="N57" s="57"/>
       <c r="O57" s="57"/>
       <c r="P57" s="57"/>
       <c r="Q57" s="57"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="113" t="s">
+      <c r="A58" s="190" t="s">
         <v>62</v>
       </c>
       <c r="B58" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="150"/>
-      <c r="D58" s="162"/>
-      <c r="E58" s="168"/>
+      <c r="C58" s="132"/>
+      <c r="D58" s="144"/>
+      <c r="E58" s="150"/>
       <c r="F58" s="66"/>
-      <c r="G58" s="140">
-        <f>IF(G43&gt;$I$35, EXP((LN(1.08)/10)*(G43-$I$35)),1)</f>
+      <c r="G58" s="122">
+        <f t="shared" ref="G58:Q58" si="8">IF(G43&gt;$I$35, EXP((LN(1.08)/10)*(G43-$I$35)),1)</f>
         <v>1</v>
       </c>
-      <c r="H58" s="140">
-        <f>IF(H43&gt;$I$35, EXP((LN(1.08)/10)*(H43-$I$35)),1)</f>
+      <c r="H58" s="122">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I58" s="140">
-        <f>IF(I43&gt;$I$35, EXP((LN(1.08)/10)*(I43-$I$35)),1)</f>
+      <c r="I58" s="122">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="J58" s="140">
-        <f>IF(J43&gt;$I$35, EXP((LN(1.08)/10)*(J43-$I$35)),1)</f>
+      <c r="J58" s="122">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K58" s="140">
-        <f>IF(K43&gt;$I$35, EXP((LN(1.08)/10)*(K43-$I$35)),1)</f>
+      <c r="K58" s="122">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="L58" s="140">
-        <f>IF(L43&gt;$I$35, EXP((LN(1.08)/10)*(L43-$I$35)),1)</f>
+      <c r="L58" s="122">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="M58" s="132">
-        <f>IF(M43&gt;$I$35, EXP((LN(1.08)/10)*(M43-$I$35)),1)</f>
+      <c r="M58" s="115">
+        <f t="shared" si="8"/>
         <v>1.0312631565524872</v>
       </c>
       <c r="N58" s="55">
-        <f>IF(N43&gt;$I$35, EXP((LN(1.08)/10)*(N43-$I$35)),1)</f>
+        <f t="shared" si="8"/>
         <v>1.0717201098736591</v>
       </c>
       <c r="O58" s="55">
-        <f>IF(O43&gt;$I$35, EXP((LN(1.08)/10)*(O43-$I$35)),1)</f>
+        <f t="shared" si="8"/>
         <v>1.1137642090766864</v>
       </c>
       <c r="P58" s="55">
-        <f>IF(P43&gt;$I$35, EXP((LN(1.08)/10)*(P43-$I$35)),1)</f>
+        <f t="shared" si="8"/>
         <v>1.157457718663552</v>
       </c>
       <c r="Q58" s="55">
-        <f>IF(Q43&gt;$I$35, EXP((LN(1.08)/10)*(Q43-$I$35)),1)</f>
+        <f t="shared" si="8"/>
         <v>1.2028653458028213</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="114"/>
+      <c r="A59" s="191"/>
       <c r="B59" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C59" s="118">
+      <c r="C59" s="103">
         <f>SUM(M59:Q59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="D59" s="160">
+      <c r="D59" s="142">
         <f>SUM(L59:Q59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="E59" s="161">
+      <c r="E59" s="143">
         <f>SUM(G59:Q59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
@@ -5140,267 +5144,267 @@
         <f>SUM(G59:Q59)</f>
         <v>3.8331542536053996E-2</v>
       </c>
-      <c r="G59" s="138">
-        <f>G44*(G58-1)</f>
+      <c r="G59" s="120">
+        <f t="shared" ref="G59:Q59" si="9">G44*(G58-1)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="138">
-        <f>H44*(H58-1)</f>
+      <c r="H59" s="120">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I59" s="138">
-        <f>I44*(I58-1)</f>
+      <c r="I59" s="120">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J59" s="138">
-        <f>J44*(J58-1)</f>
+      <c r="J59" s="120">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K59" s="138">
-        <f>K44*(K58-1)</f>
+      <c r="K59" s="120">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L59" s="138">
-        <f>L44*(L58-1)</f>
+      <c r="L59" s="120">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M59" s="130">
-        <f>M44*(M58-1)</f>
+      <c r="M59" s="113">
+        <f t="shared" si="9"/>
         <v>5.6555463277831062E-3</v>
       </c>
       <c r="N59" s="54">
-        <f>N44*(N58-1)</f>
+        <f t="shared" si="9"/>
         <v>1.0521564520921027E-2</v>
       </c>
       <c r="O59" s="54">
-        <f>O44*(O58-1)</f>
+        <f t="shared" si="9"/>
         <v>1.3561058273543175E-2</v>
       </c>
       <c r="P59" s="54">
-        <f>P44*(P58-1)</f>
+        <f t="shared" si="9"/>
         <v>7.6198423572209177E-3</v>
       </c>
       <c r="Q59" s="54">
-        <f>Q44*(Q58-1)</f>
+        <f t="shared" si="9"/>
         <v>9.7353105658576995E-4</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="114"/>
+      <c r="A60" s="191"/>
       <c r="B60" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C60" s="118">
+      <c r="C60" s="103">
         <f>C59/(1+C59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="D60" s="160">
-        <f t="shared" ref="D60:E60" si="1">D59/(1+D59)</f>
+      <c r="D60" s="142">
+        <f t="shared" ref="D60:E60" si="10">D59/(1+D59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="E60" s="161">
-        <f t="shared" si="1"/>
+      <c r="E60" s="143">
+        <f t="shared" si="10"/>
         <v>3.69164770266266E-2</v>
       </c>
       <c r="F60" s="68">
         <f>F59/(1+F59)</f>
         <v>3.69164770266266E-2</v>
       </c>
-      <c r="G60" s="138"/>
-      <c r="H60" s="138"/>
-      <c r="I60" s="138"/>
-      <c r="J60" s="138"/>
-      <c r="K60" s="138"/>
-      <c r="L60" s="138"/>
-      <c r="M60" s="130"/>
+      <c r="G60" s="120"/>
+      <c r="H60" s="120"/>
+      <c r="I60" s="120"/>
+      <c r="J60" s="120"/>
+      <c r="K60" s="120"/>
+      <c r="L60" s="120"/>
+      <c r="M60" s="113"/>
       <c r="N60" s="54"/>
       <c r="O60" s="54"/>
       <c r="P60" s="54"/>
       <c r="Q60" s="54"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="115"/>
+      <c r="A61" s="192"/>
       <c r="B61" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="C61" s="119">
+      <c r="C61" s="104">
         <f>0.00127695*C60*$F$42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="D61" s="163">
-        <f t="shared" ref="D61:E61" si="2">0.00127695*D60*$F$42</f>
+      <c r="D61" s="145">
+        <f t="shared" ref="D61:E61" si="11">0.00127695*D60*$F$42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="E61" s="169">
-        <f t="shared" si="2"/>
+      <c r="E61" s="151">
+        <f t="shared" si="11"/>
         <v>980.35357762371382</v>
       </c>
       <c r="F61" s="70">
         <f>0.00127695*F60*F42</f>
         <v>980.35357762371382</v>
       </c>
-      <c r="G61" s="139"/>
-      <c r="H61" s="139"/>
-      <c r="I61" s="139"/>
-      <c r="J61" s="139"/>
-      <c r="K61" s="139"/>
-      <c r="L61" s="139"/>
-      <c r="M61" s="134"/>
+      <c r="G61" s="121"/>
+      <c r="H61" s="121"/>
+      <c r="I61" s="121"/>
+      <c r="J61" s="121"/>
+      <c r="K61" s="121"/>
+      <c r="L61" s="121"/>
+      <c r="M61" s="117"/>
       <c r="N61" s="57"/>
       <c r="O61" s="57"/>
       <c r="P61" s="57"/>
       <c r="Q61" s="57"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="111" t="s">
+      <c r="A62" s="185" t="s">
         <v>43</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C62" s="116"/>
-      <c r="D62" s="164"/>
-      <c r="E62" s="170"/>
-      <c r="F62" s="157"/>
-      <c r="G62" s="142">
-        <f>IF(G43&gt;$I$30,((78.927 - 3.1162 * G43 + 0.0342 * G43^2)/100),0)</f>
+      <c r="C62" s="101"/>
+      <c r="D62" s="146"/>
+      <c r="E62" s="152"/>
+      <c r="F62" s="139"/>
+      <c r="G62" s="124">
+        <f t="shared" ref="G62:Q62" si="12">IF(G43&gt;$I$30,((78.927 - 3.1162 * G43 + 0.0342 * G43^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="H62" s="142">
-        <f>IF(H43&gt;$I$30,((78.927 - 3.1162 * H43 + 0.0342 * H43^2)/100),0)</f>
+      <c r="H62" s="124">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I62" s="142">
-        <f>IF(I43&gt;$I$30,((78.927 - 3.1162 * I43 + 0.0342 * I43^2)/100),0)</f>
+      <c r="I62" s="124">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J62" s="142">
-        <f>IF(J43&gt;$I$30,((78.927 - 3.1162 * J43 + 0.0342 * J43^2)/100),0)</f>
+      <c r="J62" s="124">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K62" s="142">
-        <f>IF(K43&gt;$I$30,((78.927 - 3.1162 * K43 + 0.0342 * K43^2)/100),0)</f>
+      <c r="K62" s="124">
+        <f t="shared" si="12"/>
         <v>8.0134000000000191E-2</v>
       </c>
-      <c r="L62" s="142">
-        <f>IF(L43&gt;$I$30,((78.927 - 3.1162 * L43 + 0.0342 * L43^2)/100),0)</f>
+      <c r="L62" s="124">
+        <f t="shared" si="12"/>
         <v>9.3613999999999892E-2</v>
       </c>
-      <c r="M62" s="135">
-        <f>IF(M43&gt;$I$30,((78.927 - 3.1162 * M43 + 0.0342 * M43^2)/100),0)</f>
+      <c r="M62" s="118">
+        <f t="shared" si="12"/>
         <v>0.1241940000000001</v>
       </c>
       <c r="N62" s="58">
-        <f>IF(N43&gt;$I$30,((78.927 - 3.1162 * N43 + 0.0342 * N43^2)/100),0)</f>
+        <f t="shared" si="12"/>
         <v>0.17187400000000011</v>
       </c>
       <c r="O62" s="58">
-        <f>IF(O43&gt;$I$30,((78.927 - 3.1162 * O43 + 0.0342 * O43^2)/100),0)</f>
+        <f t="shared" si="12"/>
         <v>0.23665399999999978</v>
       </c>
       <c r="P62" s="58">
-        <f>IF(P43&gt;$I$30,((78.927 - 3.1162 * P43 + 0.0342 * P43^2)/100),0)</f>
+        <f t="shared" si="12"/>
         <v>0.31853400000000021</v>
       </c>
       <c r="Q62" s="58">
-        <f>IF(Q43&gt;$I$30,((78.927 - 3.1162 * Q43 + 0.0342 * Q43^2)/100),0)</f>
+        <f t="shared" si="12"/>
         <v>0.41751400000000016</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="112"/>
+      <c r="A63" s="186"/>
       <c r="B63" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C63" s="116">
+      <c r="C63" s="101">
         <f>SUM(M63:Q63)</f>
         <v>9.3309634085492005E-2</v>
       </c>
-      <c r="D63" s="164">
+      <c r="D63" s="146">
         <f>SUM(L63:Q63)</f>
         <v>0.12284145144967462</v>
       </c>
-      <c r="E63" s="170">
+      <c r="E63" s="152">
         <f>SUM(G63:Q63)</f>
         <v>0.13400005972406637</v>
       </c>
-      <c r="F63" s="157">
+      <c r="F63" s="139">
         <f>SUM(G63:Q63)</f>
         <v>0.13400005972406637</v>
       </c>
       <c r="G63" s="73">
-        <f>G44*G62</f>
+        <f t="shared" ref="G63:Q63" si="13">G44*G62</f>
         <v>0</v>
       </c>
       <c r="H63" s="73">
-        <f>H44*H62</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I63" s="73">
-        <f>I44*I62</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J63" s="73">
-        <f>J44*J62</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K63" s="73">
-        <f>K44*K62</f>
+        <f t="shared" si="13"/>
         <v>1.1158608274391753E-2</v>
       </c>
       <c r="L63" s="73">
-        <f>L44*L62</f>
+        <f t="shared" si="13"/>
         <v>2.9531817364182603E-2</v>
       </c>
-      <c r="M63" s="130">
-        <f>M44*M62</f>
+      <c r="M63" s="113">
+        <f t="shared" si="13"/>
         <v>2.2466858695265539E-2</v>
       </c>
       <c r="N63" s="54">
-        <f>N44*N62</f>
+        <f t="shared" si="13"/>
         <v>2.5214453570336123E-2</v>
       </c>
       <c r="O63" s="54">
-        <f>O44*O62</f>
+        <f t="shared" si="13"/>
         <v>2.8209915145665603E-2</v>
       </c>
       <c r="P63" s="54">
-        <f>P44*P62</f>
+        <f t="shared" si="13"/>
         <v>1.5414797610533706E-2</v>
       </c>
       <c r="Q63" s="54">
-        <f>Q44*Q62</f>
+        <f t="shared" si="13"/>
         <v>2.0036090636910467E-3</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="110"/>
+      <c r="A64" s="184"/>
       <c r="B64" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="C64" s="120">
+      <c r="C64" s="105">
         <f>C63*$J$30*$F$42</f>
         <v>21345.5705628</v>
       </c>
-      <c r="D64" s="165">
-        <f t="shared" ref="D64:E64" si="3">D63*$J$30*$F$42</f>
+      <c r="D64" s="147">
+        <f t="shared" ref="D64:E64" si="14">D63*$J$30*$F$42</f>
         <v>28101.287671467711</v>
       </c>
-      <c r="E64" s="171">
-        <f t="shared" si="3"/>
+      <c r="E64" s="153">
+        <f t="shared" si="14"/>
         <v>30653.937916408569</v>
       </c>
-      <c r="F64" s="155">
+      <c r="F64" s="137">
         <f>J30*F63*F42</f>
         <v>30653.937916408569</v>
       </c>
-      <c r="G64" s="139"/>
-      <c r="H64" s="139"/>
-      <c r="I64" s="139"/>
-      <c r="J64" s="139"/>
-      <c r="K64" s="139"/>
-      <c r="L64" s="139"/>
-      <c r="M64" s="134"/>
+      <c r="G64" s="121"/>
+      <c r="H64" s="121"/>
+      <c r="I64" s="121"/>
+      <c r="J64" s="121"/>
+      <c r="K64" s="121"/>
+      <c r="L64" s="121"/>
+      <c r="M64" s="117"/>
       <c r="N64" s="57"/>
       <c r="O64" s="57"/>
       <c r="P64" s="57"/>
@@ -5432,20 +5436,20 @@
       <c r="D66" s="22"/>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
-      <c r="G66" s="123" t="s">
+      <c r="G66" s="180" t="s">
         <v>84</v>
       </c>
-      <c r="H66" s="123"/>
-      <c r="I66" s="123"/>
-      <c r="J66" s="123"/>
-      <c r="K66" s="123"/>
-      <c r="L66" s="107" t="s">
+      <c r="H66" s="180"/>
+      <c r="I66" s="180"/>
+      <c r="J66" s="180"/>
+      <c r="K66" s="180"/>
+      <c r="L66" s="181" t="s">
         <v>85</v>
       </c>
-      <c r="M66" s="108"/>
-      <c r="N66" s="108"/>
-      <c r="O66" s="108"/>
-      <c r="P66" s="108"/>
+      <c r="M66" s="182"/>
+      <c r="N66" s="182"/>
+      <c r="O66" s="182"/>
+      <c r="P66" s="182"/>
       <c r="Q66" s="23"/>
     </row>
     <row r="67" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -5457,19 +5461,19 @@
       <c r="F67" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="G67" s="124" t="s">
+      <c r="G67" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="H67" s="124" t="s">
+      <c r="H67" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="I67" s="124" t="s">
+      <c r="I67" s="108" t="s">
         <v>101</v>
       </c>
-      <c r="J67" s="124" t="s">
+      <c r="J67" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="K67" s="124" t="s">
+      <c r="K67" s="108" t="s">
         <v>105</v>
       </c>
       <c r="L67" s="46" t="s">
@@ -5490,7 +5494,7 @@
       <c r="Q67" s="15"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68" s="113" t="s">
+      <c r="A68" s="190" t="s">
         <v>92</v>
       </c>
       <c r="B68" s="18" t="s">
@@ -5503,23 +5507,23 @@
         <f>SUM(G68:P68)</f>
         <v>15021000</v>
       </c>
-      <c r="G68" s="143">
+      <c r="G68" s="125">
         <f>C14</f>
         <v>64582.789500000006</v>
       </c>
-      <c r="H68" s="143">
+      <c r="H68" s="125">
         <f>D14</f>
         <v>239111.78849999997</v>
       </c>
-      <c r="I68" s="143">
+      <c r="I68" s="125">
         <f>E14</f>
         <v>1126116.8595</v>
       </c>
-      <c r="J68" s="143">
+      <c r="J68" s="125">
         <f>F14</f>
         <v>2838600.9855</v>
       </c>
-      <c r="K68" s="143">
+      <c r="K68" s="125">
         <f>G14</f>
         <v>3242087.577</v>
       </c>
@@ -5546,7 +5550,7 @@
       <c r="Q68" s="15"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="114"/>
+      <c r="A69" s="191"/>
       <c r="B69" s="15" t="s">
         <v>97</v>
       </c>
@@ -5554,19 +5558,19 @@
       <c r="D69" s="15"/>
       <c r="E69" s="15"/>
       <c r="F69" s="15"/>
-      <c r="G69" s="125">
+      <c r="G69" s="109">
         <v>27</v>
       </c>
-      <c r="H69" s="125">
+      <c r="H69" s="109">
         <v>32</v>
       </c>
-      <c r="I69" s="125">
+      <c r="I69" s="109">
         <v>37</v>
       </c>
-      <c r="J69" s="125">
+      <c r="J69" s="109">
         <v>42</v>
       </c>
-      <c r="K69" s="125">
+      <c r="K69" s="109">
         <v>47</v>
       </c>
       <c r="L69" s="48">
@@ -5587,7 +5591,7 @@
       <c r="Q69" s="15"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="115"/>
+      <c r="A70" s="192"/>
       <c r="B70" s="19" t="s">
         <v>98</v>
       </c>
@@ -5595,44 +5599,44 @@
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
       <c r="F70" s="25"/>
-      <c r="G70" s="144">
+      <c r="G70" s="126">
         <f>G68/$F$68</f>
         <v>4.2995000000000004E-3</v>
       </c>
-      <c r="H70" s="144">
-        <f t="shared" ref="H70:P70" si="4">H68/$F$68</f>
+      <c r="H70" s="126">
+        <f t="shared" ref="H70:P70" si="15">H68/$F$68</f>
         <v>1.5918499999999999E-2</v>
       </c>
-      <c r="I70" s="144">
-        <f t="shared" si="4"/>
+      <c r="I70" s="126">
+        <f t="shared" si="15"/>
         <v>7.4969499999999994E-2</v>
       </c>
-      <c r="J70" s="144">
-        <f t="shared" si="4"/>
+      <c r="J70" s="126">
+        <f t="shared" si="15"/>
         <v>0.18897549999999999</v>
       </c>
-      <c r="K70" s="144">
-        <f t="shared" si="4"/>
+      <c r="K70" s="126">
+        <f t="shared" si="15"/>
         <v>0.215837</v>
       </c>
       <c r="L70" s="63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>0.2252513148259104</v>
       </c>
       <c r="M70" s="60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>0.17857665934358566</v>
       </c>
       <c r="N70" s="60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>8.5447040809533317E-2</v>
       </c>
       <c r="O70" s="60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>1.0398775048265762E-2</v>
       </c>
       <c r="P70" s="60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>3.2620997270487985E-4</v>
       </c>
       <c r="Q70" s="15"/>
@@ -5642,23 +5646,23 @@
         <v>93</v>
       </c>
       <c r="B71" s="31"/>
-      <c r="C71" s="121" t="s">
+      <c r="C71" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="D71" s="166" t="s">
+      <c r="D71" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="172" t="s">
+      <c r="E71" s="154" t="s">
         <v>167</v>
       </c>
-      <c r="F71" s="158" t="s">
+      <c r="F71" s="140" t="s">
         <v>125</v>
       </c>
-      <c r="G71" s="145"/>
-      <c r="H71" s="145"/>
-      <c r="I71" s="145"/>
-      <c r="J71" s="145"/>
-      <c r="K71" s="145"/>
+      <c r="G71" s="127"/>
+      <c r="H71" s="127"/>
+      <c r="I71" s="127"/>
+      <c r="J71" s="127"/>
+      <c r="K71" s="127"/>
       <c r="L71" s="64"/>
       <c r="M71" s="61"/>
       <c r="N71" s="61"/>
@@ -5667,150 +5671,150 @@
       <c r="Q71" s="15"/>
     </row>
     <row r="72" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="109" t="s">
+      <c r="A72" s="183" t="s">
         <v>50</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C72" s="122"/>
-      <c r="D72" s="167"/>
-      <c r="E72" s="173"/>
-      <c r="F72" s="159"/>
-      <c r="G72" s="146">
+      <c r="C72" s="107"/>
+      <c r="D72" s="149"/>
+      <c r="E72" s="155"/>
+      <c r="F72" s="141"/>
+      <c r="G72" s="128">
         <f>IF(G69&gt;$I$31,((19.4312 - 0.9336 *  G69 + 0.0126 *  G69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="H72" s="146">
-        <f t="shared" ref="H72:P72" si="5">IF(H69&gt;$I$31,((19.4312 - 0.9336 *  H69 + 0.0126 *  H69^2)/100),0)</f>
+      <c r="H72" s="128">
+        <f t="shared" ref="H72:P72" si="16">IF(H69&gt;$I$31,((19.4312 - 0.9336 *  H69 + 0.0126 *  H69^2)/100),0)</f>
         <v>0</v>
       </c>
-      <c r="I72" s="146">
-        <f t="shared" si="5"/>
+      <c r="I72" s="128">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J72" s="146">
-        <f t="shared" si="5"/>
+      <c r="J72" s="128">
+        <f t="shared" si="16"/>
         <v>2.4464000000000041E-2</v>
       </c>
-      <c r="K72" s="146">
-        <f t="shared" si="5"/>
+      <c r="K72" s="128">
+        <f t="shared" si="16"/>
         <v>3.3854000000000044E-2</v>
       </c>
       <c r="L72" s="51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>4.9544000000000032E-2</v>
       </c>
       <c r="M72" s="52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>7.1534000000000125E-2</v>
       </c>
       <c r="N72" s="52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>9.9824000000000052E-2</v>
       </c>
       <c r="O72" s="52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>0.13441399999999995</v>
       </c>
       <c r="P72" s="52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>0.17530400000000002</v>
       </c>
     </row>
     <row r="73" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="109"/>
+      <c r="A73" s="183"/>
       <c r="B73" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C73" s="122">
+      <c r="C73" s="107">
         <f>SUM(L73:P73)</f>
         <v>3.3918746155382498E-2</v>
       </c>
-      <c r="D73" s="167">
+      <c r="D73" s="149">
         <f>SUM(K73:P73)</f>
         <v>4.1225691953382514E-2</v>
       </c>
-      <c r="E73" s="173">
+      <c r="E73" s="155">
         <f>SUM(G73:P73)</f>
         <v>4.5848788585382522E-2</v>
       </c>
-      <c r="F73" s="159">
+      <c r="F73" s="141">
         <f>SUM(G73:P73)</f>
         <v>4.5848788585382522E-2</v>
       </c>
-      <c r="G73" s="146">
+      <c r="G73" s="128">
         <f>G72*G70</f>
         <v>0</v>
       </c>
-      <c r="H73" s="146">
-        <f t="shared" ref="H73:P73" si="6">H72*H70</f>
+      <c r="H73" s="128">
+        <f t="shared" ref="H73:P73" si="17">H72*H70</f>
         <v>0</v>
       </c>
-      <c r="I73" s="146">
-        <f t="shared" si="6"/>
+      <c r="I73" s="128">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J73" s="146">
-        <f t="shared" si="6"/>
+      <c r="J73" s="128">
+        <f t="shared" si="17"/>
         <v>4.6230966320000072E-3</v>
       </c>
-      <c r="K73" s="146">
-        <f t="shared" si="6"/>
+      <c r="K73" s="128">
+        <f t="shared" si="17"/>
         <v>7.3069457980000094E-3</v>
       </c>
       <c r="L73" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.1159851141734912E-2</v>
       </c>
       <c r="M73" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.2774302749484078E-2</v>
       </c>
       <c r="N73" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>8.5296654017708584E-3</v>
       </c>
       <c r="O73" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.3977409493375935E-3</v>
       </c>
       <c r="P73" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>5.718591305505626E-5</v>
       </c>
     </row>
     <row r="74" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="110"/>
+      <c r="A74" s="184"/>
       <c r="B74" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="C74" s="120">
+      <c r="C74" s="105">
         <f>$J$31*C73*$F$68</f>
         <v>5094.9348600000048</v>
       </c>
-      <c r="D74" s="165">
-        <f t="shared" ref="D74:E74" si="7">$J$31*D73*$F$68</f>
+      <c r="D74" s="147">
+        <f t="shared" ref="D74:E74" si="18">$J$31*D73*$F$68</f>
         <v>6192.5111883175869</v>
       </c>
-      <c r="E74" s="171">
-        <f t="shared" si="7"/>
+      <c r="E74" s="153">
+        <f t="shared" si="18"/>
         <v>6886.9465334103088</v>
       </c>
-      <c r="F74" s="155">
+      <c r="F74" s="137">
         <f>J31*F73*F68</f>
         <v>6886.9465334103088</v>
       </c>
-      <c r="G74" s="147"/>
-      <c r="H74" s="147"/>
-      <c r="I74" s="147"/>
-      <c r="J74" s="147"/>
-      <c r="K74" s="147"/>
-      <c r="L74" s="149"/>
-      <c r="M74" s="148"/>
-      <c r="N74" s="148"/>
-      <c r="O74" s="148"/>
-      <c r="P74" s="148"/>
+      <c r="G74" s="129"/>
+      <c r="H74" s="129"/>
+      <c r="I74" s="129"/>
+      <c r="J74" s="129"/>
+      <c r="K74" s="129"/>
+      <c r="L74" s="131"/>
+      <c r="M74" s="130"/>
+      <c r="N74" s="130"/>
+      <c r="O74" s="130"/>
+      <c r="P74" s="130"/>
       <c r="Q74" s="19"/>
     </row>
     <row r="77" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.35">
@@ -5822,16 +5826,16 @@
       </c>
     </row>
     <row r="78" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="116" t="s">
+      <c r="C78" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="D78" s="164" t="s">
+      <c r="D78" s="146" t="s">
         <v>165</v>
       </c>
-      <c r="E78" s="170" t="s">
+      <c r="E78" s="152" t="s">
         <v>167</v>
       </c>
-      <c r="F78" s="157" t="s">
+      <c r="F78" s="139" t="s">
         <v>125</v>
       </c>
       <c r="H78" s="4"/>
@@ -5840,19 +5844,19 @@
       <c r="B79" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C79" s="174">
+      <c r="C79" s="156">
         <f>C61+C64+C74</f>
         <v>27420.859000423719</v>
       </c>
-      <c r="D79" s="177">
-        <f t="shared" ref="D79" si="8">D61+D64+D74</f>
+      <c r="D79" s="159">
+        <f t="shared" ref="D79" si="19">D61+D64+D74</f>
         <v>35274.152437409015</v>
       </c>
-      <c r="E79" s="180">
+      <c r="E79" s="162">
         <f>E61+E64+E74</f>
         <v>38521.238027442596</v>
       </c>
-      <c r="F79" s="183">
+      <c r="F79" s="165">
         <f>F49+F53+F57+F64+F74</f>
         <v>308626.30242553435</v>
       </c>
@@ -5862,19 +5866,19 @@
       <c r="B80" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="175">
+      <c r="C80" s="157">
         <f>C79*$C$85</f>
         <v>1919460130.0296605</v>
       </c>
-      <c r="D80" s="178">
-        <f t="shared" ref="D80:E80" si="9">D79*$C$85</f>
+      <c r="D80" s="160">
+        <f t="shared" ref="D80:E80" si="20">D79*$C$85</f>
         <v>2469190670.6186309</v>
       </c>
-      <c r="E80" s="181">
-        <f t="shared" si="9"/>
+      <c r="E80" s="163">
+        <f t="shared" si="20"/>
         <v>2696486661.9209819</v>
       </c>
-      <c r="F80" s="184">
+      <c r="F80" s="166">
         <f>F79*C85</f>
         <v>21603841169.787403</v>
       </c>
@@ -5884,19 +5888,19 @@
       <c r="B81" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="C81" s="174">
+      <c r="C81" s="156">
         <f>(C79/$C$86)*100000</f>
         <v>106.86035636315063</v>
       </c>
-      <c r="D81" s="177">
-        <f t="shared" ref="D81:E81" si="10">(D79/$C$86)*100000</f>
+      <c r="D81" s="159">
+        <f t="shared" ref="D81:E81" si="21">(D79/$C$86)*100000</f>
         <v>137.46500428055077</v>
       </c>
-      <c r="E81" s="180">
-        <f t="shared" si="10"/>
+      <c r="E81" s="162">
+        <f t="shared" si="21"/>
         <v>150.11904707648497</v>
       </c>
-      <c r="F81" s="183">
+      <c r="F81" s="165">
         <f>(F79/C86)*100000</f>
         <v>1202.730981539436</v>
       </c>
@@ -5905,19 +5909,19 @@
       <c r="B82" s="85" t="s">
         <v>142</v>
       </c>
-      <c r="C82" s="176">
+      <c r="C82" s="158">
         <f>C80/$C$86</f>
         <v>74.802249454205437</v>
       </c>
-      <c r="D82" s="179">
-        <f t="shared" ref="D82:E82" si="11">D80/$C$86</f>
+      <c r="D82" s="161">
+        <f t="shared" ref="D82:E82" si="22">D80/$C$86</f>
         <v>96.225502996385529</v>
       </c>
-      <c r="E82" s="182">
-        <f t="shared" si="11"/>
+      <c r="E82" s="164">
+        <f t="shared" si="22"/>
         <v>105.08333295353948</v>
       </c>
-      <c r="F82" s="185">
+      <c r="F82" s="167">
         <f>(F80/C86)</f>
         <v>841.91168707760517</v>
       </c>
@@ -5974,7 +5978,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E626FF22-8137-4E66-B950-E8DCA56124BF}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -5985,7 +5989,7 @@
     <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>91</v>
       </c>
@@ -5999,7 +6003,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -6016,192 +6020,229 @@
         <v>308626.30242553435</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="193" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="193">
+        <v>27420.859000423719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="193" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="193">
+        <v>35274.152437409015</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="193" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="193">
+        <v>38521.238027442596</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="193" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="193">
+        <v>308626.30242553435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>93</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C16" t="s">
         <v>91</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D16" t="s">
         <v>165</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E16" t="s">
         <v>167</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F16" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>171</v>
-      </c>
-      <c r="F7">
-        <v>254483.32856966133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F8">
-        <v>8431.0399571348571</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F9">
-        <v>8171.0494489193279</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10">
-        <v>980.35357762371382</v>
-      </c>
-      <c r="D10">
-        <v>980.35357762371382</v>
-      </c>
-      <c r="E10">
-        <v>980.35357762371382</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11">
-        <v>21345.5705628</v>
-      </c>
-      <c r="D11">
-        <v>28101.287671467711</v>
-      </c>
-      <c r="E11">
-        <v>30653.937916408569</v>
-      </c>
-      <c r="F11">
-        <v>30653.937916408569</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12">
-        <v>5094.9348600000048</v>
-      </c>
-      <c r="D12">
-        <v>6192.5111883175869</v>
-      </c>
-      <c r="E12">
-        <v>6886.9465334103088</v>
-      </c>
-      <c r="F12">
-        <v>6886.9465334103088</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16">
-        <v>980.35357762371382</v>
-      </c>
-      <c r="F16">
-        <v>21345.5705628</v>
-      </c>
-      <c r="G16">
-        <v>5094.9348600000048</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>165</v>
-      </c>
-      <c r="E17">
-        <v>980.35357762371382</v>
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>171</v>
       </c>
       <c r="F17">
-        <v>28101.287671467711</v>
-      </c>
-      <c r="G17">
-        <v>6192.5111883175869</v>
+        <v>254483.32856966133</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18">
-        <v>980.35357762371382</v>
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>172</v>
       </c>
       <c r="F18">
-        <v>30653.937916408569</v>
-      </c>
-      <c r="G18">
-        <v>6886.9465334103088</v>
+        <v>8431.0399571348571</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F19">
+        <v>8171.0494489193279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="D20">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="E20">
+        <v>980.35357762371382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21">
+        <v>21345.5705628</v>
+      </c>
+      <c r="D21">
+        <v>28101.287671467711</v>
+      </c>
+      <c r="E21">
+        <v>30653.937916408569</v>
+      </c>
+      <c r="F21">
+        <v>30653.937916408569</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22">
+        <v>5094.9348600000048</v>
+      </c>
+      <c r="D22">
+        <v>6192.5111883175869</v>
+      </c>
+      <c r="E22">
+        <v>6886.9465334103088</v>
+      </c>
+      <c r="F22">
+        <v>6886.9465334103088</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F26">
+        <v>21345.5705628</v>
+      </c>
+      <c r="G26">
+        <v>5094.9348600000048</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F27">
+        <v>28101.287671467711</v>
+      </c>
+      <c r="G27">
+        <v>6192.5111883175869</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28">
+        <v>980.35357762371382</v>
+      </c>
+      <c r="F28">
+        <v>30653.937916408569</v>
+      </c>
+      <c r="G28">
+        <v>6886.9465334103088</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>125</v>
       </c>
-      <c r="B19">
+      <c r="B29">
         <v>254483.32856966133</v>
       </c>
-      <c r="C19">
+      <c r="C29">
         <v>8431.0399571348571</v>
       </c>
-      <c r="D19">
+      <c r="D29">
         <v>8171.0494489193279</v>
       </c>
-      <c r="F19">
+      <c r="F29">
         <v>30653.937916408569</v>
       </c>
-      <c r="G19">
+      <c r="G29">
         <v>6886.9465334103088</v>
       </c>
     </row>
